--- a/trades_all.xlsx
+++ b/trades_all.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1381"/>
+  <dimension ref="A1:K1399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66643,6 +66643,852 @@
         </is>
       </c>
     </row>
+    <row r="1382">
+      <c r="A1382" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B1382" t="inlineStr">
+        <is>
+          <t>10:12:56</t>
+        </is>
+      </c>
+      <c r="C1382" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1382" t="n">
+        <v>769.855</v>
+      </c>
+      <c r="G1382" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1382" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I1382" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1382" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="K1382" t="inlineStr">
+        <is>
+          <t>10:16:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B1383" t="inlineStr">
+        <is>
+          <t>10:16:52</t>
+        </is>
+      </c>
+      <c r="C1383" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1383" t="n">
+        <v>770.6701</v>
+      </c>
+      <c r="E1383" t="inlineStr">
+        <is>
+          <t>多</t>
+        </is>
+      </c>
+      <c r="F1383" t="n">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="G1383" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1383" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I1383" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1383" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="K1383" t="inlineStr">
+        <is>
+          <t>10:12:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B1384" t="inlineStr">
+        <is>
+          <t>10:25:04</t>
+        </is>
+      </c>
+      <c r="C1384" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1384" t="n">
+        <v>772.2299</v>
+      </c>
+      <c r="G1384" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1384" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I1384" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1384" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="K1384" t="inlineStr">
+        <is>
+          <t>10:27:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B1385" t="inlineStr">
+        <is>
+          <t>10:27:20</t>
+        </is>
+      </c>
+      <c r="C1385" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1385" t="n">
+        <v>772.655</v>
+      </c>
+      <c r="E1385" t="inlineStr">
+        <is>
+          <t>多</t>
+        </is>
+      </c>
+      <c r="F1385" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="G1385" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1385" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I1385" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1385" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="K1385" t="inlineStr">
+        <is>
+          <t>10:25:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B1386" t="inlineStr">
+        <is>
+          <t>10:30:28</t>
+        </is>
+      </c>
+      <c r="C1386" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1386" t="n">
+        <v>772.965</v>
+      </c>
+      <c r="G1386" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1386" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I1386" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1386" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="K1386" t="inlineStr">
+        <is>
+          <t>10:56:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B1387" t="inlineStr">
+        <is>
+          <t>10:33:36</t>
+        </is>
+      </c>
+      <c r="C1387" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1387" t="n">
+        <v>772.6108</v>
+      </c>
+      <c r="G1387" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1387" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I1387" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1387" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="K1387" t="inlineStr">
+        <is>
+          <t>10:56:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B1388" t="inlineStr">
+        <is>
+          <t>10:56:10</t>
+        </is>
+      </c>
+      <c r="C1388" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1388" t="n">
+        <v>772.6193</v>
+      </c>
+      <c r="E1388" t="inlineStr">
+        <is>
+          <t>多</t>
+        </is>
+      </c>
+      <c r="F1388" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="G1388" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1388" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I1388" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1388" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="K1388" t="inlineStr">
+        <is>
+          <t>10:33:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B1389" t="inlineStr">
+        <is>
+          <t>10:56:57</t>
+        </is>
+      </c>
+      <c r="C1389" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1389" t="n">
+        <v>772.425</v>
+      </c>
+      <c r="E1389" t="inlineStr">
+        <is>
+          <t>多</t>
+        </is>
+      </c>
+      <c r="F1389" t="n">
+        <v>-55.61</v>
+      </c>
+      <c r="G1389" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1389" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I1389" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1389" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="K1389" t="inlineStr">
+        <is>
+          <t>10:30:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B1390" t="inlineStr">
+        <is>
+          <t>11:21:41</t>
+        </is>
+      </c>
+      <c r="C1390" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1390" t="n">
+        <v>772.8996</v>
+      </c>
+      <c r="G1390" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1390" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I1390" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1390" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="K1390" t="inlineStr">
+        <is>
+          <t>11:23:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B1391" t="inlineStr">
+        <is>
+          <t>11:23:34</t>
+        </is>
+      </c>
+      <c r="C1391" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1391" t="n">
+        <v>773.4472</v>
+      </c>
+      <c r="E1391" t="inlineStr">
+        <is>
+          <t>多</t>
+        </is>
+      </c>
+      <c r="F1391" t="n">
+        <v>53.15</v>
+      </c>
+      <c r="G1391" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1391" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I1391" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1391" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="K1391" t="inlineStr">
+        <is>
+          <t>11:21:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B1392" t="inlineStr">
+        <is>
+          <t>11:36:55</t>
+        </is>
+      </c>
+      <c r="C1392" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1392" t="n">
+        <v>773.4299</v>
+      </c>
+      <c r="G1392" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1392" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I1392" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1392" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="K1392" t="inlineStr">
+        <is>
+          <t>11:38:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B1393" t="inlineStr">
+        <is>
+          <t>11:38:56</t>
+        </is>
+      </c>
+      <c r="C1393" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1393" t="n">
+        <v>773.45</v>
+      </c>
+      <c r="E1393" t="inlineStr">
+        <is>
+          <t>多</t>
+        </is>
+      </c>
+      <c r="F1393" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G1393" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1393" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I1393" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1393" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="K1393" t="inlineStr">
+        <is>
+          <t>11:36:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B1394" t="inlineStr">
+        <is>
+          <t>11:41:18</t>
+        </is>
+      </c>
+      <c r="C1394" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1394" t="n">
+        <v>773.4099</v>
+      </c>
+      <c r="G1394" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1394" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I1394" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1394" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="K1394" t="inlineStr">
+        <is>
+          <t>13:47:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B1395" t="inlineStr">
+        <is>
+          <t>12:04:43</t>
+        </is>
+      </c>
+      <c r="C1395" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1395" t="n">
+        <v>772.9645</v>
+      </c>
+      <c r="G1395" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1395" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I1395" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1395" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="K1395" t="inlineStr">
+        <is>
+          <t>12:07:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B1396" t="inlineStr">
+        <is>
+          <t>12:07:01</t>
+        </is>
+      </c>
+      <c r="C1396" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1396" t="n">
+        <v>773.3</v>
+      </c>
+      <c r="E1396" t="inlineStr">
+        <is>
+          <t>多</t>
+        </is>
+      </c>
+      <c r="F1396" t="n">
+        <v>31.94</v>
+      </c>
+      <c r="G1396" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1396" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I1396" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1396" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="K1396" t="inlineStr">
+        <is>
+          <t>12:04:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B1397" t="inlineStr">
+        <is>
+          <t>13:05:37</t>
+        </is>
+      </c>
+      <c r="C1397" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1397" t="n">
+        <v>772.175</v>
+      </c>
+      <c r="G1397" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1397" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I1397" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1397" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="K1397" t="inlineStr">
+        <is>
+          <t>13:45:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B1398" t="inlineStr">
+        <is>
+          <t>13:45:44</t>
+        </is>
+      </c>
+      <c r="C1398" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1398" t="n">
+        <v>772.2313</v>
+      </c>
+      <c r="E1398" t="inlineStr">
+        <is>
+          <t>多</t>
+        </is>
+      </c>
+      <c r="F1398" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="G1398" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1398" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I1398" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1398" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="K1398" t="inlineStr">
+        <is>
+          <t>13:05:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B1399" t="inlineStr">
+        <is>
+          <t>13:47:32</t>
+        </is>
+      </c>
+      <c r="C1399" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1399" t="n">
+        <v>772.3749</v>
+      </c>
+      <c r="E1399" t="inlineStr">
+        <is>
+          <t>多</t>
+        </is>
+      </c>
+      <c r="F1399" t="n">
+        <v>-105.11</v>
+      </c>
+      <c r="G1399" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1399" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I1399" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1399" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="K1399" t="inlineStr">
+        <is>
+          <t>11:41:18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trades_all.xlsx
+++ b/trades_all.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1399"/>
+  <dimension ref="A1:K1425"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67489,6 +67489,1228 @@
         </is>
       </c>
     </row>
+    <row r="1400">
+      <c r="A1400" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B1400" t="inlineStr">
+        <is>
+          <t>10:12:32</t>
+        </is>
+      </c>
+      <c r="C1400" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1400" t="n">
+        <v>774.025</v>
+      </c>
+      <c r="G1400" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1400" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I1400" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1400" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="K1400" t="inlineStr">
+        <is>
+          <t>10:17:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B1401" t="inlineStr">
+        <is>
+          <t>10:17:06</t>
+        </is>
+      </c>
+      <c r="C1401" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1401" t="n">
+        <v>774.1699</v>
+      </c>
+      <c r="E1401" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F1401" t="n">
+        <v>-16.1</v>
+      </c>
+      <c r="G1401" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1401" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I1401" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1401" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="K1401" t="inlineStr">
+        <is>
+          <t>10:12:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B1402" t="inlineStr">
+        <is>
+          <t>10:19:56</t>
+        </is>
+      </c>
+      <c r="C1402" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1402" t="n">
+        <v>774.3001</v>
+      </c>
+      <c r="G1402" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1402" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I1402" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1402" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="K1402" t="inlineStr">
+        <is>
+          <t>10:39:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B1403" t="inlineStr">
+        <is>
+          <t>10:39:13</t>
+        </is>
+      </c>
+      <c r="C1403" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1403" t="n">
+        <v>774.23</v>
+      </c>
+      <c r="E1403" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F1403" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="G1403" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1403" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I1403" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1403" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="K1403" t="inlineStr">
+        <is>
+          <t>10:19:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B1404" t="inlineStr">
+        <is>
+          <t>10:44:58</t>
+        </is>
+      </c>
+      <c r="C1404" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1404" t="n">
+        <v>774.6101</v>
+      </c>
+      <c r="G1404" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1404" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I1404" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1404" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="K1404" t="inlineStr">
+        <is>
+          <t>10:53:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B1405" t="inlineStr">
+        <is>
+          <t>10:53:47</t>
+        </is>
+      </c>
+      <c r="C1405" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1405" t="n">
+        <v>774.02</v>
+      </c>
+      <c r="E1405" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F1405" t="n">
+        <v>57.39</v>
+      </c>
+      <c r="G1405" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1405" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I1405" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1405" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="K1405" t="inlineStr">
+        <is>
+          <t>10:44:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B1406" t="inlineStr">
+        <is>
+          <t>11:02:33</t>
+        </is>
+      </c>
+      <c r="C1406" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1406" t="n">
+        <v>773.628</v>
+      </c>
+      <c r="G1406" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1406" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I1406" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1406" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="K1406" t="inlineStr">
+        <is>
+          <t>11:03:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B1407" t="inlineStr">
+        <is>
+          <t>11:03:54</t>
+        </is>
+      </c>
+      <c r="C1407" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1407" t="n">
+        <v>773.8150000000001</v>
+      </c>
+      <c r="E1407" t="inlineStr">
+        <is>
+          <t>多</t>
+        </is>
+      </c>
+      <c r="F1407" t="n">
+        <v>17.09</v>
+      </c>
+      <c r="G1407" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1407" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I1407" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1407" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="K1407" t="inlineStr">
+        <is>
+          <t>11:02:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B1408" t="inlineStr">
+        <is>
+          <t>11:17:20</t>
+        </is>
+      </c>
+      <c r="C1408" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1408" t="n">
+        <v>773.9657999999999</v>
+      </c>
+      <c r="G1408" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1408" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I1408" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1408" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="K1408" t="inlineStr">
+        <is>
+          <t>11:18:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B1409" t="inlineStr">
+        <is>
+          <t>11:18:12</t>
+        </is>
+      </c>
+      <c r="C1409" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1409" t="n">
+        <v>773.905</v>
+      </c>
+      <c r="E1409" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F1409" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="G1409" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1409" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I1409" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1409" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="K1409" t="inlineStr">
+        <is>
+          <t>11:17:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B1410" t="inlineStr">
+        <is>
+          <t>11:25:30</t>
+        </is>
+      </c>
+      <c r="C1410" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1410" t="n">
+        <v>773.77</v>
+      </c>
+      <c r="G1410" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1410" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I1410" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1410" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="K1410" t="inlineStr">
+        <is>
+          <t>11:26:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B1411" t="inlineStr">
+        <is>
+          <t>11:26:42</t>
+        </is>
+      </c>
+      <c r="C1411" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1411" t="n">
+        <v>773.4450000000001</v>
+      </c>
+      <c r="E1411" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F1411" t="n">
+        <v>30.89</v>
+      </c>
+      <c r="G1411" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1411" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I1411" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1411" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="K1411" t="inlineStr">
+        <is>
+          <t>11:25:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B1412" t="inlineStr">
+        <is>
+          <t>11:41:16</t>
+        </is>
+      </c>
+      <c r="C1412" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1412" t="n">
+        <v>773.46</v>
+      </c>
+      <c r="G1412" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1412" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I1412" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1412" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="K1412" t="inlineStr">
+        <is>
+          <t>11:43:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B1413" t="inlineStr">
+        <is>
+          <t>11:43:01</t>
+        </is>
+      </c>
+      <c r="C1413" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1413" t="n">
+        <v>773.4189</v>
+      </c>
+      <c r="E1413" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F1413" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G1413" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1413" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I1413" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1413" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="K1413" t="inlineStr">
+        <is>
+          <t>11:41:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B1414" t="inlineStr">
+        <is>
+          <t>11:51:38</t>
+        </is>
+      </c>
+      <c r="C1414" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1414" t="n">
+        <v>773.9</v>
+      </c>
+      <c r="G1414" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1414" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I1414" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1414" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="K1414" t="inlineStr">
+        <is>
+          <t>11:52:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B1415" t="inlineStr">
+        <is>
+          <t>11:52:02</t>
+        </is>
+      </c>
+      <c r="C1415" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1415" t="n">
+        <v>774.02</v>
+      </c>
+      <c r="E1415" t="inlineStr">
+        <is>
+          <t>多</t>
+        </is>
+      </c>
+      <c r="F1415" t="n">
+        <v>10.39</v>
+      </c>
+      <c r="G1415" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1415" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I1415" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1415" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="K1415" t="inlineStr">
+        <is>
+          <t>11:51:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B1416" t="inlineStr">
+        <is>
+          <t>11:53:14</t>
+        </is>
+      </c>
+      <c r="C1416" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1416" t="n">
+        <v>774.115</v>
+      </c>
+      <c r="G1416" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1416" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I1416" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1416" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="K1416" t="inlineStr">
+        <is>
+          <t>11:54:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B1417" t="inlineStr">
+        <is>
+          <t>11:54:31</t>
+        </is>
+      </c>
+      <c r="C1417" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1417" t="n">
+        <v>774.2464</v>
+      </c>
+      <c r="E1417" t="inlineStr">
+        <is>
+          <t>多</t>
+        </is>
+      </c>
+      <c r="F1417" t="n">
+        <v>11.53</v>
+      </c>
+      <c r="G1417" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1417" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I1417" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1417" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="K1417" t="inlineStr">
+        <is>
+          <t>11:53:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B1418" t="inlineStr">
+        <is>
+          <t>12:26:14</t>
+        </is>
+      </c>
+      <c r="C1418" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1418" t="n">
+        <v>773.7472</v>
+      </c>
+      <c r="G1418" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1418" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I1418" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1418" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="K1418" t="inlineStr">
+        <is>
+          <t>12:26:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B1419" t="inlineStr">
+        <is>
+          <t>12:26:41</t>
+        </is>
+      </c>
+      <c r="C1419" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1419" t="n">
+        <v>773.689</v>
+      </c>
+      <c r="E1419" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F1419" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="G1419" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1419" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I1419" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1419" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="K1419" t="inlineStr">
+        <is>
+          <t>12:26:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B1420" t="inlineStr">
+        <is>
+          <t>13:12:23</t>
+        </is>
+      </c>
+      <c r="C1420" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1420" t="n">
+        <v>772.9363</v>
+      </c>
+      <c r="G1420" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1420" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I1420" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1420" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="K1420" t="inlineStr">
+        <is>
+          <t>13:13:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B1421" t="inlineStr">
+        <is>
+          <t>13:13:35</t>
+        </is>
+      </c>
+      <c r="C1421" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1421" t="n">
+        <v>773.0299</v>
+      </c>
+      <c r="E1421" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F1421" t="n">
+        <v>-10.97</v>
+      </c>
+      <c r="G1421" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1421" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I1421" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1421" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="K1421" t="inlineStr">
+        <is>
+          <t>13:12:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B1422" t="inlineStr">
+        <is>
+          <t>13:25:29</t>
+        </is>
+      </c>
+      <c r="C1422" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1422" t="n">
+        <v>773.1</v>
+      </c>
+      <c r="G1422" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1422" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I1422" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1422" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="K1422" t="inlineStr">
+        <is>
+          <t>13:27:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B1423" t="inlineStr">
+        <is>
+          <t>13:27:29</t>
+        </is>
+      </c>
+      <c r="C1423" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1423" t="n">
+        <v>773.079</v>
+      </c>
+      <c r="E1423" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F1423" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="G1423" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1423" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I1423" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1423" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="K1423" t="inlineStr">
+        <is>
+          <t>13:25:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B1424" t="inlineStr">
+        <is>
+          <t>13:37:58</t>
+        </is>
+      </c>
+      <c r="C1424" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1424" t="n">
+        <v>772.7795</v>
+      </c>
+      <c r="G1424" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1424" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I1424" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1424" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="K1424" t="inlineStr">
+        <is>
+          <t>13:38:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B1425" t="inlineStr">
+        <is>
+          <t>13:38:43</t>
+        </is>
+      </c>
+      <c r="C1425" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1425" t="n">
+        <v>772.85</v>
+      </c>
+      <c r="E1425" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F1425" t="n">
+        <v>-8.66</v>
+      </c>
+      <c r="G1425" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1425" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I1425" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1425" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="K1425" t="inlineStr">
+        <is>
+          <t>13:37:58</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trades_all.xlsx
+++ b/trades_all.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1425"/>
+  <dimension ref="A1:K1427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68711,6 +68711,100 @@
         </is>
       </c>
     </row>
+    <row r="1426">
+      <c r="A1426" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1426" t="inlineStr">
+        <is>
+          <t>10:33:23</t>
+        </is>
+      </c>
+      <c r="C1426" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1426" t="n">
+        <v>759.16</v>
+      </c>
+      <c r="G1426" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1426" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I1426" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1426" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="K1426" t="inlineStr">
+        <is>
+          <t>10:39:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1427" t="inlineStr">
+        <is>
+          <t>10:39:43</t>
+        </is>
+      </c>
+      <c r="C1427" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1427" t="n">
+        <v>759.415</v>
+      </c>
+      <c r="E1427" t="inlineStr">
+        <is>
+          <t>多</t>
+        </is>
+      </c>
+      <c r="F1427" t="n">
+        <v>23.92</v>
+      </c>
+      <c r="G1427" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1427" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I1427" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1427" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="K1427" t="inlineStr">
+        <is>
+          <t>10:33:23</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trades_all.xlsx
+++ b/trades_all.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1429"/>
+  <dimension ref="A1:K1430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,8 +494,6 @@
           <t>684.07</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>100</t>
@@ -543,8 +541,6 @@
           <t>683.1162</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>100</t>
@@ -592,8 +588,6 @@
           <t>642.13</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>100</t>
@@ -698,8 +692,6 @@
           <t>640.05</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>100</t>
@@ -804,8 +796,6 @@
           <t>638.85</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>100</t>
@@ -910,8 +900,6 @@
           <t>639.2632</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>100</t>
@@ -1016,8 +1004,6 @@
           <t>639.3</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>100</t>
@@ -1122,8 +1108,6 @@
           <t>640.47</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>100</t>
@@ -1228,8 +1212,6 @@
           <t>640.64</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>100</t>
@@ -1334,8 +1316,6 @@
           <t>639.3</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>100</t>
@@ -1440,8 +1420,6 @@
           <t>639.37</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>100</t>
@@ -1546,8 +1524,6 @@
           <t>638.87</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>100</t>
@@ -1652,8 +1628,6 @@
           <t>638.79</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>100</t>
@@ -1758,8 +1732,6 @@
           <t>638.77</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>100</t>
@@ -1864,8 +1836,6 @@
           <t>639.62</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>100</t>
@@ -1970,8 +1940,6 @@
           <t>640.41</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>100</t>
@@ -2076,8 +2044,6 @@
           <t>641.75</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>100</t>
@@ -2182,8 +2148,6 @@
           <t>641.74</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>100</t>
@@ -2288,8 +2252,6 @@
           <t>640.18</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>100</t>
@@ -2394,8 +2356,6 @@
           <t>639.98</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
           <t>100</t>
@@ -2500,8 +2460,6 @@
           <t>639.45</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
           <t>100</t>
@@ -2606,8 +2564,6 @@
           <t>639.2</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
           <t>100</t>
@@ -2712,8 +2668,6 @@
           <t>637.67</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
           <t>100</t>
@@ -2818,8 +2772,6 @@
           <t>635.83</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
           <t>100</t>
@@ -2924,8 +2876,6 @@
           <t>635.9</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
           <t>100</t>
@@ -3030,8 +2980,6 @@
           <t>636</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
           <t>100</t>
@@ -3136,8 +3084,6 @@
           <t>636.35</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
           <t>100</t>
@@ -3242,8 +3188,6 @@
           <t>636.05</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
           <t>100</t>
@@ -3348,8 +3292,6 @@
           <t>635.69</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
           <t>100</t>
@@ -3454,8 +3396,6 @@
           <t>635.26</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
           <t>100</t>
@@ -3560,8 +3500,6 @@
           <t>636.11</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
           <t>100</t>
@@ -3666,8 +3604,6 @@
           <t>635.66</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
           <t>100</t>
@@ -3772,8 +3708,6 @@
           <t>636.93</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
           <t>100</t>
@@ -3878,8 +3812,6 @@
           <t>637</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
           <t>100</t>
@@ -3984,8 +3916,6 @@
           <t>637.97</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
           <t>100</t>
@@ -4090,8 +4020,6 @@
           <t>637.61</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
           <t>100</t>
@@ -4196,8 +4124,6 @@
           <t>637.86</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
           <t>100</t>
@@ -4302,8 +4228,6 @@
           <t>638.02</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
           <t>100</t>
@@ -4408,8 +4332,6 @@
           <t>637.75</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
           <t>100</t>
@@ -4514,8 +4436,6 @@
           <t>638.22</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
           <t>100</t>
@@ -4620,8 +4540,6 @@
           <t>636.48</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
           <t>100</t>
@@ -4726,8 +4644,6 @@
           <t>636.74</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
           <t>100</t>
@@ -4832,8 +4748,6 @@
           <t>633.51</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
           <t>100</t>
@@ -4938,8 +4852,6 @@
           <t>639.66</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
           <t>100</t>
@@ -5044,8 +4956,6 @@
           <t>638.82</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
           <t>100</t>
@@ -5150,8 +5060,6 @@
           <t>642.42</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
           <t>100</t>
@@ -5256,8 +5164,6 @@
           <t>641.57</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
           <t>100</t>
@@ -5362,8 +5268,6 @@
           <t>641.67</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
           <t>100</t>
@@ -5468,8 +5372,6 @@
           <t>642.04</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
           <t>100</t>
@@ -5574,8 +5476,6 @@
           <t>642.17</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
           <t>100</t>
@@ -5680,8 +5580,6 @@
           <t>640.33</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
           <t>100</t>
@@ -5786,8 +5684,6 @@
           <t>639.91</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
           <t>100</t>
@@ -5892,8 +5788,6 @@
           <t>639.29</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
           <t>100</t>
@@ -5998,8 +5892,6 @@
           <t>638.39</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
           <t>100</t>
@@ -6104,8 +5996,6 @@
           <t>638.68</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
           <t>100</t>
@@ -6210,8 +6100,6 @@
           <t>640.74</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
           <t>100</t>
@@ -6316,8 +6204,6 @@
           <t>641.67</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
           <t>100</t>
@@ -6422,8 +6308,6 @@
           <t>640.78</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
           <t>100</t>
@@ -6528,8 +6412,6 @@
           <t>640.79</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
           <t>100</t>
@@ -6634,8 +6516,6 @@
           <t>640.1</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
           <t>100</t>
@@ -6740,8 +6620,6 @@
           <t>640.97</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
           <t>100</t>
@@ -6846,8 +6724,6 @@
           <t>640.82</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
           <t>100</t>
@@ -6952,8 +6828,6 @@
           <t>640.28</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
           <t>100</t>
@@ -7058,8 +6932,6 @@
           <t>640.89</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
           <t>100</t>
@@ -7164,8 +7036,6 @@
           <t>646.96</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
           <t>100</t>
@@ -7270,8 +7140,6 @@
           <t>654.25</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
           <t>100</t>
@@ -7376,8 +7244,6 @@
           <t>654.25</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
           <t>100</t>
@@ -7482,8 +7348,6 @@
           <t>656.55</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
           <t>100</t>
@@ -7588,8 +7452,6 @@
           <t>656.89</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
           <t>100</t>
@@ -7694,8 +7556,6 @@
           <t>657.61</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
           <t>100</t>
@@ -7800,8 +7660,6 @@
           <t>657.61</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
           <t>100</t>
@@ -7906,8 +7764,6 @@
           <t>646.7</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
           <t>100</t>
@@ -7955,8 +7811,6 @@
           <t>646.44</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr"/>
-      <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
           <t>100</t>
@@ -8118,8 +7972,6 @@
           <t>646.39</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr">
         <is>
           <t>100</t>
@@ -8224,8 +8076,6 @@
           <t>645.95</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr">
         <is>
           <t>100</t>
@@ -8330,8 +8180,6 @@
           <t>647.01</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr">
         <is>
           <t>100</t>
@@ -8436,8 +8284,6 @@
           <t>654.59</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr">
         <is>
           <t>100</t>
@@ -8542,8 +8388,6 @@
           <t>655.31</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr"/>
-      <c r="F154" t="inlineStr"/>
       <c r="G154" t="inlineStr">
         <is>
           <t>100</t>
@@ -8648,8 +8492,6 @@
           <t>653.93</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr"/>
-      <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr">
         <is>
           <t>100</t>
@@ -8754,8 +8596,6 @@
           <t>654.95</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr"/>
-      <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr">
         <is>
           <t>100</t>
@@ -8860,8 +8700,6 @@
           <t>654.79</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr"/>
-      <c r="F160" t="inlineStr"/>
       <c r="G160" t="inlineStr">
         <is>
           <t>100</t>
@@ -8966,8 +8804,6 @@
           <t>655.45</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr"/>
-      <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr">
         <is>
           <t>100</t>
@@ -9072,8 +8908,6 @@
           <t>655.05</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr"/>
-      <c r="F164" t="inlineStr"/>
       <c r="G164" t="inlineStr">
         <is>
           <t>100</t>
@@ -9178,8 +9012,6 @@
           <t>654.41</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr"/>
-      <c r="F166" t="inlineStr"/>
       <c r="G166" t="inlineStr">
         <is>
           <t>100</t>
@@ -9227,8 +9059,6 @@
           <t>655.6</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr"/>
-      <c r="F167" t="inlineStr"/>
       <c r="G167" t="inlineStr">
         <is>
           <t>100</t>
@@ -9390,8 +9220,6 @@
           <t>653.79</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr"/>
-      <c r="F170" t="inlineStr"/>
       <c r="G170" t="inlineStr">
         <is>
           <t>100</t>
@@ -9496,8 +9324,6 @@
           <t>653.4428</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr"/>
-      <c r="F172" t="inlineStr"/>
       <c r="G172" t="inlineStr">
         <is>
           <t>100</t>
@@ -9602,8 +9428,6 @@
           <t>653.37</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr"/>
-      <c r="F174" t="inlineStr"/>
       <c r="G174" t="inlineStr">
         <is>
           <t>100</t>
@@ -9708,8 +9532,6 @@
           <t>652.79</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr"/>
       <c r="G176" t="inlineStr">
         <is>
           <t>100</t>
@@ -9814,8 +9636,6 @@
           <t>652.51</t>
         </is>
       </c>
-      <c r="E178" t="inlineStr"/>
-      <c r="F178" t="inlineStr"/>
       <c r="G178" t="inlineStr">
         <is>
           <t>100</t>
@@ -9863,8 +9683,6 @@
           <t>652.82</t>
         </is>
       </c>
-      <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr"/>
       <c r="G179" t="inlineStr">
         <is>
           <t>100</t>
@@ -10026,8 +9844,6 @@
           <t>652.7</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr"/>
       <c r="G182" t="inlineStr">
         <is>
           <t>100</t>
@@ -10132,8 +9948,6 @@
           <t>652.83</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr"/>
-      <c r="F184" t="inlineStr"/>
       <c r="G184" t="inlineStr">
         <is>
           <t>100</t>
@@ -10238,8 +10052,6 @@
           <t>656.61</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr"/>
-      <c r="F186" t="inlineStr"/>
       <c r="G186" t="inlineStr">
         <is>
           <t>100</t>
@@ -10344,8 +10156,6 @@
           <t>657.25</t>
         </is>
       </c>
-      <c r="E188" t="inlineStr"/>
-      <c r="F188" t="inlineStr"/>
       <c r="G188" t="inlineStr">
         <is>
           <t>100</t>
@@ -10450,8 +10260,6 @@
           <t>657.62</t>
         </is>
       </c>
-      <c r="E190" t="inlineStr"/>
-      <c r="F190" t="inlineStr"/>
       <c r="G190" t="inlineStr">
         <is>
           <t>100</t>
@@ -10556,8 +10364,6 @@
           <t>657.84</t>
         </is>
       </c>
-      <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr"/>
       <c r="G192" t="inlineStr">
         <is>
           <t>100</t>
@@ -10662,8 +10468,6 @@
           <t>656.79</t>
         </is>
       </c>
-      <c r="E194" t="inlineStr"/>
-      <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr">
         <is>
           <t>100</t>
@@ -10768,8 +10572,6 @@
           <t>657.55</t>
         </is>
       </c>
-      <c r="E196" t="inlineStr"/>
-      <c r="F196" t="inlineStr"/>
       <c r="G196" t="inlineStr">
         <is>
           <t>100</t>
@@ -10874,8 +10676,6 @@
           <t>658.1699</t>
         </is>
       </c>
-      <c r="E198" t="inlineStr"/>
-      <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr">
         <is>
           <t>100</t>
@@ -10980,8 +10780,6 @@
           <t>658.65</t>
         </is>
       </c>
-      <c r="E200" t="inlineStr"/>
-      <c r="F200" t="inlineStr"/>
       <c r="G200" t="inlineStr">
         <is>
           <t>100</t>
@@ -11086,8 +10884,6 @@
           <t>658.39</t>
         </is>
       </c>
-      <c r="E202" t="inlineStr"/>
-      <c r="F202" t="inlineStr"/>
       <c r="G202" t="inlineStr">
         <is>
           <t>100</t>
@@ -11192,8 +10988,6 @@
           <t>657.26</t>
         </is>
       </c>
-      <c r="E204" t="inlineStr"/>
-      <c r="F204" t="inlineStr"/>
       <c r="G204" t="inlineStr">
         <is>
           <t>100</t>
@@ -11298,8 +11092,6 @@
           <t>656.07</t>
         </is>
       </c>
-      <c r="E206" t="inlineStr"/>
-      <c r="F206" t="inlineStr"/>
       <c r="G206" t="inlineStr">
         <is>
           <t>100</t>
@@ -11404,8 +11196,6 @@
           <t>653.95</t>
         </is>
       </c>
-      <c r="E208" t="inlineStr"/>
-      <c r="F208" t="inlineStr"/>
       <c r="G208" t="inlineStr">
         <is>
           <t>100</t>
@@ -11510,8 +11300,6 @@
           <t>656.34</t>
         </is>
       </c>
-      <c r="E210" t="inlineStr"/>
-      <c r="F210" t="inlineStr"/>
       <c r="G210" t="inlineStr">
         <is>
           <t>100</t>
@@ -11616,8 +11404,6 @@
           <t>675.74</t>
         </is>
       </c>
-      <c r="E212" t="inlineStr"/>
-      <c r="F212" t="inlineStr"/>
       <c r="G212" t="inlineStr">
         <is>
           <t>100</t>
@@ -11722,8 +11508,6 @@
           <t>674.25</t>
         </is>
       </c>
-      <c r="E214" t="inlineStr"/>
-      <c r="F214" t="inlineStr"/>
       <c r="G214" t="inlineStr">
         <is>
           <t>100</t>
@@ -11828,8 +11612,6 @@
           <t>674.91</t>
         </is>
       </c>
-      <c r="E216" t="inlineStr"/>
-      <c r="F216" t="inlineStr"/>
       <c r="G216" t="inlineStr">
         <is>
           <t>100</t>
@@ -11934,8 +11716,6 @@
           <t>675.42</t>
         </is>
       </c>
-      <c r="E218" t="inlineStr"/>
-      <c r="F218" t="inlineStr"/>
       <c r="G218" t="inlineStr">
         <is>
           <t>100</t>
@@ -12040,8 +11820,6 @@
           <t>675.23</t>
         </is>
       </c>
-      <c r="E220" t="inlineStr"/>
-      <c r="F220" t="inlineStr"/>
       <c r="G220" t="inlineStr">
         <is>
           <t>100</t>
@@ -12146,8 +11924,6 @@
           <t>675.29</t>
         </is>
       </c>
-      <c r="E222" t="inlineStr"/>
-      <c r="F222" t="inlineStr"/>
       <c r="G222" t="inlineStr">
         <is>
           <t>100</t>
@@ -12252,8 +12028,6 @@
           <t>674.96</t>
         </is>
       </c>
-      <c r="E224" t="inlineStr"/>
-      <c r="F224" t="inlineStr"/>
       <c r="G224" t="inlineStr">
         <is>
           <t>100</t>
@@ -12358,8 +12132,6 @@
           <t>675.24</t>
         </is>
       </c>
-      <c r="E226" t="inlineStr"/>
-      <c r="F226" t="inlineStr"/>
       <c r="G226" t="inlineStr">
         <is>
           <t>100</t>
@@ -12464,8 +12236,6 @@
           <t>675.35</t>
         </is>
       </c>
-      <c r="E228" t="inlineStr"/>
-      <c r="F228" t="inlineStr"/>
       <c r="G228" t="inlineStr">
         <is>
           <t>100</t>
@@ -12570,8 +12340,6 @@
           <t>675.32</t>
         </is>
       </c>
-      <c r="E230" t="inlineStr"/>
-      <c r="F230" t="inlineStr"/>
       <c r="G230" t="inlineStr">
         <is>
           <t>100</t>
@@ -12676,8 +12444,6 @@
           <t>675.64</t>
         </is>
       </c>
-      <c r="E232" t="inlineStr"/>
-      <c r="F232" t="inlineStr"/>
       <c r="G232" t="inlineStr">
         <is>
           <t>100</t>
@@ -12782,8 +12548,6 @@
           <t>675.6</t>
         </is>
       </c>
-      <c r="E234" t="inlineStr"/>
-      <c r="F234" t="inlineStr"/>
       <c r="G234" t="inlineStr">
         <is>
           <t>100</t>
@@ -12888,8 +12652,6 @@
           <t>675.33</t>
         </is>
       </c>
-      <c r="E236" t="inlineStr"/>
-      <c r="F236" t="inlineStr"/>
       <c r="G236" t="inlineStr">
         <is>
           <t>100</t>
@@ -12994,8 +12756,6 @@
           <t>674.96</t>
         </is>
       </c>
-      <c r="E238" t="inlineStr"/>
-      <c r="F238" t="inlineStr"/>
       <c r="G238" t="inlineStr">
         <is>
           <t>100</t>
@@ -13100,8 +12860,6 @@
           <t>674.52</t>
         </is>
       </c>
-      <c r="E240" t="inlineStr"/>
-      <c r="F240" t="inlineStr"/>
       <c r="G240" t="inlineStr">
         <is>
           <t>100</t>
@@ -13206,8 +12964,6 @@
           <t>674.4</t>
         </is>
       </c>
-      <c r="E242" t="inlineStr"/>
-      <c r="F242" t="inlineStr"/>
       <c r="G242" t="inlineStr">
         <is>
           <t>100</t>
@@ -13312,8 +13068,6 @@
           <t>674.93</t>
         </is>
       </c>
-      <c r="E244" t="inlineStr"/>
-      <c r="F244" t="inlineStr"/>
       <c r="G244" t="inlineStr">
         <is>
           <t>100</t>
@@ -13418,8 +13172,6 @@
           <t>675.03</t>
         </is>
       </c>
-      <c r="E246" t="inlineStr"/>
-      <c r="F246" t="inlineStr"/>
       <c r="G246" t="inlineStr">
         <is>
           <t>100</t>
@@ -13524,8 +13276,6 @@
           <t>675.25</t>
         </is>
       </c>
-      <c r="E248" t="inlineStr"/>
-      <c r="F248" t="inlineStr"/>
       <c r="G248" t="inlineStr">
         <is>
           <t>100</t>
@@ -13630,8 +13380,6 @@
           <t>674.93</t>
         </is>
       </c>
-      <c r="E250" t="inlineStr"/>
-      <c r="F250" t="inlineStr"/>
       <c r="G250" t="inlineStr">
         <is>
           <t>100</t>
@@ -13736,8 +13484,6 @@
           <t>675.07</t>
         </is>
       </c>
-      <c r="E252" t="inlineStr"/>
-      <c r="F252" t="inlineStr"/>
       <c r="G252" t="inlineStr">
         <is>
           <t>100</t>
@@ -13842,8 +13588,6 @@
           <t>675.13</t>
         </is>
       </c>
-      <c r="E254" t="inlineStr"/>
-      <c r="F254" t="inlineStr"/>
       <c r="G254" t="inlineStr">
         <is>
           <t>100</t>
@@ -13948,8 +13692,6 @@
           <t>675.49</t>
         </is>
       </c>
-      <c r="E256" t="inlineStr"/>
-      <c r="F256" t="inlineStr"/>
       <c r="G256" t="inlineStr">
         <is>
           <t>100</t>
@@ -14054,8 +13796,6 @@
           <t>675.95</t>
         </is>
       </c>
-      <c r="E258" t="inlineStr"/>
-      <c r="F258" t="inlineStr"/>
       <c r="G258" t="inlineStr">
         <is>
           <t>100</t>
@@ -14160,8 +13900,6 @@
           <t>676.32</t>
         </is>
       </c>
-      <c r="E260" t="inlineStr"/>
-      <c r="F260" t="inlineStr"/>
       <c r="G260" t="inlineStr">
         <is>
           <t>100</t>
@@ -14266,8 +14004,6 @@
           <t>677.46</t>
         </is>
       </c>
-      <c r="E262" t="inlineStr"/>
-      <c r="F262" t="inlineStr"/>
       <c r="G262" t="inlineStr">
         <is>
           <t>100</t>
@@ -14372,8 +14108,6 @@
           <t>680.8588</t>
         </is>
       </c>
-      <c r="E264" t="inlineStr"/>
-      <c r="F264" t="inlineStr"/>
       <c r="G264" t="inlineStr">
         <is>
           <t>100</t>
@@ -14478,8 +14212,6 @@
           <t>680.77</t>
         </is>
       </c>
-      <c r="E266" t="inlineStr"/>
-      <c r="F266" t="inlineStr"/>
       <c r="G266" t="inlineStr">
         <is>
           <t>100</t>
@@ -14584,8 +14316,6 @@
           <t>681.38</t>
         </is>
       </c>
-      <c r="E268" t="inlineStr"/>
-      <c r="F268" t="inlineStr"/>
       <c r="G268" t="inlineStr">
         <is>
           <t>100</t>
@@ -14690,8 +14420,6 @@
           <t>681.2</t>
         </is>
       </c>
-      <c r="E270" t="inlineStr"/>
-      <c r="F270" t="inlineStr"/>
       <c r="G270" t="inlineStr">
         <is>
           <t>100</t>
@@ -14796,8 +14524,6 @@
           <t>681.46</t>
         </is>
       </c>
-      <c r="E272" t="inlineStr"/>
-      <c r="F272" t="inlineStr"/>
       <c r="G272" t="inlineStr">
         <is>
           <t>100</t>
@@ -14902,8 +14628,6 @@
           <t>681.34</t>
         </is>
       </c>
-      <c r="E274" t="inlineStr"/>
-      <c r="F274" t="inlineStr"/>
       <c r="G274" t="inlineStr">
         <is>
           <t>100</t>
@@ -15008,8 +14732,6 @@
           <t>680.68</t>
         </is>
       </c>
-      <c r="E276" t="inlineStr"/>
-      <c r="F276" t="inlineStr"/>
       <c r="G276" t="inlineStr">
         <is>
           <t>100</t>
@@ -15057,8 +14779,6 @@
           <t>679.21</t>
         </is>
       </c>
-      <c r="E277" t="inlineStr"/>
-      <c r="F277" t="inlineStr"/>
       <c r="G277" t="inlineStr">
         <is>
           <t>100</t>
@@ -15163,8 +14883,6 @@
           <t>679.04</t>
         </is>
       </c>
-      <c r="E279" t="inlineStr"/>
-      <c r="F279" t="inlineStr"/>
       <c r="G279" t="inlineStr">
         <is>
           <t>100</t>
@@ -15269,8 +14987,6 @@
           <t>679.38</t>
         </is>
       </c>
-      <c r="E281" t="inlineStr"/>
-      <c r="F281" t="inlineStr"/>
       <c r="G281" t="inlineStr">
         <is>
           <t>100</t>
@@ -15432,8 +15148,6 @@
           <t>679.32</t>
         </is>
       </c>
-      <c r="E284" t="inlineStr"/>
-      <c r="F284" t="inlineStr"/>
       <c r="G284" t="inlineStr">
         <is>
           <t>100</t>
@@ -15538,8 +15252,6 @@
           <t>678.93</t>
         </is>
       </c>
-      <c r="E286" t="inlineStr"/>
-      <c r="F286" t="inlineStr"/>
       <c r="G286" t="inlineStr">
         <is>
           <t>100</t>
@@ -15644,8 +15356,6 @@
           <t>679.95</t>
         </is>
       </c>
-      <c r="E288" t="inlineStr"/>
-      <c r="F288" t="inlineStr"/>
       <c r="G288" t="inlineStr">
         <is>
           <t>100</t>
@@ -15750,8 +15460,6 @@
           <t>679.42</t>
         </is>
       </c>
-      <c r="E290" t="inlineStr"/>
-      <c r="F290" t="inlineStr"/>
       <c r="G290" t="inlineStr">
         <is>
           <t>100</t>
@@ -15856,8 +15564,6 @@
           <t>679.6</t>
         </is>
       </c>
-      <c r="E292" t="inlineStr"/>
-      <c r="F292" t="inlineStr"/>
       <c r="G292" t="inlineStr">
         <is>
           <t>100</t>
@@ -15962,8 +15668,6 @@
           <t>680.4</t>
         </is>
       </c>
-      <c r="E294" t="inlineStr"/>
-      <c r="F294" t="inlineStr"/>
       <c r="G294" t="inlineStr">
         <is>
           <t>100</t>
@@ -16068,8 +15772,6 @@
           <t>679.96</t>
         </is>
       </c>
-      <c r="E296" t="inlineStr"/>
-      <c r="F296" t="inlineStr"/>
       <c r="G296" t="inlineStr">
         <is>
           <t>100</t>
@@ -16174,8 +15876,6 @@
           <t>679.97</t>
         </is>
       </c>
-      <c r="E298" t="inlineStr"/>
-      <c r="F298" t="inlineStr"/>
       <c r="G298" t="inlineStr">
         <is>
           <t>100</t>
@@ -16280,8 +15980,6 @@
           <t>679.62</t>
         </is>
       </c>
-      <c r="E300" t="inlineStr"/>
-      <c r="F300" t="inlineStr"/>
       <c r="G300" t="inlineStr">
         <is>
           <t>100</t>
@@ -16386,8 +16084,6 @@
           <t>679.99</t>
         </is>
       </c>
-      <c r="E302" t="inlineStr"/>
-      <c r="F302" t="inlineStr"/>
       <c r="G302" t="inlineStr">
         <is>
           <t>100</t>
@@ -16492,8 +16188,6 @@
           <t>679.52</t>
         </is>
       </c>
-      <c r="E304" t="inlineStr"/>
-      <c r="F304" t="inlineStr"/>
       <c r="G304" t="inlineStr">
         <is>
           <t>100</t>
@@ -16598,8 +16292,6 @@
           <t>679.53</t>
         </is>
       </c>
-      <c r="E306" t="inlineStr"/>
-      <c r="F306" t="inlineStr"/>
       <c r="G306" t="inlineStr">
         <is>
           <t>100</t>
@@ -16704,8 +16396,6 @@
           <t>679.41</t>
         </is>
       </c>
-      <c r="E308" t="inlineStr"/>
-      <c r="F308" t="inlineStr"/>
       <c r="G308" t="inlineStr">
         <is>
           <t>100</t>
@@ -16810,8 +16500,6 @@
           <t>679.46</t>
         </is>
       </c>
-      <c r="E310" t="inlineStr"/>
-      <c r="F310" t="inlineStr"/>
       <c r="G310" t="inlineStr">
         <is>
           <t>100</t>
@@ -16916,8 +16604,6 @@
           <t>679.64</t>
         </is>
       </c>
-      <c r="E312" t="inlineStr"/>
-      <c r="F312" t="inlineStr"/>
       <c r="G312" t="inlineStr">
         <is>
           <t>100</t>
@@ -17022,8 +16708,6 @@
           <t>679.61</t>
         </is>
       </c>
-      <c r="E314" t="inlineStr"/>
-      <c r="F314" t="inlineStr"/>
       <c r="G314" t="inlineStr">
         <is>
           <t>100</t>
@@ -17128,8 +16812,6 @@
           <t>679.09</t>
         </is>
       </c>
-      <c r="E316" t="inlineStr"/>
-      <c r="F316" t="inlineStr"/>
       <c r="G316" t="inlineStr">
         <is>
           <t>100</t>
@@ -17234,8 +16916,6 @@
           <t>679.21</t>
         </is>
       </c>
-      <c r="E318" t="inlineStr"/>
-      <c r="F318" t="inlineStr"/>
       <c r="G318" t="inlineStr">
         <is>
           <t>100</t>
@@ -17340,8 +17020,6 @@
           <t>679.87</t>
         </is>
       </c>
-      <c r="E320" t="inlineStr"/>
-      <c r="F320" t="inlineStr"/>
       <c r="G320" t="inlineStr">
         <is>
           <t>100</t>
@@ -17446,8 +17124,6 @@
           <t>682.32</t>
         </is>
       </c>
-      <c r="E322" t="inlineStr"/>
-      <c r="F322" t="inlineStr"/>
       <c r="G322" t="inlineStr">
         <is>
           <t>100</t>
@@ -17552,8 +17228,6 @@
           <t>682.41</t>
         </is>
       </c>
-      <c r="E324" t="inlineStr"/>
-      <c r="F324" t="inlineStr"/>
       <c r="G324" t="inlineStr">
         <is>
           <t>100</t>
@@ -17658,8 +17332,6 @@
           <t>689.71</t>
         </is>
       </c>
-      <c r="E326" t="inlineStr"/>
-      <c r="F326" t="inlineStr"/>
       <c r="G326" t="inlineStr">
         <is>
           <t>100</t>
@@ -17764,8 +17436,6 @@
           <t>689.62</t>
         </is>
       </c>
-      <c r="E328" t="inlineStr"/>
-      <c r="F328" t="inlineStr"/>
       <c r="G328" t="inlineStr">
         <is>
           <t>100</t>
@@ -17870,8 +17540,6 @@
           <t>690.74</t>
         </is>
       </c>
-      <c r="E330" t="inlineStr"/>
-      <c r="F330" t="inlineStr"/>
       <c r="G330" t="inlineStr">
         <is>
           <t>100</t>
@@ -17976,8 +17644,6 @@
           <t>691.28</t>
         </is>
       </c>
-      <c r="E332" t="inlineStr"/>
-      <c r="F332" t="inlineStr"/>
       <c r="G332" t="inlineStr">
         <is>
           <t>100</t>
@@ -18082,8 +17748,6 @@
           <t>691.45</t>
         </is>
       </c>
-      <c r="E334" t="inlineStr"/>
-      <c r="F334" t="inlineStr"/>
       <c r="G334" t="inlineStr">
         <is>
           <t>100</t>
@@ -18188,8 +17852,6 @@
           <t>691.95</t>
         </is>
       </c>
-      <c r="E336" t="inlineStr"/>
-      <c r="F336" t="inlineStr"/>
       <c r="G336" t="inlineStr">
         <is>
           <t>100</t>
@@ -18294,8 +17956,6 @@
           <t>692.52</t>
         </is>
       </c>
-      <c r="E338" t="inlineStr"/>
-      <c r="F338" t="inlineStr"/>
       <c r="G338" t="inlineStr">
         <is>
           <t>100</t>
@@ -18514,8 +18174,6 @@
           <t>695.14</t>
         </is>
       </c>
-      <c r="E342" t="inlineStr"/>
-      <c r="F342" t="inlineStr"/>
       <c r="G342" t="inlineStr">
         <is>
           <t>100</t>
@@ -18620,8 +18278,6 @@
           <t>695.405</t>
         </is>
       </c>
-      <c r="E344" t="inlineStr"/>
-      <c r="F344" t="inlineStr"/>
       <c r="G344" t="inlineStr">
         <is>
           <t>100</t>
@@ -18726,8 +18382,6 @@
           <t>696.875</t>
         </is>
       </c>
-      <c r="E346" t="inlineStr"/>
-      <c r="F346" t="inlineStr"/>
       <c r="G346" t="inlineStr">
         <is>
           <t>100</t>
@@ -18832,8 +18486,6 @@
           <t>696.9199</t>
         </is>
       </c>
-      <c r="E348" t="inlineStr"/>
-      <c r="F348" t="inlineStr"/>
       <c r="G348" t="inlineStr">
         <is>
           <t>100</t>
@@ -18938,8 +18590,6 @@
           <t>697.3</t>
         </is>
       </c>
-      <c r="E350" t="inlineStr"/>
-      <c r="F350" t="inlineStr"/>
       <c r="G350" t="inlineStr">
         <is>
           <t>100</t>
@@ -19044,8 +18694,6 @@
           <t>697.1599</t>
         </is>
       </c>
-      <c r="E352" t="inlineStr"/>
-      <c r="F352" t="inlineStr"/>
       <c r="G352" t="inlineStr">
         <is>
           <t>100</t>
@@ -19150,8 +18798,6 @@
           <t>696.6536</t>
         </is>
       </c>
-      <c r="E354" t="inlineStr"/>
-      <c r="F354" t="inlineStr"/>
       <c r="G354" t="inlineStr">
         <is>
           <t>100</t>
@@ -19256,8 +18902,6 @@
           <t>700.94</t>
         </is>
       </c>
-      <c r="E356" t="inlineStr"/>
-      <c r="F356" t="inlineStr"/>
       <c r="G356" t="inlineStr">
         <is>
           <t>100</t>
@@ -19362,8 +19006,6 @@
           <t>700.22</t>
         </is>
       </c>
-      <c r="E358" t="inlineStr"/>
-      <c r="F358" t="inlineStr"/>
       <c r="G358" t="inlineStr">
         <is>
           <t>100</t>
@@ -19468,8 +19110,6 @@
           <t>700.4173</t>
         </is>
       </c>
-      <c r="E360" t="inlineStr"/>
-      <c r="F360" t="inlineStr"/>
       <c r="G360" t="inlineStr">
         <is>
           <t>100</t>
@@ -19574,8 +19214,6 @@
           <t>699.8135</t>
         </is>
       </c>
-      <c r="E362" t="inlineStr"/>
-      <c r="F362" t="inlineStr"/>
       <c r="G362" t="inlineStr">
         <is>
           <t>100</t>
@@ -19680,8 +19318,6 @@
           <t>699.81</t>
         </is>
       </c>
-      <c r="E364" t="inlineStr"/>
-      <c r="F364" t="inlineStr"/>
       <c r="G364" t="inlineStr">
         <is>
           <t>100</t>
@@ -19786,8 +19422,6 @@
           <t>699.1299</t>
         </is>
       </c>
-      <c r="E366" t="inlineStr"/>
-      <c r="F366" t="inlineStr"/>
       <c r="G366" t="inlineStr">
         <is>
           <t>100</t>
@@ -19892,8 +19526,6 @@
           <t>699.28</t>
         </is>
       </c>
-      <c r="E368" t="inlineStr"/>
-      <c r="F368" t="inlineStr"/>
       <c r="G368" t="inlineStr">
         <is>
           <t>100</t>
@@ -19998,8 +19630,6 @@
           <t>699.89</t>
         </is>
       </c>
-      <c r="E370" t="inlineStr"/>
-      <c r="F370" t="inlineStr"/>
       <c r="G370" t="inlineStr">
         <is>
           <t>100</t>
@@ -20104,8 +19734,6 @@
           <t>700.1867</t>
         </is>
       </c>
-      <c r="E372" t="inlineStr"/>
-      <c r="F372" t="inlineStr"/>
       <c r="G372" t="inlineStr">
         <is>
           <t>100</t>
@@ -20210,8 +19838,6 @@
           <t>700.485</t>
         </is>
       </c>
-      <c r="E374" t="inlineStr"/>
-      <c r="F374" t="inlineStr"/>
       <c r="G374" t="inlineStr">
         <is>
           <t>100</t>
@@ -20316,8 +19942,6 @@
           <t>700.64</t>
         </is>
       </c>
-      <c r="E376" t="inlineStr"/>
-      <c r="F376" t="inlineStr"/>
       <c r="G376" t="inlineStr">
         <is>
           <t>100</t>
@@ -20422,8 +20046,6 @@
           <t>701.94</t>
         </is>
       </c>
-      <c r="E378" t="inlineStr"/>
-      <c r="F378" t="inlineStr"/>
       <c r="G378" t="inlineStr">
         <is>
           <t>100</t>
@@ -20528,8 +20150,6 @@
           <t>700.95</t>
         </is>
       </c>
-      <c r="E380" t="inlineStr"/>
-      <c r="F380" t="inlineStr"/>
       <c r="G380" t="inlineStr">
         <is>
           <t>100</t>
@@ -20634,8 +20254,6 @@
           <t>701.1861</t>
         </is>
       </c>
-      <c r="E382" t="inlineStr"/>
-      <c r="F382" t="inlineStr"/>
       <c r="G382" t="inlineStr">
         <is>
           <t>100</t>
@@ -20740,8 +20358,6 @@
           <t>701.22</t>
         </is>
       </c>
-      <c r="E384" t="inlineStr"/>
-      <c r="F384" t="inlineStr"/>
       <c r="G384" t="inlineStr">
         <is>
           <t>100</t>
@@ -20846,8 +20462,6 @@
           <t>707.475</t>
         </is>
       </c>
-      <c r="E386" t="inlineStr"/>
-      <c r="F386" t="inlineStr"/>
       <c r="G386" t="inlineStr">
         <is>
           <t>100</t>
@@ -20952,8 +20566,6 @@
           <t>710.86</t>
         </is>
       </c>
-      <c r="E388" t="inlineStr"/>
-      <c r="F388" t="inlineStr"/>
       <c r="G388" t="inlineStr">
         <is>
           <t>100</t>
@@ -21058,8 +20670,6 @@
           <t>711.115</t>
         </is>
       </c>
-      <c r="E390" t="inlineStr"/>
-      <c r="F390" t="inlineStr"/>
       <c r="G390" t="inlineStr">
         <is>
           <t>100</t>
@@ -21107,8 +20717,6 @@
           <t>710.59</t>
         </is>
       </c>
-      <c r="E391" t="inlineStr"/>
-      <c r="F391" t="inlineStr"/>
       <c r="G391" t="inlineStr">
         <is>
           <t>100</t>
@@ -21270,8 +20878,6 @@
           <t>710.6</t>
         </is>
       </c>
-      <c r="E394" t="inlineStr"/>
-      <c r="F394" t="inlineStr"/>
       <c r="G394" t="inlineStr">
         <is>
           <t>100</t>
@@ -21319,8 +20925,6 @@
           <t>710.36</t>
         </is>
       </c>
-      <c r="E395" t="inlineStr"/>
-      <c r="F395" t="inlineStr"/>
       <c r="G395" t="inlineStr">
         <is>
           <t>100</t>
@@ -21482,8 +21086,6 @@
           <t>707.5342</t>
         </is>
       </c>
-      <c r="E398" t="inlineStr"/>
-      <c r="F398" t="inlineStr"/>
       <c r="G398" t="inlineStr">
         <is>
           <t>100</t>
@@ -21588,8 +21190,6 @@
           <t>707.05</t>
         </is>
       </c>
-      <c r="E400" t="inlineStr"/>
-      <c r="F400" t="inlineStr"/>
       <c r="G400" t="inlineStr">
         <is>
           <t>100</t>
@@ -21694,8 +21294,6 @@
           <t>705.6</t>
         </is>
       </c>
-      <c r="E402" t="inlineStr"/>
-      <c r="F402" t="inlineStr"/>
       <c r="G402" t="inlineStr">
         <is>
           <t>100</t>
@@ -21800,8 +21398,6 @@
           <t>706.0572</t>
         </is>
       </c>
-      <c r="E404" t="inlineStr"/>
-      <c r="F404" t="inlineStr"/>
       <c r="G404" t="inlineStr">
         <is>
           <t>100</t>
@@ -21906,8 +21502,6 @@
           <t>709.073</t>
         </is>
       </c>
-      <c r="E406" t="inlineStr"/>
-      <c r="F406" t="inlineStr"/>
       <c r="G406" t="inlineStr">
         <is>
           <t>100</t>
@@ -22012,8 +21606,6 @@
           <t>710.4659</t>
         </is>
       </c>
-      <c r="E408" t="inlineStr"/>
-      <c r="F408" t="inlineStr"/>
       <c r="G408" t="inlineStr">
         <is>
           <t>100</t>
@@ -22118,8 +21710,6 @@
           <t>709.74</t>
         </is>
       </c>
-      <c r="E410" t="inlineStr"/>
-      <c r="F410" t="inlineStr"/>
       <c r="G410" t="inlineStr">
         <is>
           <t>100</t>
@@ -22224,8 +21814,6 @@
           <t>709.8199</t>
         </is>
       </c>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
       <c r="G412" t="inlineStr">
         <is>
           <t>100</t>
@@ -22330,8 +21918,6 @@
           <t>710.595</t>
         </is>
       </c>
-      <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr"/>
       <c r="G414" t="inlineStr">
         <is>
           <t>100</t>
@@ -22436,8 +22022,6 @@
           <t>710.78</t>
         </is>
       </c>
-      <c r="E416" t="inlineStr"/>
-      <c r="F416" t="inlineStr"/>
       <c r="G416" t="inlineStr">
         <is>
           <t>100</t>
@@ -22542,8 +22126,6 @@
           <t>710.605</t>
         </is>
       </c>
-      <c r="E418" t="inlineStr"/>
-      <c r="F418" t="inlineStr"/>
       <c r="G418" t="inlineStr">
         <is>
           <t>100</t>
@@ -22648,8 +22230,6 @@
           <t>711.7299</t>
         </is>
       </c>
-      <c r="E420" t="inlineStr"/>
-      <c r="F420" t="inlineStr"/>
       <c r="G420" t="inlineStr">
         <is>
           <t>100</t>
@@ -22754,8 +22334,6 @@
           <t>712.0599</t>
         </is>
       </c>
-      <c r="E422" t="inlineStr"/>
-      <c r="F422" t="inlineStr"/>
       <c r="G422" t="inlineStr">
         <is>
           <t>100</t>
@@ -22803,8 +22381,6 @@
           <t>711.29</t>
         </is>
       </c>
-      <c r="E423" t="inlineStr"/>
-      <c r="F423" t="inlineStr"/>
       <c r="G423" t="inlineStr">
         <is>
           <t>100</t>
@@ -22966,8 +22542,6 @@
           <t>713.8816</t>
         </is>
       </c>
-      <c r="E426" t="inlineStr"/>
-      <c r="F426" t="inlineStr"/>
       <c r="G426" t="inlineStr">
         <is>
           <t>100</t>
@@ -23072,8 +22646,6 @@
           <t>711.7058</t>
         </is>
       </c>
-      <c r="E428" t="inlineStr"/>
-      <c r="F428" t="inlineStr"/>
       <c r="G428" t="inlineStr">
         <is>
           <t>100</t>
@@ -23178,8 +22750,6 @@
           <t>712.4038</t>
         </is>
       </c>
-      <c r="E430" t="inlineStr"/>
-      <c r="F430" t="inlineStr"/>
       <c r="G430" t="inlineStr">
         <is>
           <t>100</t>
@@ -23227,8 +22797,6 @@
           <t>712.41</t>
         </is>
       </c>
-      <c r="E431" t="inlineStr"/>
-      <c r="F431" t="inlineStr"/>
       <c r="G431" t="inlineStr">
         <is>
           <t>100</t>
@@ -23333,8 +22901,6 @@
           <t>712.05</t>
         </is>
       </c>
-      <c r="E433" t="inlineStr"/>
-      <c r="F433" t="inlineStr"/>
       <c r="G433" t="inlineStr">
         <is>
           <t>100</t>
@@ -23382,8 +22948,6 @@
           <t>711.14</t>
         </is>
       </c>
-      <c r="E434" t="inlineStr"/>
-      <c r="F434" t="inlineStr"/>
       <c r="G434" t="inlineStr">
         <is>
           <t>100</t>
@@ -23602,8 +23166,6 @@
           <t>714.3934</t>
         </is>
       </c>
-      <c r="E438" t="inlineStr"/>
-      <c r="F438" t="inlineStr"/>
       <c r="G438" t="inlineStr">
         <is>
           <t>100</t>
@@ -23708,8 +23270,6 @@
           <t>723.1785</t>
         </is>
       </c>
-      <c r="E440" t="inlineStr"/>
-      <c r="F440" t="inlineStr"/>
       <c r="G440" t="inlineStr">
         <is>
           <t>100</t>
@@ -23814,8 +23374,6 @@
           <t>723.41</t>
         </is>
       </c>
-      <c r="E442" t="inlineStr"/>
-      <c r="F442" t="inlineStr"/>
       <c r="G442" t="inlineStr">
         <is>
           <t>100</t>
@@ -23920,8 +23478,6 @@
           <t>722.2</t>
         </is>
       </c>
-      <c r="E444" t="inlineStr"/>
-      <c r="F444" t="inlineStr"/>
       <c r="G444" t="inlineStr">
         <is>
           <t>100</t>
@@ -24026,8 +23582,6 @@
           <t>720.37</t>
         </is>
       </c>
-      <c r="E446" t="inlineStr"/>
-      <c r="F446" t="inlineStr"/>
       <c r="G446" t="inlineStr">
         <is>
           <t>100</t>
@@ -24132,8 +23686,6 @@
           <t>721.2701</t>
         </is>
       </c>
-      <c r="E448" t="inlineStr"/>
-      <c r="F448" t="inlineStr"/>
       <c r="G448" t="inlineStr">
         <is>
           <t>100</t>
@@ -24238,8 +23790,6 @@
           <t>721.241</t>
         </is>
       </c>
-      <c r="E450" t="inlineStr"/>
-      <c r="F450" t="inlineStr"/>
       <c r="G450" t="inlineStr">
         <is>
           <t>100</t>
@@ -24344,8 +23894,6 @@
           <t>721.975</t>
         </is>
       </c>
-      <c r="E452" t="inlineStr"/>
-      <c r="F452" t="inlineStr"/>
       <c r="G452" t="inlineStr">
         <is>
           <t>100</t>
@@ -24450,8 +23998,6 @@
           <t>721.2849</t>
         </is>
       </c>
-      <c r="E454" t="inlineStr"/>
-      <c r="F454" t="inlineStr"/>
       <c r="G454" t="inlineStr">
         <is>
           <t>100</t>
@@ -24499,8 +24045,6 @@
           <t>720.3499</t>
         </is>
       </c>
-      <c r="E455" t="inlineStr"/>
-      <c r="F455" t="inlineStr"/>
       <c r="G455" t="inlineStr">
         <is>
           <t>100</t>
@@ -24548,8 +24092,6 @@
           <t>717.9041</t>
         </is>
       </c>
-      <c r="E456" t="inlineStr"/>
-      <c r="F456" t="inlineStr"/>
       <c r="G456" t="inlineStr">
         <is>
           <t>100</t>
@@ -24654,8 +24196,6 @@
           <t>718.22</t>
         </is>
       </c>
-      <c r="E458" t="inlineStr"/>
-      <c r="F458" t="inlineStr"/>
       <c r="G458" t="inlineStr">
         <is>
           <t>100</t>
@@ -24760,8 +24300,6 @@
           <t>717.7455</t>
         </is>
       </c>
-      <c r="E460" t="inlineStr"/>
-      <c r="F460" t="inlineStr"/>
       <c r="G460" t="inlineStr">
         <is>
           <t>100</t>
@@ -24980,8 +24518,6 @@
           <t>723.575</t>
         </is>
       </c>
-      <c r="E464" t="inlineStr"/>
-      <c r="F464" t="inlineStr"/>
       <c r="G464" t="inlineStr">
         <is>
           <t>100</t>
@@ -25086,8 +24622,6 @@
           <t>723.11</t>
         </is>
       </c>
-      <c r="E466" t="inlineStr"/>
-      <c r="F466" t="inlineStr"/>
       <c r="G466" t="inlineStr">
         <is>
           <t>100</t>
@@ -25192,8 +24726,6 @@
           <t>734.33</t>
         </is>
       </c>
-      <c r="E468" t="inlineStr"/>
-      <c r="F468" t="inlineStr"/>
       <c r="G468" t="inlineStr">
         <is>
           <t>100</t>
@@ -25298,8 +24830,6 @@
           <t>734.785</t>
         </is>
       </c>
-      <c r="E470" t="inlineStr"/>
-      <c r="F470" t="inlineStr"/>
       <c r="G470" t="inlineStr">
         <is>
           <t>100</t>
@@ -25404,8 +24934,6 @@
           <t>735.2299</t>
         </is>
       </c>
-      <c r="E472" t="inlineStr"/>
-      <c r="F472" t="inlineStr"/>
       <c r="G472" t="inlineStr">
         <is>
           <t>100</t>
@@ -25510,8 +25038,6 @@
           <t>735.5099</t>
         </is>
       </c>
-      <c r="E474" t="inlineStr"/>
-      <c r="F474" t="inlineStr"/>
       <c r="G474" t="inlineStr">
         <is>
           <t>100</t>
@@ -25559,8 +25085,6 @@
           <t>731.8999</t>
         </is>
       </c>
-      <c r="E475" t="inlineStr"/>
-      <c r="F475" t="inlineStr"/>
       <c r="G475" t="inlineStr">
         <is>
           <t>100</t>
@@ -25722,8 +25246,6 @@
           <t>732.575</t>
         </is>
       </c>
-      <c r="E478" t="inlineStr"/>
-      <c r="F478" t="inlineStr"/>
       <c r="G478" t="inlineStr">
         <is>
           <t>100</t>
@@ -25828,8 +25350,6 @@
           <t>735.17</t>
         </is>
       </c>
-      <c r="E480" t="inlineStr"/>
-      <c r="F480" t="inlineStr"/>
       <c r="G480" t="inlineStr">
         <is>
           <t>100</t>
@@ -25934,8 +25454,6 @@
           <t>736.68</t>
         </is>
       </c>
-      <c r="E482" t="inlineStr"/>
-      <c r="F482" t="inlineStr"/>
       <c r="G482" t="inlineStr">
         <is>
           <t>100</t>
@@ -26040,8 +25558,6 @@
           <t>737.1672</t>
         </is>
       </c>
-      <c r="E484" t="inlineStr"/>
-      <c r="F484" t="inlineStr"/>
       <c r="G484" t="inlineStr">
         <is>
           <t>100</t>
@@ -26146,8 +25662,6 @@
           <t>736.745</t>
         </is>
       </c>
-      <c r="E486" t="inlineStr"/>
-      <c r="F486" t="inlineStr"/>
       <c r="G486" t="inlineStr">
         <is>
           <t>100</t>
@@ -26252,8 +25766,6 @@
           <t>736.26</t>
         </is>
       </c>
-      <c r="E488" t="inlineStr"/>
-      <c r="F488" t="inlineStr"/>
       <c r="G488" t="inlineStr">
         <is>
           <t>100</t>
@@ -26358,8 +25870,6 @@
           <t>737.195</t>
         </is>
       </c>
-      <c r="E490" t="inlineStr"/>
-      <c r="F490" t="inlineStr"/>
       <c r="G490" t="inlineStr">
         <is>
           <t>100</t>
@@ -26464,8 +25974,6 @@
           <t>739.47</t>
         </is>
       </c>
-      <c r="E492" t="inlineStr"/>
-      <c r="F492" t="inlineStr"/>
       <c r="G492" t="inlineStr">
         <is>
           <t>100</t>
@@ -26513,8 +26021,6 @@
           <t>738.7</t>
         </is>
       </c>
-      <c r="E493" t="inlineStr"/>
-      <c r="F493" t="inlineStr"/>
       <c r="G493" t="inlineStr">
         <is>
           <t>100</t>
@@ -26676,8 +26182,6 @@
           <t>736.18</t>
         </is>
       </c>
-      <c r="E496" t="inlineStr"/>
-      <c r="F496" t="inlineStr"/>
       <c r="G496" t="inlineStr">
         <is>
           <t>100</t>
@@ -26725,8 +26229,6 @@
           <t>735.3042</t>
         </is>
       </c>
-      <c r="E497" t="inlineStr"/>
-      <c r="F497" t="inlineStr"/>
       <c r="G497" t="inlineStr">
         <is>
           <t>100</t>
@@ -26888,8 +26390,6 @@
           <t>735.6034</t>
         </is>
       </c>
-      <c r="E500" t="inlineStr"/>
-      <c r="F500" t="inlineStr"/>
       <c r="G500" t="inlineStr">
         <is>
           <t>100</t>
@@ -26937,8 +26437,6 @@
           <t>733.58</t>
         </is>
       </c>
-      <c r="E501" t="inlineStr"/>
-      <c r="F501" t="inlineStr"/>
       <c r="G501" t="inlineStr">
         <is>
           <t>100</t>
@@ -27100,8 +26598,6 @@
           <t>740.5154</t>
         </is>
       </c>
-      <c r="E504" t="inlineStr"/>
-      <c r="F504" t="inlineStr"/>
       <c r="G504" t="inlineStr">
         <is>
           <t>100</t>
@@ -27206,8 +26702,6 @@
           <t>749.0692</t>
         </is>
       </c>
-      <c r="E506" t="inlineStr"/>
-      <c r="F506" t="inlineStr"/>
       <c r="G506" t="inlineStr">
         <is>
           <t>100</t>
@@ -27312,8 +26806,6 @@
           <t>747.595</t>
         </is>
       </c>
-      <c r="E508" t="inlineStr"/>
-      <c r="F508" t="inlineStr"/>
       <c r="G508" t="inlineStr">
         <is>
           <t>100</t>
@@ -27418,8 +26910,6 @@
           <t>740.705</t>
         </is>
       </c>
-      <c r="E510" t="inlineStr"/>
-      <c r="F510" t="inlineStr"/>
       <c r="G510" t="inlineStr">
         <is>
           <t>100</t>
@@ -27467,8 +26957,6 @@
           <t>739.25</t>
         </is>
       </c>
-      <c r="E511" t="inlineStr"/>
-      <c r="F511" t="inlineStr"/>
       <c r="G511" t="inlineStr">
         <is>
           <t>100</t>
@@ -27573,8 +27061,6 @@
           <t>739.555</t>
         </is>
       </c>
-      <c r="E513" t="inlineStr"/>
-      <c r="F513" t="inlineStr"/>
       <c r="G513" t="inlineStr">
         <is>
           <t>100</t>
@@ -27622,8 +27108,6 @@
           <t>741.475</t>
         </is>
       </c>
-      <c r="E514" t="inlineStr"/>
-      <c r="F514" t="inlineStr"/>
       <c r="G514" t="inlineStr">
         <is>
           <t>100</t>
@@ -27728,8 +27212,6 @@
           <t>741.8191</t>
         </is>
       </c>
-      <c r="E516" t="inlineStr"/>
-      <c r="F516" t="inlineStr"/>
       <c r="G516" t="inlineStr">
         <is>
           <t>100</t>
@@ -27834,8 +27316,6 @@
           <t>741.225</t>
         </is>
       </c>
-      <c r="E518" t="inlineStr"/>
-      <c r="F518" t="inlineStr"/>
       <c r="G518" t="inlineStr">
         <is>
           <t>100</t>
@@ -27940,8 +27420,6 @@
           <t>738.5799</t>
         </is>
       </c>
-      <c r="E520" t="inlineStr"/>
-      <c r="F520" t="inlineStr"/>
       <c r="G520" t="inlineStr">
         <is>
           <t>100</t>
@@ -28046,8 +27524,6 @@
           <t>737.195</t>
         </is>
       </c>
-      <c r="E522" t="inlineStr"/>
-      <c r="F522" t="inlineStr"/>
       <c r="G522" t="inlineStr">
         <is>
           <t>100</t>
@@ -28152,8 +27628,6 @@
           <t>734.695</t>
         </is>
       </c>
-      <c r="E524" t="inlineStr"/>
-      <c r="F524" t="inlineStr"/>
       <c r="G524" t="inlineStr">
         <is>
           <t>100</t>
@@ -28258,8 +27732,6 @@
           <t>732.225</t>
         </is>
       </c>
-      <c r="E526" t="inlineStr"/>
-      <c r="F526" t="inlineStr"/>
       <c r="G526" t="inlineStr">
         <is>
           <t>100</t>
@@ -28364,8 +27836,6 @@
           <t>735.5499</t>
         </is>
       </c>
-      <c r="E528" t="inlineStr"/>
-      <c r="F528" t="inlineStr"/>
       <c r="G528" t="inlineStr">
         <is>
           <t>100</t>
@@ -28413,8 +27883,6 @@
           <t>734.678</t>
         </is>
       </c>
-      <c r="E529" t="inlineStr"/>
-      <c r="F529" t="inlineStr"/>
       <c r="G529" t="inlineStr">
         <is>
           <t>100</t>
@@ -28519,8 +27987,6 @@
           <t>736.06</t>
         </is>
       </c>
-      <c r="E531" t="inlineStr"/>
-      <c r="F531" t="inlineStr"/>
       <c r="G531" t="inlineStr">
         <is>
           <t>100</t>
@@ -28682,8 +28148,6 @@
           <t>738.71</t>
         </is>
       </c>
-      <c r="E534" t="inlineStr"/>
-      <c r="F534" t="inlineStr"/>
       <c r="G534" t="inlineStr">
         <is>
           <t>100</t>
@@ -28788,8 +28252,6 @@
           <t>739.275</t>
         </is>
       </c>
-      <c r="E536" t="inlineStr"/>
-      <c r="F536" t="inlineStr"/>
       <c r="G536" t="inlineStr">
         <is>
           <t>100</t>
@@ -28894,8 +28356,6 @@
           <t>738.056</t>
         </is>
       </c>
-      <c r="E538" t="inlineStr"/>
-      <c r="F538" t="inlineStr"/>
       <c r="G538" t="inlineStr">
         <is>
           <t>100</t>
@@ -29000,8 +28460,6 @@
           <t>739.1004</t>
         </is>
       </c>
-      <c r="E540" t="inlineStr"/>
-      <c r="F540" t="inlineStr"/>
       <c r="G540" t="inlineStr">
         <is>
           <t>100</t>
@@ -29106,8 +28564,6 @@
           <t>739.68</t>
         </is>
       </c>
-      <c r="E542" t="inlineStr"/>
-      <c r="F542" t="inlineStr"/>
       <c r="G542" t="inlineStr">
         <is>
           <t>100</t>
@@ -29155,8 +28611,6 @@
           <t>738.589</t>
         </is>
       </c>
-      <c r="E543" t="inlineStr"/>
-      <c r="F543" t="inlineStr"/>
       <c r="G543" t="inlineStr">
         <is>
           <t>100</t>
@@ -29432,8 +28886,6 @@
           <t>751.4201</t>
         </is>
       </c>
-      <c r="E548" t="inlineStr"/>
-      <c r="F548" t="inlineStr"/>
       <c r="G548" t="inlineStr">
         <is>
           <t>100</t>
@@ -29538,8 +28990,6 @@
           <t>750.91</t>
         </is>
       </c>
-      <c r="E550" t="inlineStr"/>
-      <c r="F550" t="inlineStr"/>
       <c r="G550" t="inlineStr">
         <is>
           <t>100</t>
@@ -29644,8 +29094,6 @@
           <t>750.82</t>
         </is>
       </c>
-      <c r="E552" t="inlineStr"/>
-      <c r="F552" t="inlineStr"/>
       <c r="G552" t="inlineStr">
         <is>
           <t>100</t>
@@ -29750,8 +29198,6 @@
           <t>749.86</t>
         </is>
       </c>
-      <c r="E554" t="inlineStr"/>
-      <c r="F554" t="inlineStr"/>
       <c r="G554" t="inlineStr">
         <is>
           <t>100</t>
@@ -29856,8 +29302,6 @@
           <t>750.3794</t>
         </is>
       </c>
-      <c r="E556" t="inlineStr"/>
-      <c r="F556" t="inlineStr"/>
       <c r="G556" t="inlineStr">
         <is>
           <t>100</t>
@@ -29905,8 +29349,6 @@
           <t>750.735</t>
         </is>
       </c>
-      <c r="E557" t="inlineStr"/>
-      <c r="F557" t="inlineStr"/>
       <c r="G557" t="inlineStr">
         <is>
           <t>100</t>
@@ -30011,8 +29453,6 @@
           <t>749.795</t>
         </is>
       </c>
-      <c r="E559" t="inlineStr"/>
-      <c r="F559" t="inlineStr"/>
       <c r="G559" t="inlineStr">
         <is>
           <t>100</t>
@@ -30060,8 +29500,6 @@
           <t>749.205</t>
         </is>
       </c>
-      <c r="E560" t="inlineStr"/>
-      <c r="F560" t="inlineStr"/>
       <c r="G560" t="inlineStr">
         <is>
           <t>100</t>
@@ -30166,8 +29604,6 @@
           <t>748.745</t>
         </is>
       </c>
-      <c r="E562" t="inlineStr"/>
-      <c r="F562" t="inlineStr"/>
       <c r="G562" t="inlineStr">
         <is>
           <t>100</t>
@@ -30386,8 +29822,6 @@
           <t>751.809</t>
         </is>
       </c>
-      <c r="E566" t="inlineStr"/>
-      <c r="F566" t="inlineStr"/>
       <c r="G566" t="inlineStr">
         <is>
           <t>100</t>
@@ -30492,8 +29926,6 @@
           <t>752.255</t>
         </is>
       </c>
-      <c r="E568" t="inlineStr"/>
-      <c r="F568" t="inlineStr"/>
       <c r="G568" t="inlineStr">
         <is>
           <t>100</t>
@@ -30598,8 +30030,6 @@
           <t>754.0793</t>
         </is>
       </c>
-      <c r="E570" t="inlineStr"/>
-      <c r="F570" t="inlineStr"/>
       <c r="G570" t="inlineStr">
         <is>
           <t>100</t>
@@ -30704,8 +30134,6 @@
           <t>754.3999</t>
         </is>
       </c>
-      <c r="E572" t="inlineStr"/>
-      <c r="F572" t="inlineStr"/>
       <c r="G572" t="inlineStr">
         <is>
           <t>100</t>
@@ -30753,8 +30181,6 @@
           <t>754.3299</t>
         </is>
       </c>
-      <c r="E573" t="inlineStr"/>
-      <c r="F573" t="inlineStr"/>
       <c r="G573" t="inlineStr">
         <is>
           <t>100</t>
@@ -30916,8 +30342,6 @@
           <t>756.286</t>
         </is>
       </c>
-      <c r="E576" t="inlineStr"/>
-      <c r="F576" t="inlineStr"/>
       <c r="G576" t="inlineStr">
         <is>
           <t>100</t>
@@ -30965,8 +30389,6 @@
           <t>754.9899</t>
         </is>
       </c>
-      <c r="E577" t="inlineStr"/>
-      <c r="F577" t="inlineStr"/>
       <c r="G577" t="inlineStr">
         <is>
           <t>100</t>
@@ -31128,8 +30550,6 @@
           <t>756.935</t>
         </is>
       </c>
-      <c r="E580" t="inlineStr"/>
-      <c r="F580" t="inlineStr"/>
       <c r="G580" t="inlineStr">
         <is>
           <t>100</t>
@@ -31234,8 +30654,6 @@
           <t>755.185</t>
         </is>
       </c>
-      <c r="E582" t="inlineStr"/>
-      <c r="F582" t="inlineStr"/>
       <c r="G582" t="inlineStr">
         <is>
           <t>100</t>
@@ -31340,8 +30758,6 @@
           <t>756.0203</t>
         </is>
       </c>
-      <c r="E584" t="inlineStr"/>
-      <c r="F584" t="inlineStr"/>
       <c r="G584" t="inlineStr">
         <is>
           <t>100</t>
@@ -31446,8 +30862,6 @@
           <t>755.075</t>
         </is>
       </c>
-      <c r="E586" t="inlineStr"/>
-      <c r="F586" t="inlineStr"/>
       <c r="G586" t="inlineStr">
         <is>
           <t>100</t>
@@ -31552,8 +30966,6 @@
           <t>755.475</t>
         </is>
       </c>
-      <c r="E588" t="inlineStr"/>
-      <c r="F588" t="inlineStr"/>
       <c r="G588" t="inlineStr">
         <is>
           <t>100</t>
@@ -31658,8 +31070,6 @@
           <t>755.15</t>
         </is>
       </c>
-      <c r="E590" t="inlineStr"/>
-      <c r="F590" t="inlineStr"/>
       <c r="G590" t="inlineStr">
         <is>
           <t>100</t>
@@ -31764,8 +31174,6 @@
           <t>754.7048</t>
         </is>
       </c>
-      <c r="E592" t="inlineStr"/>
-      <c r="F592" t="inlineStr"/>
       <c r="G592" t="inlineStr">
         <is>
           <t>100</t>
@@ -31870,8 +31278,6 @@
           <t>753.175</t>
         </is>
       </c>
-      <c r="E594" t="inlineStr"/>
-      <c r="F594" t="inlineStr"/>
       <c r="G594" t="inlineStr">
         <is>
           <t>100</t>
@@ -31976,8 +31382,6 @@
           <t>754.0544</t>
         </is>
       </c>
-      <c r="E596" t="inlineStr"/>
-      <c r="F596" t="inlineStr"/>
       <c r="G596" t="inlineStr">
         <is>
           <t>100</t>
@@ -32082,8 +31486,6 @@
           <t>754.7288</t>
         </is>
       </c>
-      <c r="E598" t="inlineStr"/>
-      <c r="F598" t="inlineStr"/>
       <c r="G598" t="inlineStr">
         <is>
           <t>100</t>
@@ -32188,8 +31590,6 @@
           <t>755.17</t>
         </is>
       </c>
-      <c r="E600" t="inlineStr"/>
-      <c r="F600" t="inlineStr"/>
       <c r="G600" t="inlineStr">
         <is>
           <t>100</t>
@@ -32294,8 +31694,6 @@
           <t>755.459</t>
         </is>
       </c>
-      <c r="E602" t="inlineStr"/>
-      <c r="F602" t="inlineStr"/>
       <c r="G602" t="inlineStr">
         <is>
           <t>100</t>
@@ -32400,8 +31798,6 @@
           <t>755.54</t>
         </is>
       </c>
-      <c r="E604" t="inlineStr"/>
-      <c r="F604" t="inlineStr"/>
       <c r="G604" t="inlineStr">
         <is>
           <t>100</t>
@@ -32506,8 +31902,6 @@
           <t>750.5</t>
         </is>
       </c>
-      <c r="E606" t="inlineStr"/>
-      <c r="F606" t="inlineStr"/>
       <c r="G606" t="inlineStr">
         <is>
           <t>100</t>
@@ -32555,8 +31949,6 @@
           <t>749.855</t>
         </is>
       </c>
-      <c r="E607" t="inlineStr"/>
-      <c r="F607" t="inlineStr"/>
       <c r="G607" t="inlineStr">
         <is>
           <t>100</t>
@@ -32661,8 +32053,6 @@
           <t>749.1694</t>
         </is>
       </c>
-      <c r="E609" t="inlineStr"/>
-      <c r="F609" t="inlineStr"/>
       <c r="G609" t="inlineStr">
         <is>
           <t>100</t>
@@ -32824,8 +32214,6 @@
           <t>749.33</t>
         </is>
       </c>
-      <c r="E612" t="inlineStr"/>
-      <c r="F612" t="inlineStr"/>
       <c r="G612" t="inlineStr">
         <is>
           <t>100</t>
@@ -32930,8 +32318,6 @@
           <t>749.7746</t>
         </is>
       </c>
-      <c r="E614" t="inlineStr"/>
-      <c r="F614" t="inlineStr"/>
       <c r="G614" t="inlineStr">
         <is>
           <t>100</t>
@@ -33036,8 +32422,6 @@
           <t>749.37</t>
         </is>
       </c>
-      <c r="E616" t="inlineStr"/>
-      <c r="F616" t="inlineStr"/>
       <c r="G616" t="inlineStr">
         <is>
           <t>100</t>
@@ -33085,8 +32469,6 @@
           <t>748.45</t>
         </is>
       </c>
-      <c r="E617" t="inlineStr"/>
-      <c r="F617" t="inlineStr"/>
       <c r="G617" t="inlineStr">
         <is>
           <t>100</t>
@@ -33134,8 +32516,6 @@
           <t>746.53</t>
         </is>
       </c>
-      <c r="E618" t="inlineStr"/>
-      <c r="F618" t="inlineStr"/>
       <c r="G618" t="inlineStr">
         <is>
           <t>100</t>
@@ -33183,8 +32563,6 @@
           <t>742.225</t>
         </is>
       </c>
-      <c r="E619" t="inlineStr"/>
-      <c r="F619" t="inlineStr"/>
       <c r="G619" t="inlineStr">
         <is>
           <t>100</t>
@@ -33289,8 +32667,6 @@
           <t>743.5268</t>
         </is>
       </c>
-      <c r="E621" t="inlineStr"/>
-      <c r="F621" t="inlineStr"/>
       <c r="G621" t="inlineStr">
         <is>
           <t>100</t>
@@ -33395,8 +32771,6 @@
           <t>742.838</t>
         </is>
       </c>
-      <c r="E623" t="inlineStr"/>
-      <c r="F623" t="inlineStr"/>
       <c r="G623" t="inlineStr">
         <is>
           <t>100</t>
@@ -33558,8 +32932,6 @@
           <t>741.135</t>
         </is>
       </c>
-      <c r="E626" t="inlineStr"/>
-      <c r="F626" t="inlineStr"/>
       <c r="G626" t="inlineStr">
         <is>
           <t>100</t>
@@ -33664,8 +33036,6 @@
           <t>744.535</t>
         </is>
       </c>
-      <c r="E628" t="inlineStr"/>
-      <c r="F628" t="inlineStr"/>
       <c r="G628" t="inlineStr">
         <is>
           <t>100</t>
@@ -33770,8 +33140,6 @@
           <t>746.7199</t>
         </is>
       </c>
-      <c r="E630" t="inlineStr"/>
-      <c r="F630" t="inlineStr"/>
       <c r="G630" t="inlineStr">
         <is>
           <t>100</t>
@@ -33876,8 +33244,6 @@
           <t>745.27</t>
         </is>
       </c>
-      <c r="E632" t="inlineStr"/>
-      <c r="F632" t="inlineStr"/>
       <c r="G632" t="inlineStr">
         <is>
           <t>100</t>
@@ -33982,8 +33348,6 @@
           <t>744.176</t>
         </is>
       </c>
-      <c r="E634" t="inlineStr"/>
-      <c r="F634" t="inlineStr"/>
       <c r="G634" t="inlineStr">
         <is>
           <t>100</t>
@@ -34088,8 +33452,6 @@
           <t>742.915</t>
         </is>
       </c>
-      <c r="E636" t="inlineStr"/>
-      <c r="F636" t="inlineStr"/>
       <c r="G636" t="inlineStr">
         <is>
           <t>100</t>
@@ -34137,8 +33499,6 @@
           <t>740.8973</t>
         </is>
       </c>
-      <c r="E637" t="inlineStr"/>
-      <c r="F637" t="inlineStr"/>
       <c r="G637" t="inlineStr">
         <is>
           <t>100</t>
@@ -34243,8 +33603,6 @@
           <t>735.489</t>
         </is>
       </c>
-      <c r="E639" t="inlineStr"/>
-      <c r="F639" t="inlineStr"/>
       <c r="G639" t="inlineStr">
         <is>
           <t>100</t>
@@ -34349,8 +33707,6 @@
           <t>736.5999</t>
         </is>
       </c>
-      <c r="E641" t="inlineStr"/>
-      <c r="F641" t="inlineStr"/>
       <c r="G641" t="inlineStr">
         <is>
           <t>100</t>
@@ -34455,8 +33811,6 @@
           <t>736.49</t>
         </is>
       </c>
-      <c r="E643" t="inlineStr"/>
-      <c r="F643" t="inlineStr"/>
       <c r="G643" t="inlineStr">
         <is>
           <t>100</t>
@@ -34561,8 +33915,6 @@
           <t>737.355</t>
         </is>
       </c>
-      <c r="E645" t="inlineStr"/>
-      <c r="F645" t="inlineStr"/>
       <c r="G645" t="inlineStr">
         <is>
           <t>100</t>
@@ -34667,8 +34019,6 @@
           <t>737.6199</t>
         </is>
       </c>
-      <c r="E647" t="inlineStr"/>
-      <c r="F647" t="inlineStr"/>
       <c r="G647" t="inlineStr">
         <is>
           <t>100</t>
@@ -34773,8 +34123,6 @@
           <t>724.9499</t>
         </is>
       </c>
-      <c r="E649" t="inlineStr"/>
-      <c r="F649" t="inlineStr"/>
       <c r="G649" t="inlineStr">
         <is>
           <t>100</t>
@@ -34879,8 +34227,6 @@
           <t>734.66</t>
         </is>
       </c>
-      <c r="E651" t="inlineStr"/>
-      <c r="F651" t="inlineStr"/>
       <c r="G651" t="inlineStr">
         <is>
           <t>100</t>
@@ -34985,8 +34331,6 @@
           <t>735.235</t>
         </is>
       </c>
-      <c r="E653" t="inlineStr"/>
-      <c r="F653" t="inlineStr"/>
       <c r="G653" t="inlineStr">
         <is>
           <t>100</t>
@@ -35091,8 +34435,6 @@
           <t>736.01</t>
         </is>
       </c>
-      <c r="E655" t="inlineStr"/>
-      <c r="F655" t="inlineStr"/>
       <c r="G655" t="inlineStr">
         <is>
           <t>100</t>
@@ -35197,8 +34539,6 @@
           <t>736.64</t>
         </is>
       </c>
-      <c r="E657" t="inlineStr"/>
-      <c r="F657" t="inlineStr"/>
       <c r="G657" t="inlineStr">
         <is>
           <t>100</t>
@@ -35303,8 +34643,6 @@
           <t>736.86</t>
         </is>
       </c>
-      <c r="E659" t="inlineStr"/>
-      <c r="F659" t="inlineStr"/>
       <c r="G659" t="inlineStr">
         <is>
           <t>100</t>
@@ -35409,8 +34747,6 @@
           <t>736.2251</t>
         </is>
       </c>
-      <c r="E661" t="inlineStr"/>
-      <c r="F661" t="inlineStr"/>
       <c r="G661" t="inlineStr">
         <is>
           <t>100</t>
@@ -35515,8 +34851,6 @@
           <t>736.614</t>
         </is>
       </c>
-      <c r="E663" t="inlineStr"/>
-      <c r="F663" t="inlineStr"/>
       <c r="G663" t="inlineStr">
         <is>
           <t>100</t>
@@ -35621,8 +34955,6 @@
           <t>737.195</t>
         </is>
       </c>
-      <c r="E665" t="inlineStr"/>
-      <c r="F665" t="inlineStr"/>
       <c r="G665" t="inlineStr">
         <is>
           <t>100</t>
@@ -35727,8 +35059,6 @@
           <t>735.6195</t>
         </is>
       </c>
-      <c r="E667" t="inlineStr"/>
-      <c r="F667" t="inlineStr"/>
       <c r="G667" t="inlineStr">
         <is>
           <t>100</t>
@@ -35833,8 +35163,6 @@
           <t>732.2546</t>
         </is>
       </c>
-      <c r="E669" t="inlineStr"/>
-      <c r="F669" t="inlineStr"/>
       <c r="G669" t="inlineStr">
         <is>
           <t>100</t>
@@ -35939,8 +35267,6 @@
           <t>730.8375</t>
         </is>
       </c>
-      <c r="E671" t="inlineStr"/>
-      <c r="F671" t="inlineStr"/>
       <c r="G671" t="inlineStr">
         <is>
           <t>100</t>
@@ -36045,8 +35371,6 @@
           <t>727.785</t>
         </is>
       </c>
-      <c r="E673" t="inlineStr"/>
-      <c r="F673" t="inlineStr"/>
       <c r="G673" t="inlineStr">
         <is>
           <t>100</t>
@@ -36151,8 +35475,6 @@
           <t>730.51</t>
         </is>
       </c>
-      <c r="E675" t="inlineStr"/>
-      <c r="F675" t="inlineStr"/>
       <c r="G675" t="inlineStr">
         <is>
           <t>100</t>
@@ -36257,8 +35579,6 @@
           <t>727.03</t>
         </is>
       </c>
-      <c r="E677" t="inlineStr"/>
-      <c r="F677" t="inlineStr"/>
       <c r="G677" t="inlineStr">
         <is>
           <t>100</t>
@@ -36363,8 +35683,6 @@
           <t>729.09</t>
         </is>
       </c>
-      <c r="E679" t="inlineStr"/>
-      <c r="F679" t="inlineStr"/>
       <c r="G679" t="inlineStr">
         <is>
           <t>100</t>
@@ -36469,8 +35787,6 @@
           <t>729.859</t>
         </is>
       </c>
-      <c r="E681" t="inlineStr"/>
-      <c r="F681" t="inlineStr"/>
       <c r="G681" t="inlineStr">
         <is>
           <t>100</t>
@@ -36575,8 +35891,6 @@
           <t>726.4348</t>
         </is>
       </c>
-      <c r="E683" t="inlineStr"/>
-      <c r="F683" t="inlineStr"/>
       <c r="G683" t="inlineStr">
         <is>
           <t>100</t>
@@ -36681,8 +35995,6 @@
           <t>727.0299</t>
         </is>
       </c>
-      <c r="E685" t="inlineStr"/>
-      <c r="F685" t="inlineStr"/>
       <c r="G685" t="inlineStr">
         <is>
           <t>100</t>
@@ -36787,8 +36099,6 @@
           <t>727.0799</t>
         </is>
       </c>
-      <c r="E687" t="inlineStr"/>
-      <c r="F687" t="inlineStr"/>
       <c r="G687" t="inlineStr">
         <is>
           <t>100</t>
@@ -36893,8 +36203,6 @@
           <t>727.9459</t>
         </is>
       </c>
-      <c r="E689" t="inlineStr"/>
-      <c r="F689" t="inlineStr"/>
       <c r="G689" t="inlineStr">
         <is>
           <t>100</t>
@@ -36942,8 +36250,6 @@
           <t>728.535</t>
         </is>
       </c>
-      <c r="E690" t="inlineStr"/>
-      <c r="F690" t="inlineStr"/>
       <c r="G690" t="inlineStr">
         <is>
           <t>100</t>
@@ -37048,8 +36354,6 @@
           <t>738.859</t>
         </is>
       </c>
-      <c r="E692" t="inlineStr"/>
-      <c r="F692" t="inlineStr"/>
       <c r="G692" t="inlineStr">
         <is>
           <t>100</t>
@@ -37154,8 +36458,6 @@
           <t>739.3193</t>
         </is>
       </c>
-      <c r="E694" t="inlineStr"/>
-      <c r="F694" t="inlineStr"/>
       <c r="G694" t="inlineStr">
         <is>
           <t>100</t>
@@ -37260,8 +36562,6 @@
           <t>741.605</t>
         </is>
       </c>
-      <c r="E696" t="inlineStr"/>
-      <c r="F696" t="inlineStr"/>
       <c r="G696" t="inlineStr">
         <is>
           <t>100</t>
@@ -37366,8 +36666,6 @@
           <t>740.715</t>
         </is>
       </c>
-      <c r="E698" t="inlineStr"/>
-      <c r="F698" t="inlineStr"/>
       <c r="G698" t="inlineStr">
         <is>
           <t>100</t>
@@ -37472,8 +36770,6 @@
           <t>740.76</t>
         </is>
       </c>
-      <c r="E700" t="inlineStr"/>
-      <c r="F700" t="inlineStr"/>
       <c r="G700" t="inlineStr">
         <is>
           <t>100</t>
@@ -37578,8 +36874,6 @@
           <t>740.76</t>
         </is>
       </c>
-      <c r="E702" t="inlineStr"/>
-      <c r="F702" t="inlineStr"/>
       <c r="G702" t="inlineStr">
         <is>
           <t>100</t>
@@ -37684,8 +36978,6 @@
           <t>741.7299</t>
         </is>
       </c>
-      <c r="E704" t="inlineStr"/>
-      <c r="F704" t="inlineStr"/>
       <c r="G704" t="inlineStr">
         <is>
           <t>100</t>
@@ -38018,8 +37310,6 @@
           <t>752.965</t>
         </is>
       </c>
-      <c r="E710" t="inlineStr"/>
-      <c r="F710" t="inlineStr"/>
       <c r="G710" t="inlineStr">
         <is>
           <t>100</t>
@@ -38124,8 +37414,6 @@
           <t>755.9399</t>
         </is>
       </c>
-      <c r="E712" t="inlineStr"/>
-      <c r="F712" t="inlineStr"/>
       <c r="G712" t="inlineStr">
         <is>
           <t>100</t>
@@ -38230,8 +37518,6 @@
           <t>754.5865</t>
         </is>
       </c>
-      <c r="E714" t="inlineStr"/>
-      <c r="F714" t="inlineStr"/>
       <c r="G714" t="inlineStr">
         <is>
           <t>100</t>
@@ -38279,8 +37565,6 @@
           <t>754.41</t>
         </is>
       </c>
-      <c r="E715" t="inlineStr"/>
-      <c r="F715" t="inlineStr"/>
       <c r="G715" t="inlineStr">
         <is>
           <t>100</t>
@@ -38442,8 +37726,6 @@
           <t>753.13</t>
         </is>
       </c>
-      <c r="E718" t="inlineStr"/>
-      <c r="F718" t="inlineStr"/>
       <c r="G718" t="inlineStr">
         <is>
           <t>100</t>
@@ -38491,8 +37773,6 @@
           <t>752.755</t>
         </is>
       </c>
-      <c r="E719" t="inlineStr"/>
-      <c r="F719" t="inlineStr"/>
       <c r="G719" t="inlineStr">
         <is>
           <t>100</t>
@@ -38597,8 +37877,6 @@
           <t>752.535</t>
         </is>
       </c>
-      <c r="E721" t="inlineStr"/>
-      <c r="F721" t="inlineStr"/>
       <c r="G721" t="inlineStr">
         <is>
           <t>100</t>
@@ -38703,8 +37981,6 @@
           <t>752.285</t>
         </is>
       </c>
-      <c r="E723" t="inlineStr"/>
-      <c r="F723" t="inlineStr"/>
       <c r="G723" t="inlineStr">
         <is>
           <t>100</t>
@@ -38809,8 +38085,6 @@
           <t>752.33</t>
         </is>
       </c>
-      <c r="E725" t="inlineStr"/>
-      <c r="F725" t="inlineStr"/>
       <c r="G725" t="inlineStr">
         <is>
           <t>100</t>
@@ -38915,8 +38189,6 @@
           <t>750.4806</t>
         </is>
       </c>
-      <c r="E727" t="inlineStr"/>
-      <c r="F727" t="inlineStr"/>
       <c r="G727" t="inlineStr">
         <is>
           <t>100</t>
@@ -39021,8 +38293,6 @@
           <t>751.36</t>
         </is>
       </c>
-      <c r="E729" t="inlineStr"/>
-      <c r="F729" t="inlineStr"/>
       <c r="G729" t="inlineStr">
         <is>
           <t>100</t>
@@ -39127,8 +38397,6 @@
           <t>751.1218</t>
         </is>
       </c>
-      <c r="E731" t="inlineStr"/>
-      <c r="F731" t="inlineStr"/>
       <c r="G731" t="inlineStr">
         <is>
           <t>100</t>
@@ -39233,8 +38501,6 @@
           <t>749.9399</t>
         </is>
       </c>
-      <c r="E733" t="inlineStr"/>
-      <c r="F733" t="inlineStr"/>
       <c r="G733" t="inlineStr">
         <is>
           <t>100</t>
@@ -39339,8 +38605,6 @@
           <t>750.96</t>
         </is>
       </c>
-      <c r="E735" t="inlineStr"/>
-      <c r="F735" t="inlineStr"/>
       <c r="G735" t="inlineStr">
         <is>
           <t>100</t>
@@ -39445,8 +38709,6 @@
           <t>750.8</t>
         </is>
       </c>
-      <c r="E737" t="inlineStr"/>
-      <c r="F737" t="inlineStr"/>
       <c r="G737" t="inlineStr">
         <is>
           <t>100</t>
@@ -39551,8 +38813,6 @@
           <t>751.715</t>
         </is>
       </c>
-      <c r="E739" t="inlineStr"/>
-      <c r="F739" t="inlineStr"/>
       <c r="G739" t="inlineStr">
         <is>
           <t>100</t>
@@ -39657,8 +38917,6 @@
           <t>751.81</t>
         </is>
       </c>
-      <c r="E741" t="inlineStr"/>
-      <c r="F741" t="inlineStr"/>
       <c r="G741" t="inlineStr">
         <is>
           <t>100</t>
@@ -39763,8 +39021,6 @@
           <t>750.569</t>
         </is>
       </c>
-      <c r="E743" t="inlineStr"/>
-      <c r="F743" t="inlineStr"/>
       <c r="G743" t="inlineStr">
         <is>
           <t>100</t>
@@ -39869,8 +39125,6 @@
           <t>750.419</t>
         </is>
       </c>
-      <c r="E745" t="inlineStr"/>
-      <c r="F745" t="inlineStr"/>
       <c r="G745" t="inlineStr">
         <is>
           <t>100</t>
@@ -39975,8 +39229,6 @@
           <t>750.861</t>
         </is>
       </c>
-      <c r="E747" t="inlineStr"/>
-      <c r="F747" t="inlineStr"/>
       <c r="G747" t="inlineStr">
         <is>
           <t>100</t>
@@ -40081,8 +39333,6 @@
           <t>750.883</t>
         </is>
       </c>
-      <c r="E749" t="inlineStr"/>
-      <c r="F749" t="inlineStr"/>
       <c r="G749" t="inlineStr">
         <is>
           <t>100</t>
@@ -40187,8 +39437,6 @@
           <t>749.9899</t>
         </is>
       </c>
-      <c r="E751" t="inlineStr"/>
-      <c r="F751" t="inlineStr"/>
       <c r="G751" t="inlineStr">
         <is>
           <t>100</t>
@@ -40293,8 +39541,6 @@
           <t>750.005</t>
         </is>
       </c>
-      <c r="E753" t="inlineStr"/>
-      <c r="F753" t="inlineStr"/>
       <c r="G753" t="inlineStr">
         <is>
           <t>100</t>
@@ -40399,8 +39645,6 @@
           <t>750.005</t>
         </is>
       </c>
-      <c r="E755" t="inlineStr"/>
-      <c r="F755" t="inlineStr"/>
       <c r="G755" t="inlineStr">
         <is>
           <t>100</t>
@@ -40505,8 +39749,6 @@
           <t>744.875</t>
         </is>
       </c>
-      <c r="E757" t="inlineStr"/>
-      <c r="F757" t="inlineStr"/>
       <c r="G757" t="inlineStr">
         <is>
           <t>100</t>
@@ -40611,8 +39853,6 @@
           <t>746.87</t>
         </is>
       </c>
-      <c r="E759" t="inlineStr"/>
-      <c r="F759" t="inlineStr"/>
       <c r="G759" t="inlineStr">
         <is>
           <t>100</t>
@@ -40717,8 +39957,6 @@
           <t>746.7696</t>
         </is>
       </c>
-      <c r="E761" t="inlineStr"/>
-      <c r="F761" t="inlineStr"/>
       <c r="G761" t="inlineStr">
         <is>
           <t>100</t>
@@ -40823,8 +40061,6 @@
           <t>746.345</t>
         </is>
       </c>
-      <c r="E763" t="inlineStr"/>
-      <c r="F763" t="inlineStr"/>
       <c r="G763" t="inlineStr">
         <is>
           <t>100</t>
@@ -40929,8 +40165,6 @@
           <t>745.669</t>
         </is>
       </c>
-      <c r="E765" t="inlineStr"/>
-      <c r="F765" t="inlineStr"/>
       <c r="G765" t="inlineStr">
         <is>
           <t>100</t>
@@ -41035,8 +40269,6 @@
           <t>745.77</t>
         </is>
       </c>
-      <c r="E767" t="inlineStr"/>
-      <c r="F767" t="inlineStr"/>
       <c r="G767" t="inlineStr">
         <is>
           <t>100</t>
@@ -41141,8 +40373,6 @@
           <t>746.7371</t>
         </is>
       </c>
-      <c r="E769" t="inlineStr"/>
-      <c r="F769" t="inlineStr"/>
       <c r="G769" t="inlineStr">
         <is>
           <t>100</t>
@@ -41247,8 +40477,6 @@
           <t>746.5604</t>
         </is>
       </c>
-      <c r="E771" t="inlineStr"/>
-      <c r="F771" t="inlineStr"/>
       <c r="G771" t="inlineStr">
         <is>
           <t>100</t>
@@ -41353,8 +40581,6 @@
           <t>749.086</t>
         </is>
       </c>
-      <c r="E773" t="inlineStr"/>
-      <c r="F773" t="inlineStr"/>
       <c r="G773" t="inlineStr">
         <is>
           <t>100</t>
@@ -41459,8 +40685,6 @@
           <t>749.76</t>
         </is>
       </c>
-      <c r="E775" t="inlineStr"/>
-      <c r="F775" t="inlineStr"/>
       <c r="G775" t="inlineStr">
         <is>
           <t>100</t>
@@ -41565,8 +40789,6 @@
           <t>744.8677</t>
         </is>
       </c>
-      <c r="E777" t="inlineStr"/>
-      <c r="F777" t="inlineStr"/>
       <c r="G777" t="inlineStr">
         <is>
           <t>100</t>
@@ -41671,8 +40893,6 @@
           <t>744.7685</t>
         </is>
       </c>
-      <c r="E779" t="inlineStr"/>
-      <c r="F779" t="inlineStr"/>
       <c r="G779" t="inlineStr">
         <is>
           <t>100</t>
@@ -41777,8 +40997,6 @@
           <t>744.43</t>
         </is>
       </c>
-      <c r="E781" t="inlineStr"/>
-      <c r="F781" t="inlineStr"/>
       <c r="G781" t="inlineStr">
         <is>
           <t>100</t>
@@ -41883,8 +41101,6 @@
           <t>744.175</t>
         </is>
       </c>
-      <c r="E783" t="inlineStr"/>
-      <c r="F783" t="inlineStr"/>
       <c r="G783" t="inlineStr">
         <is>
           <t>100</t>
@@ -41989,8 +41205,6 @@
           <t>744.335</t>
         </is>
       </c>
-      <c r="E785" t="inlineStr"/>
-      <c r="F785" t="inlineStr"/>
       <c r="G785" t="inlineStr">
         <is>
           <t>100</t>
@@ -42095,8 +41309,6 @@
           <t>737.9878</t>
         </is>
       </c>
-      <c r="E787" t="inlineStr"/>
-      <c r="F787" t="inlineStr"/>
       <c r="G787" t="inlineStr">
         <is>
           <t>100</t>
@@ -42201,8 +41413,6 @@
           <t>738.723</t>
         </is>
       </c>
-      <c r="E789" t="inlineStr"/>
-      <c r="F789" t="inlineStr"/>
       <c r="G789" t="inlineStr">
         <is>
           <t>100</t>
@@ -42307,8 +41517,6 @@
           <t>738.4288</t>
         </is>
       </c>
-      <c r="E791" t="inlineStr"/>
-      <c r="F791" t="inlineStr"/>
       <c r="G791" t="inlineStr">
         <is>
           <t>100</t>
@@ -42413,8 +41621,6 @@
           <t>738.4473</t>
         </is>
       </c>
-      <c r="E793" t="inlineStr"/>
-      <c r="F793" t="inlineStr"/>
       <c r="G793" t="inlineStr">
         <is>
           <t>100</t>
@@ -42519,8 +41725,6 @@
           <t>736.95</t>
         </is>
       </c>
-      <c r="E795" t="inlineStr"/>
-      <c r="F795" t="inlineStr"/>
       <c r="G795" t="inlineStr">
         <is>
           <t>100</t>
@@ -42568,8 +41772,6 @@
           <t>735.905</t>
         </is>
       </c>
-      <c r="E796" t="inlineStr"/>
-      <c r="F796" t="inlineStr"/>
       <c r="G796" t="inlineStr">
         <is>
           <t>100</t>
@@ -42731,8 +41933,6 @@
           <t>737.8499</t>
         </is>
       </c>
-      <c r="E799" t="inlineStr"/>
-      <c r="F799" t="inlineStr"/>
       <c r="G799" t="inlineStr">
         <is>
           <t>100</t>
@@ -42837,8 +42037,6 @@
           <t>735.3259</t>
         </is>
       </c>
-      <c r="E801" t="inlineStr"/>
-      <c r="F801" t="inlineStr"/>
       <c r="G801" t="inlineStr">
         <is>
           <t>100</t>
@@ -42943,8 +42141,6 @@
           <t>735.8106</t>
         </is>
       </c>
-      <c r="E803" t="inlineStr"/>
-      <c r="F803" t="inlineStr"/>
       <c r="G803" t="inlineStr">
         <is>
           <t>100</t>
@@ -43049,8 +42245,6 @@
           <t>734.51</t>
         </is>
       </c>
-      <c r="E805" t="inlineStr"/>
-      <c r="F805" t="inlineStr"/>
       <c r="G805" t="inlineStr">
         <is>
           <t>100</t>
@@ -43155,8 +42349,6 @@
           <t>736.105</t>
         </is>
       </c>
-      <c r="E807" t="inlineStr"/>
-      <c r="F807" t="inlineStr"/>
       <c r="G807" t="inlineStr">
         <is>
           <t>100</t>
@@ -43261,8 +42453,6 @@
           <t>737.485</t>
         </is>
       </c>
-      <c r="E809" t="inlineStr"/>
-      <c r="F809" t="inlineStr"/>
       <c r="G809" t="inlineStr">
         <is>
           <t>100</t>
@@ -43367,8 +42557,6 @@
           <t>735.9898</t>
         </is>
       </c>
-      <c r="E811" t="inlineStr"/>
-      <c r="F811" t="inlineStr"/>
       <c r="G811" t="inlineStr">
         <is>
           <t>100</t>
@@ -43473,8 +42661,6 @@
           <t>739.37</t>
         </is>
       </c>
-      <c r="E813" t="inlineStr"/>
-      <c r="F813" t="inlineStr"/>
       <c r="G813" t="inlineStr">
         <is>
           <t>100</t>
@@ -43579,8 +42765,6 @@
           <t>738.69</t>
         </is>
       </c>
-      <c r="E815" t="inlineStr"/>
-      <c r="F815" t="inlineStr"/>
       <c r="G815" t="inlineStr">
         <is>
           <t>100</t>
@@ -43685,8 +42869,6 @@
           <t>737.9302</t>
         </is>
       </c>
-      <c r="E817" t="inlineStr"/>
-      <c r="F817" t="inlineStr"/>
       <c r="G817" t="inlineStr">
         <is>
           <t>100</t>
@@ -43791,8 +42973,6 @@
           <t>738.6</t>
         </is>
       </c>
-      <c r="E819" t="inlineStr"/>
-      <c r="F819" t="inlineStr"/>
       <c r="G819" t="inlineStr">
         <is>
           <t>100</t>
@@ -43897,8 +43077,6 @@
           <t>738.19</t>
         </is>
       </c>
-      <c r="E821" t="inlineStr"/>
-      <c r="F821" t="inlineStr"/>
       <c r="G821" t="inlineStr">
         <is>
           <t>100</t>
@@ -44003,8 +43181,6 @@
           <t>737.045</t>
         </is>
       </c>
-      <c r="E823" t="inlineStr"/>
-      <c r="F823" t="inlineStr"/>
       <c r="G823" t="inlineStr">
         <is>
           <t>100</t>
@@ -44052,8 +43228,6 @@
           <t>732.475</t>
         </is>
       </c>
-      <c r="E824" t="inlineStr"/>
-      <c r="F824" t="inlineStr"/>
       <c r="G824" t="inlineStr">
         <is>
           <t>100</t>
@@ -44101,8 +43275,6 @@
           <t>733.2678</t>
         </is>
       </c>
-      <c r="E825" t="inlineStr"/>
-      <c r="F825" t="inlineStr"/>
       <c r="G825" t="inlineStr">
         <is>
           <t>100</t>
@@ -44150,8 +43322,6 @@
           <t>730.6634</t>
         </is>
       </c>
-      <c r="E826" t="inlineStr"/>
-      <c r="F826" t="inlineStr"/>
       <c r="G826" t="inlineStr">
         <is>
           <t>100</t>
@@ -44427,8 +43597,6 @@
           <t>732.875</t>
         </is>
       </c>
-      <c r="E831" t="inlineStr"/>
-      <c r="F831" t="inlineStr"/>
       <c r="G831" t="inlineStr">
         <is>
           <t>100</t>
@@ -44533,8 +43701,6 @@
           <t>732.56</t>
         </is>
       </c>
-      <c r="E833" t="inlineStr"/>
-      <c r="F833" t="inlineStr"/>
       <c r="G833" t="inlineStr">
         <is>
           <t>100</t>
@@ -44639,8 +43805,6 @@
           <t>728.0175</t>
         </is>
       </c>
-      <c r="E835" t="inlineStr"/>
-      <c r="F835" t="inlineStr"/>
       <c r="G835" t="inlineStr">
         <is>
           <t>100</t>
@@ -44688,8 +43852,6 @@
           <t>729.585</t>
         </is>
       </c>
-      <c r="E836" t="inlineStr"/>
-      <c r="F836" t="inlineStr"/>
       <c r="G836" t="inlineStr">
         <is>
           <t>100</t>
@@ -44851,8 +44013,6 @@
           <t>732.8499</t>
         </is>
       </c>
-      <c r="E839" t="inlineStr"/>
-      <c r="F839" t="inlineStr"/>
       <c r="G839" t="inlineStr">
         <is>
           <t>100</t>
@@ -44957,8 +44117,6 @@
           <t>734.0225</t>
         </is>
       </c>
-      <c r="E841" t="inlineStr"/>
-      <c r="F841" t="inlineStr"/>
       <c r="G841" t="inlineStr">
         <is>
           <t>100</t>
@@ -45063,8 +44221,6 @@
           <t>732.98</t>
         </is>
       </c>
-      <c r="E843" t="inlineStr"/>
-      <c r="F843" t="inlineStr"/>
       <c r="G843" t="inlineStr">
         <is>
           <t>100</t>
@@ -45169,8 +44325,6 @@
           <t>731.755</t>
         </is>
       </c>
-      <c r="E845" t="inlineStr"/>
-      <c r="F845" t="inlineStr"/>
       <c r="G845" t="inlineStr">
         <is>
           <t>100</t>
@@ -45275,8 +44429,6 @@
           <t>732.4999</t>
         </is>
       </c>
-      <c r="E847" t="inlineStr"/>
-      <c r="F847" t="inlineStr"/>
       <c r="G847" t="inlineStr">
         <is>
           <t>100</t>
@@ -45381,8 +44533,6 @@
           <t>732.93</t>
         </is>
       </c>
-      <c r="E849" t="inlineStr"/>
-      <c r="F849" t="inlineStr"/>
       <c r="G849" t="inlineStr">
         <is>
           <t>100</t>
@@ -45430,8 +44580,6 @@
           <t>732.53</t>
         </is>
       </c>
-      <c r="E850" t="inlineStr"/>
-      <c r="F850" t="inlineStr"/>
       <c r="G850" t="inlineStr">
         <is>
           <t>100</t>
@@ -45536,8 +44684,6 @@
           <t>732.845</t>
         </is>
       </c>
-      <c r="E852" t="inlineStr"/>
-      <c r="F852" t="inlineStr"/>
       <c r="G852" t="inlineStr">
         <is>
           <t>100</t>
@@ -45585,8 +44731,6 @@
           <t>731.76</t>
         </is>
       </c>
-      <c r="E853" t="inlineStr"/>
-      <c r="F853" t="inlineStr"/>
       <c r="G853" t="inlineStr">
         <is>
           <t>100</t>
@@ -45805,8 +44949,6 @@
           <t>738.375</t>
         </is>
       </c>
-      <c r="E857" t="inlineStr"/>
-      <c r="F857" t="inlineStr"/>
       <c r="G857" t="inlineStr">
         <is>
           <t>100</t>
@@ -45911,8 +45053,6 @@
           <t>736.0399</t>
         </is>
       </c>
-      <c r="E859" t="inlineStr"/>
-      <c r="F859" t="inlineStr"/>
       <c r="G859" t="inlineStr">
         <is>
           <t>100</t>
@@ -46017,8 +45157,6 @@
           <t>734.74</t>
         </is>
       </c>
-      <c r="E861" t="inlineStr"/>
-      <c r="F861" t="inlineStr"/>
       <c r="G861" t="inlineStr">
         <is>
           <t>100</t>
@@ -46066,8 +45204,6 @@
           <t>732.9499</t>
         </is>
       </c>
-      <c r="E862" t="inlineStr"/>
-      <c r="F862" t="inlineStr"/>
       <c r="G862" t="inlineStr">
         <is>
           <t>100</t>
@@ -46229,8 +45365,6 @@
           <t>737.3799</t>
         </is>
       </c>
-      <c r="E865" t="inlineStr"/>
-      <c r="F865" t="inlineStr"/>
       <c r="G865" t="inlineStr">
         <is>
           <t>100</t>
@@ -46335,8 +45469,6 @@
           <t>736.76</t>
         </is>
       </c>
-      <c r="E867" t="inlineStr"/>
-      <c r="F867" t="inlineStr"/>
       <c r="G867" t="inlineStr">
         <is>
           <t>100</t>
@@ -46441,8 +45573,6 @@
           <t>738.06</t>
         </is>
       </c>
-      <c r="E869" t="inlineStr"/>
-      <c r="F869" t="inlineStr"/>
       <c r="G869" t="inlineStr">
         <is>
           <t>100</t>
@@ -46547,8 +45677,6 @@
           <t>737.13</t>
         </is>
       </c>
-      <c r="E871" t="inlineStr"/>
-      <c r="F871" t="inlineStr"/>
       <c r="G871" t="inlineStr">
         <is>
           <t>100</t>
@@ -46653,8 +45781,6 @@
           <t>737.865</t>
         </is>
       </c>
-      <c r="E873" t="inlineStr"/>
-      <c r="F873" t="inlineStr"/>
       <c r="G873" t="inlineStr">
         <is>
           <t>100</t>
@@ -46759,8 +45885,6 @@
           <t>742.065</t>
         </is>
       </c>
-      <c r="E875" t="inlineStr"/>
-      <c r="F875" t="inlineStr"/>
       <c r="G875" t="inlineStr">
         <is>
           <t>100</t>
@@ -46865,8 +45989,6 @@
           <t>741.81</t>
         </is>
       </c>
-      <c r="E877" t="inlineStr"/>
-      <c r="F877" t="inlineStr"/>
       <c r="G877" t="inlineStr">
         <is>
           <t>100</t>
@@ -46971,8 +46093,6 @@
           <t>742.815</t>
         </is>
       </c>
-      <c r="E879" t="inlineStr"/>
-      <c r="F879" t="inlineStr"/>
       <c r="G879" t="inlineStr">
         <is>
           <t>100</t>
@@ -47077,8 +46197,6 @@
           <t>743.555</t>
         </is>
       </c>
-      <c r="E881" t="inlineStr"/>
-      <c r="F881" t="inlineStr"/>
       <c r="G881" t="inlineStr">
         <is>
           <t>100</t>
@@ -47183,8 +46301,6 @@
           <t>745.0083</t>
         </is>
       </c>
-      <c r="E883" t="inlineStr"/>
-      <c r="F883" t="inlineStr"/>
       <c r="G883" t="inlineStr">
         <is>
           <t>100</t>
@@ -47232,8 +46348,6 @@
           <t>744.425</t>
         </is>
       </c>
-      <c r="E884" t="inlineStr"/>
-      <c r="F884" t="inlineStr"/>
       <c r="G884" t="inlineStr">
         <is>
           <t>100</t>
@@ -47395,8 +46509,6 @@
           <t>743.54</t>
         </is>
       </c>
-      <c r="E887" t="inlineStr"/>
-      <c r="F887" t="inlineStr"/>
       <c r="G887" t="inlineStr">
         <is>
           <t>100</t>
@@ -47501,8 +46613,6 @@
           <t>746.38</t>
         </is>
       </c>
-      <c r="E889" t="inlineStr"/>
-      <c r="F889" t="inlineStr"/>
       <c r="G889" t="inlineStr">
         <is>
           <t>100</t>
@@ -47607,8 +46717,6 @@
           <t>746.8</t>
         </is>
       </c>
-      <c r="E891" t="inlineStr"/>
-      <c r="F891" t="inlineStr"/>
       <c r="G891" t="inlineStr">
         <is>
           <t>100</t>
@@ -47713,8 +46821,6 @@
           <t>746.37</t>
         </is>
       </c>
-      <c r="E893" t="inlineStr"/>
-      <c r="F893" t="inlineStr"/>
       <c r="G893" t="inlineStr">
         <is>
           <t>100</t>
@@ -47819,8 +46925,6 @@
           <t>747.7736</t>
         </is>
       </c>
-      <c r="E895" t="inlineStr"/>
-      <c r="F895" t="inlineStr"/>
       <c r="G895" t="inlineStr">
         <is>
           <t>100</t>
@@ -47925,8 +47029,6 @@
           <t>748.8</t>
         </is>
       </c>
-      <c r="E897" t="inlineStr"/>
-      <c r="F897" t="inlineStr"/>
       <c r="G897" t="inlineStr">
         <is>
           <t>100</t>
@@ -48031,8 +47133,6 @@
           <t>748.7</t>
         </is>
       </c>
-      <c r="E899" t="inlineStr"/>
-      <c r="F899" t="inlineStr"/>
       <c r="G899" t="inlineStr">
         <is>
           <t>100</t>
@@ -48080,8 +47180,6 @@
           <t>748.7779</t>
         </is>
       </c>
-      <c r="E900" t="inlineStr"/>
-      <c r="F900" t="inlineStr"/>
       <c r="G900" t="inlineStr">
         <is>
           <t>100</t>
@@ -48186,8 +47284,6 @@
           <t>748.458</t>
         </is>
       </c>
-      <c r="E902" t="inlineStr"/>
-      <c r="F902" t="inlineStr"/>
       <c r="G902" t="inlineStr">
         <is>
           <t>100</t>
@@ -48349,8 +47445,6 @@
           <t>750.84</t>
         </is>
       </c>
-      <c r="E905" t="inlineStr"/>
-      <c r="F905" t="inlineStr"/>
       <c r="G905" t="inlineStr">
         <is>
           <t>100</t>
@@ -48455,8 +47549,6 @@
           <t>750.5294</t>
         </is>
       </c>
-      <c r="E907" t="inlineStr"/>
-      <c r="F907" t="inlineStr"/>
       <c r="G907" t="inlineStr">
         <is>
           <t>100</t>
@@ -48561,8 +47653,6 @@
           <t>750.74</t>
         </is>
       </c>
-      <c r="E909" t="inlineStr"/>
-      <c r="F909" t="inlineStr"/>
       <c r="G909" t="inlineStr">
         <is>
           <t>100</t>
@@ -48667,8 +47757,6 @@
           <t>750.7267</t>
         </is>
       </c>
-      <c r="E911" t="inlineStr"/>
-      <c r="F911" t="inlineStr"/>
       <c r="G911" t="inlineStr">
         <is>
           <t>100</t>
@@ -48773,8 +47861,6 @@
           <t>748.39</t>
         </is>
       </c>
-      <c r="E913" t="inlineStr"/>
-      <c r="F913" t="inlineStr"/>
       <c r="G913" t="inlineStr">
         <is>
           <t>100</t>
@@ -48879,8 +47965,6 @@
           <t>746.77</t>
         </is>
       </c>
-      <c r="E915" t="inlineStr"/>
-      <c r="F915" t="inlineStr"/>
       <c r="G915" t="inlineStr">
         <is>
           <t>100</t>
@@ -48928,8 +48012,6 @@
           <t>746.35</t>
         </is>
       </c>
-      <c r="E916" t="inlineStr"/>
-      <c r="F916" t="inlineStr"/>
       <c r="G916" t="inlineStr">
         <is>
           <t>100</t>
@@ -49034,8 +48116,6 @@
           <t>746.2618</t>
         </is>
       </c>
-      <c r="E918" t="inlineStr"/>
-      <c r="F918" t="inlineStr"/>
       <c r="G918" t="inlineStr">
         <is>
           <t>100</t>
@@ -49083,8 +48163,6 @@
           <t>745.1999</t>
         </is>
       </c>
-      <c r="E919" t="inlineStr"/>
-      <c r="F919" t="inlineStr"/>
       <c r="G919" t="inlineStr">
         <is>
           <t>100</t>
@@ -49246,8 +48324,6 @@
           <t>744.745</t>
         </is>
       </c>
-      <c r="E922" t="inlineStr"/>
-      <c r="F922" t="inlineStr"/>
       <c r="G922" t="inlineStr">
         <is>
           <t>100</t>
@@ -49352,8 +48428,6 @@
           <t>745.945</t>
         </is>
       </c>
-      <c r="E924" t="inlineStr"/>
-      <c r="F924" t="inlineStr"/>
       <c r="G924" t="inlineStr">
         <is>
           <t>100</t>
@@ -49458,8 +48532,6 @@
           <t>744.5099</t>
         </is>
       </c>
-      <c r="E926" t="inlineStr"/>
-      <c r="F926" t="inlineStr"/>
       <c r="G926" t="inlineStr">
         <is>
           <t>100</t>
@@ -49564,8 +48636,6 @@
           <t>744.152</t>
         </is>
       </c>
-      <c r="E928" t="inlineStr"/>
-      <c r="F928" t="inlineStr"/>
       <c r="G928" t="inlineStr">
         <is>
           <t>100</t>
@@ -49670,8 +48740,6 @@
           <t>744.195</t>
         </is>
       </c>
-      <c r="E930" t="inlineStr"/>
-      <c r="F930" t="inlineStr"/>
       <c r="G930" t="inlineStr">
         <is>
           <t>100</t>
@@ -49776,8 +48844,6 @@
           <t>744.5569</t>
         </is>
       </c>
-      <c r="E932" t="inlineStr"/>
-      <c r="F932" t="inlineStr"/>
       <c r="G932" t="inlineStr">
         <is>
           <t>100</t>
@@ -49882,8 +48948,6 @@
           <t>742.7499</t>
         </is>
       </c>
-      <c r="E934" t="inlineStr"/>
-      <c r="F934" t="inlineStr"/>
       <c r="G934" t="inlineStr">
         <is>
           <t>100</t>
@@ -49988,8 +49052,6 @@
           <t>742.1479</t>
         </is>
       </c>
-      <c r="E936" t="inlineStr"/>
-      <c r="F936" t="inlineStr"/>
       <c r="G936" t="inlineStr">
         <is>
           <t>100</t>
@@ -50094,8 +49156,6 @@
           <t>741.66</t>
         </is>
       </c>
-      <c r="E938" t="inlineStr"/>
-      <c r="F938" t="inlineStr"/>
       <c r="G938" t="inlineStr">
         <is>
           <t>100</t>
@@ -50200,8 +49260,6 @@
           <t>740.926</t>
         </is>
       </c>
-      <c r="E940" t="inlineStr"/>
-      <c r="F940" t="inlineStr"/>
       <c r="G940" t="inlineStr">
         <is>
           <t>100</t>
@@ -50363,8 +49421,6 @@
           <t>740.5299</t>
         </is>
       </c>
-      <c r="E943" t="inlineStr"/>
-      <c r="F943" t="inlineStr"/>
       <c r="G943" t="inlineStr">
         <is>
           <t>100</t>
@@ -50469,8 +49525,6 @@
           <t>748.755</t>
         </is>
       </c>
-      <c r="E945" t="inlineStr"/>
-      <c r="F945" t="inlineStr"/>
       <c r="G945" t="inlineStr">
         <is>
           <t>100</t>
@@ -50575,8 +49629,6 @@
           <t>748.9628</t>
         </is>
       </c>
-      <c r="E947" t="inlineStr"/>
-      <c r="F947" t="inlineStr"/>
       <c r="G947" t="inlineStr">
         <is>
           <t>100</t>
@@ -50681,8 +49733,6 @@
           <t>749.6653</t>
         </is>
       </c>
-      <c r="E949" t="inlineStr"/>
-      <c r="F949" t="inlineStr"/>
       <c r="G949" t="inlineStr">
         <is>
           <t>100</t>
@@ -50787,8 +49837,6 @@
           <t>750.575</t>
         </is>
       </c>
-      <c r="E951" t="inlineStr"/>
-      <c r="F951" t="inlineStr"/>
       <c r="G951" t="inlineStr">
         <is>
           <t>100</t>
@@ -50836,8 +49884,6 @@
           <t>750.665</t>
         </is>
       </c>
-      <c r="E952" t="inlineStr"/>
-      <c r="F952" t="inlineStr"/>
       <c r="G952" t="inlineStr">
         <is>
           <t>100</t>
@@ -50942,8 +49988,6 @@
           <t>750.66</t>
         </is>
       </c>
-      <c r="E954" t="inlineStr"/>
-      <c r="F954" t="inlineStr"/>
       <c r="G954" t="inlineStr">
         <is>
           <t>100</t>
@@ -51048,8 +50092,6 @@
           <t>750.695</t>
         </is>
       </c>
-      <c r="E956" t="inlineStr"/>
-      <c r="F956" t="inlineStr"/>
       <c r="G956" t="inlineStr">
         <is>
           <t>100</t>
@@ -51211,8 +50253,6 @@
           <t>750.62</t>
         </is>
       </c>
-      <c r="E959" t="inlineStr"/>
-      <c r="F959" t="inlineStr"/>
       <c r="G959" t="inlineStr">
         <is>
           <t>100</t>
@@ -51317,8 +50357,6 @@
           <t>749.62</t>
         </is>
       </c>
-      <c r="E961" t="inlineStr"/>
-      <c r="F961" t="inlineStr"/>
       <c r="G961" t="inlineStr">
         <is>
           <t>100</t>
@@ -51423,8 +50461,6 @@
           <t>748.745</t>
         </is>
       </c>
-      <c r="E963" t="inlineStr"/>
-      <c r="F963" t="inlineStr"/>
       <c r="G963" t="inlineStr">
         <is>
           <t>100</t>
@@ -51529,8 +50565,6 @@
           <t>746.78</t>
         </is>
       </c>
-      <c r="E965" t="inlineStr"/>
-      <c r="F965" t="inlineStr"/>
       <c r="G965" t="inlineStr">
         <is>
           <t>100</t>
@@ -51635,8 +50669,6 @@
           <t>747.15</t>
         </is>
       </c>
-      <c r="E967" t="inlineStr"/>
-      <c r="F967" t="inlineStr"/>
       <c r="G967" t="inlineStr">
         <is>
           <t>100</t>
@@ -51741,8 +50773,6 @@
           <t>746.305</t>
         </is>
       </c>
-      <c r="E969" t="inlineStr"/>
-      <c r="F969" t="inlineStr"/>
       <c r="G969" t="inlineStr">
         <is>
           <t>100</t>
@@ -51847,8 +50877,6 @@
           <t>746.5925</t>
         </is>
       </c>
-      <c r="E971" t="inlineStr"/>
-      <c r="F971" t="inlineStr"/>
       <c r="G971" t="inlineStr">
         <is>
           <t>100</t>
@@ -51953,8 +50981,6 @@
           <t>746.59</t>
         </is>
       </c>
-      <c r="E973" t="inlineStr"/>
-      <c r="F973" t="inlineStr"/>
       <c r="G973" t="inlineStr">
         <is>
           <t>100</t>
@@ -52059,8 +51085,6 @@
           <t>745.8758</t>
         </is>
       </c>
-      <c r="E975" t="inlineStr"/>
-      <c r="F975" t="inlineStr"/>
       <c r="G975" t="inlineStr">
         <is>
           <t>100</t>
@@ -52165,8 +51189,6 @@
           <t>746.035</t>
         </is>
       </c>
-      <c r="E977" t="inlineStr"/>
-      <c r="F977" t="inlineStr"/>
       <c r="G977" t="inlineStr">
         <is>
           <t>100</t>
@@ -52271,8 +51293,6 @@
           <t>748.7361</t>
         </is>
       </c>
-      <c r="E979" t="inlineStr"/>
-      <c r="F979" t="inlineStr"/>
       <c r="G979" t="inlineStr">
         <is>
           <t>100</t>
@@ -52377,8 +51397,6 @@
           <t>748.92</t>
         </is>
       </c>
-      <c r="E981" t="inlineStr"/>
-      <c r="F981" t="inlineStr"/>
       <c r="G981" t="inlineStr">
         <is>
           <t>100</t>
@@ -52483,8 +51501,6 @@
           <t>743.435</t>
         </is>
       </c>
-      <c r="E983" t="inlineStr"/>
-      <c r="F983" t="inlineStr"/>
       <c r="G983" t="inlineStr">
         <is>
           <t>100</t>
@@ -52589,8 +51605,6 @@
           <t>743.965</t>
         </is>
       </c>
-      <c r="E985" t="inlineStr"/>
-      <c r="F985" t="inlineStr"/>
       <c r="G985" t="inlineStr">
         <is>
           <t>100</t>
@@ -52695,8 +51709,6 @@
           <t>743.705</t>
         </is>
       </c>
-      <c r="E987" t="inlineStr"/>
-      <c r="F987" t="inlineStr"/>
       <c r="G987" t="inlineStr">
         <is>
           <t>100</t>
@@ -52801,8 +51813,6 @@
           <t>742.45</t>
         </is>
       </c>
-      <c r="E989" t="inlineStr"/>
-      <c r="F989" t="inlineStr"/>
       <c r="G989" t="inlineStr">
         <is>
           <t>100</t>
@@ -52907,8 +51917,6 @@
           <t>741.415</t>
         </is>
       </c>
-      <c r="E991" t="inlineStr"/>
-      <c r="F991" t="inlineStr"/>
       <c r="G991" t="inlineStr">
         <is>
           <t>100</t>
@@ -52956,8 +51964,6 @@
           <t>741.3199</t>
         </is>
       </c>
-      <c r="E992" t="inlineStr"/>
-      <c r="F992" t="inlineStr"/>
       <c r="G992" t="inlineStr">
         <is>
           <t>100</t>
@@ -53119,8 +52125,6 @@
           <t>740.335</t>
         </is>
       </c>
-      <c r="E995" t="inlineStr"/>
-      <c r="F995" t="inlineStr"/>
       <c r="G995" t="inlineStr">
         <is>
           <t>100</t>
@@ -53225,8 +52229,6 @@
           <t>740.255</t>
         </is>
       </c>
-      <c r="E997" t="inlineStr"/>
-      <c r="F997" t="inlineStr"/>
       <c r="G997" t="inlineStr">
         <is>
           <t>100</t>
@@ -53331,8 +52333,6 @@
           <t>742.229</t>
         </is>
       </c>
-      <c r="E999" t="inlineStr"/>
-      <c r="F999" t="inlineStr"/>
       <c r="G999" t="inlineStr">
         <is>
           <t>100</t>
@@ -53437,8 +52437,6 @@
           <t>748.0951</t>
         </is>
       </c>
-      <c r="E1001" t="inlineStr"/>
-      <c r="F1001" t="inlineStr"/>
       <c r="G1001" t="inlineStr">
         <is>
           <t>100</t>
@@ -53543,8 +52541,6 @@
           <t>748.885</t>
         </is>
       </c>
-      <c r="E1003" t="inlineStr"/>
-      <c r="F1003" t="inlineStr"/>
       <c r="G1003" t="inlineStr">
         <is>
           <t>100</t>
@@ -53649,8 +52645,6 @@
           <t>748.7319</t>
         </is>
       </c>
-      <c r="E1005" t="inlineStr"/>
-      <c r="F1005" t="inlineStr"/>
       <c r="G1005" t="inlineStr">
         <is>
           <t>100</t>
@@ -53755,8 +52749,6 @@
           <t>747.68</t>
         </is>
       </c>
-      <c r="E1007" t="inlineStr"/>
-      <c r="F1007" t="inlineStr"/>
       <c r="G1007" t="inlineStr">
         <is>
           <t>100</t>
@@ -53861,8 +52853,6 @@
           <t>748.115</t>
         </is>
       </c>
-      <c r="E1009" t="inlineStr"/>
-      <c r="F1009" t="inlineStr"/>
       <c r="G1009" t="inlineStr">
         <is>
           <t>100</t>
@@ -53967,8 +52957,6 @@
           <t>748.345</t>
         </is>
       </c>
-      <c r="E1011" t="inlineStr"/>
-      <c r="F1011" t="inlineStr"/>
       <c r="G1011" t="inlineStr">
         <is>
           <t>100</t>
@@ -54073,8 +53061,6 @@
           <t>748.6766</t>
         </is>
       </c>
-      <c r="E1013" t="inlineStr"/>
-      <c r="F1013" t="inlineStr"/>
       <c r="G1013" t="inlineStr">
         <is>
           <t>100</t>
@@ -54179,8 +53165,6 @@
           <t>749.38</t>
         </is>
       </c>
-      <c r="E1015" t="inlineStr"/>
-      <c r="F1015" t="inlineStr"/>
       <c r="G1015" t="inlineStr">
         <is>
           <t>100</t>
@@ -54228,8 +53212,6 @@
           <t>749.19</t>
         </is>
       </c>
-      <c r="E1016" t="inlineStr"/>
-      <c r="F1016" t="inlineStr"/>
       <c r="G1016" t="inlineStr">
         <is>
           <t>100</t>
@@ -54391,8 +53373,6 @@
           <t>749.57</t>
         </is>
       </c>
-      <c r="E1019" t="inlineStr"/>
-      <c r="F1019" t="inlineStr"/>
       <c r="G1019" t="inlineStr">
         <is>
           <t>100</t>
@@ -54497,8 +53477,6 @@
           <t>750.7382</t>
         </is>
       </c>
-      <c r="E1021" t="inlineStr"/>
-      <c r="F1021" t="inlineStr"/>
       <c r="G1021" t="inlineStr">
         <is>
           <t>100</t>
@@ -54603,8 +53581,6 @@
           <t>751.3328</t>
         </is>
       </c>
-      <c r="E1023" t="inlineStr"/>
-      <c r="F1023" t="inlineStr"/>
       <c r="G1023" t="inlineStr">
         <is>
           <t>100</t>
@@ -54766,8 +53742,6 @@
           <t>751.935</t>
         </is>
       </c>
-      <c r="E1026" t="inlineStr"/>
-      <c r="F1026" t="inlineStr"/>
       <c r="G1026" t="inlineStr">
         <is>
           <t>100</t>
@@ -54872,8 +53846,6 @@
           <t>752.8452</t>
         </is>
       </c>
-      <c r="E1028" t="inlineStr"/>
-      <c r="F1028" t="inlineStr"/>
       <c r="G1028" t="inlineStr">
         <is>
           <t>100</t>
@@ -54978,8 +53950,6 @@
           <t>753.07</t>
         </is>
       </c>
-      <c r="E1030" t="inlineStr"/>
-      <c r="F1030" t="inlineStr"/>
       <c r="G1030" t="inlineStr">
         <is>
           <t>100</t>
@@ -55084,8 +54054,6 @@
           <t>752.77</t>
         </is>
       </c>
-      <c r="E1032" t="inlineStr"/>
-      <c r="F1032" t="inlineStr"/>
       <c r="G1032" t="inlineStr">
         <is>
           <t>100</t>
@@ -55190,8 +54158,6 @@
           <t>751.93</t>
         </is>
       </c>
-      <c r="E1034" t="inlineStr"/>
-      <c r="F1034" t="inlineStr"/>
       <c r="G1034" t="inlineStr">
         <is>
           <t>100</t>
@@ -55296,8 +54262,6 @@
           <t>751.89</t>
         </is>
       </c>
-      <c r="E1036" t="inlineStr"/>
-      <c r="F1036" t="inlineStr"/>
       <c r="G1036" t="inlineStr">
         <is>
           <t>100</t>
@@ -55402,8 +54366,6 @@
           <t>752.12</t>
         </is>
       </c>
-      <c r="E1038" t="inlineStr"/>
-      <c r="F1038" t="inlineStr"/>
       <c r="G1038" t="inlineStr">
         <is>
           <t>100</t>
@@ -55508,8 +54470,6 @@
           <t>751.49</t>
         </is>
       </c>
-      <c r="E1040" t="inlineStr"/>
-      <c r="F1040" t="inlineStr"/>
       <c r="G1040" t="inlineStr">
         <is>
           <t>100</t>
@@ -55614,8 +54574,6 @@
           <t>750.4559</t>
         </is>
       </c>
-      <c r="E1042" t="inlineStr"/>
-      <c r="F1042" t="inlineStr"/>
       <c r="G1042" t="inlineStr">
         <is>
           <t>100</t>
@@ -55720,8 +54678,6 @@
           <t>750.17</t>
         </is>
       </c>
-      <c r="E1044" t="inlineStr"/>
-      <c r="F1044" t="inlineStr"/>
       <c r="G1044" t="inlineStr">
         <is>
           <t>100</t>
@@ -55826,8 +54782,6 @@
           <t>749.9307</t>
         </is>
       </c>
-      <c r="E1046" t="inlineStr"/>
-      <c r="F1046" t="inlineStr"/>
       <c r="G1046" t="inlineStr">
         <is>
           <t>100</t>
@@ -55932,8 +54886,6 @@
           <t>751.32</t>
         </is>
       </c>
-      <c r="E1048" t="inlineStr"/>
-      <c r="F1048" t="inlineStr"/>
       <c r="G1048" t="inlineStr">
         <is>
           <t>100</t>
@@ -56038,8 +54990,6 @@
           <t>750.1651</t>
         </is>
       </c>
-      <c r="E1050" t="inlineStr"/>
-      <c r="F1050" t="inlineStr"/>
       <c r="G1050" t="inlineStr">
         <is>
           <t>100</t>
@@ -56144,8 +55094,6 @@
           <t>752.0006</t>
         </is>
       </c>
-      <c r="E1052" t="inlineStr"/>
-      <c r="F1052" t="inlineStr"/>
       <c r="G1052" t="inlineStr">
         <is>
           <t>100</t>
@@ -56250,8 +55198,6 @@
           <t>751.42</t>
         </is>
       </c>
-      <c r="E1054" t="inlineStr"/>
-      <c r="F1054" t="inlineStr"/>
       <c r="G1054" t="inlineStr">
         <is>
           <t>100</t>
@@ -56356,8 +55302,6 @@
           <t>751.529</t>
         </is>
       </c>
-      <c r="E1056" t="inlineStr"/>
-      <c r="F1056" t="inlineStr"/>
       <c r="G1056" t="inlineStr">
         <is>
           <t>100</t>
@@ -56462,8 +55406,6 @@
           <t>754.8348</t>
         </is>
       </c>
-      <c r="E1058" t="inlineStr"/>
-      <c r="F1058" t="inlineStr"/>
       <c r="G1058" t="inlineStr">
         <is>
           <t>100</t>
@@ -56511,8 +55453,6 @@
           <t>753.74</t>
         </is>
       </c>
-      <c r="E1059" t="inlineStr"/>
-      <c r="F1059" t="inlineStr"/>
       <c r="G1059" t="inlineStr">
         <is>
           <t>100</t>
@@ -56617,8 +55557,6 @@
           <t>753.7177</t>
         </is>
       </c>
-      <c r="E1061" t="inlineStr"/>
-      <c r="F1061" t="inlineStr"/>
       <c r="G1061" t="inlineStr">
         <is>
           <t>100</t>
@@ -56780,8 +55718,6 @@
           <t>753.17</t>
         </is>
       </c>
-      <c r="E1064" t="inlineStr"/>
-      <c r="F1064" t="inlineStr"/>
       <c r="G1064" t="inlineStr">
         <is>
           <t>100</t>
@@ -56886,8 +55822,6 @@
           <t>753.4467</t>
         </is>
       </c>
-      <c r="E1066" t="inlineStr"/>
-      <c r="F1066" t="inlineStr"/>
       <c r="G1066" t="inlineStr">
         <is>
           <t>100</t>
@@ -56992,8 +55926,6 @@
           <t>752.98</t>
         </is>
       </c>
-      <c r="E1068" t="inlineStr"/>
-      <c r="F1068" t="inlineStr"/>
       <c r="G1068" t="inlineStr">
         <is>
           <t>100</t>
@@ -57098,8 +56030,6 @@
           <t>753.409</t>
         </is>
       </c>
-      <c r="E1070" t="inlineStr"/>
-      <c r="F1070" t="inlineStr"/>
       <c r="G1070" t="inlineStr">
         <is>
           <t>100</t>
@@ -57204,8 +56134,6 @@
           <t>751.495</t>
         </is>
       </c>
-      <c r="E1072" t="inlineStr"/>
-      <c r="F1072" t="inlineStr"/>
       <c r="G1072" t="inlineStr">
         <is>
           <t>100</t>
@@ -57310,8 +56238,6 @@
           <t>751.865</t>
         </is>
       </c>
-      <c r="E1074" t="inlineStr"/>
-      <c r="F1074" t="inlineStr"/>
       <c r="G1074" t="inlineStr">
         <is>
           <t>100</t>
@@ -57416,8 +56342,6 @@
           <t>751.69</t>
         </is>
       </c>
-      <c r="E1076" t="inlineStr"/>
-      <c r="F1076" t="inlineStr"/>
       <c r="G1076" t="inlineStr">
         <is>
           <t>100</t>
@@ -57522,8 +56446,6 @@
           <t>752.665</t>
         </is>
       </c>
-      <c r="E1078" t="inlineStr"/>
-      <c r="F1078" t="inlineStr"/>
       <c r="G1078" t="inlineStr">
         <is>
           <t>100</t>
@@ -57628,8 +56550,6 @@
           <t>753.595</t>
         </is>
       </c>
-      <c r="E1080" t="inlineStr"/>
-      <c r="F1080" t="inlineStr"/>
       <c r="G1080" t="inlineStr">
         <is>
           <t>100</t>
@@ -57734,8 +56654,6 @@
           <t>753.7598</t>
         </is>
       </c>
-      <c r="E1082" t="inlineStr"/>
-      <c r="F1082" t="inlineStr"/>
       <c r="G1082" t="inlineStr">
         <is>
           <t>100</t>
@@ -57840,8 +56758,6 @@
           <t>753.44</t>
         </is>
       </c>
-      <c r="E1084" t="inlineStr"/>
-      <c r="F1084" t="inlineStr"/>
       <c r="G1084" t="inlineStr">
         <is>
           <t>100</t>
@@ -57946,8 +56862,6 @@
           <t>753.405</t>
         </is>
       </c>
-      <c r="E1086" t="inlineStr"/>
-      <c r="F1086" t="inlineStr"/>
       <c r="G1086" t="inlineStr">
         <is>
           <t>100</t>
@@ -57995,8 +56909,6 @@
           <t>753.2393</t>
         </is>
       </c>
-      <c r="E1087" t="inlineStr"/>
-      <c r="F1087" t="inlineStr"/>
       <c r="G1087" t="inlineStr">
         <is>
           <t>100</t>
@@ -58158,8 +57070,6 @@
           <t>753.3</t>
         </is>
       </c>
-      <c r="E1090" t="inlineStr"/>
-      <c r="F1090" t="inlineStr"/>
       <c r="G1090" t="inlineStr">
         <is>
           <t>100</t>
@@ -58264,8 +57174,6 @@
           <t>753.4213</t>
         </is>
       </c>
-      <c r="E1092" t="inlineStr"/>
-      <c r="F1092" t="inlineStr"/>
       <c r="G1092" t="inlineStr">
         <is>
           <t>100</t>
@@ -58370,8 +57278,6 @@
           <t>753.5757</t>
         </is>
       </c>
-      <c r="E1094" t="inlineStr"/>
-      <c r="F1094" t="inlineStr"/>
       <c r="G1094" t="inlineStr">
         <is>
           <t>100</t>
@@ -58476,8 +57382,6 @@
           <t>753.602</t>
         </is>
       </c>
-      <c r="E1096" t="inlineStr"/>
-      <c r="F1096" t="inlineStr"/>
       <c r="G1096" t="inlineStr">
         <is>
           <t>100</t>
@@ -58525,8 +57429,6 @@
           <t>751.705</t>
         </is>
       </c>
-      <c r="E1097" t="inlineStr"/>
-      <c r="F1097" t="inlineStr"/>
       <c r="G1097" t="inlineStr">
         <is>
           <t>100</t>
@@ -58574,8 +57476,6 @@
           <t>751.5069</t>
         </is>
       </c>
-      <c r="E1098" t="inlineStr"/>
-      <c r="F1098" t="inlineStr"/>
       <c r="G1098" t="inlineStr">
         <is>
           <t>100</t>
@@ -58737,8 +57637,6 @@
           <t>749.06</t>
         </is>
       </c>
-      <c r="E1101" t="inlineStr"/>
-      <c r="F1101" t="inlineStr"/>
       <c r="G1101" t="inlineStr">
         <is>
           <t>100</t>
@@ -58843,8 +57741,6 @@
           <t>748.7699</t>
         </is>
       </c>
-      <c r="E1103" t="inlineStr"/>
-      <c r="F1103" t="inlineStr"/>
       <c r="G1103" t="inlineStr">
         <is>
           <t>100</t>
@@ -58949,8 +57845,6 @@
           <t>748.6793</t>
         </is>
       </c>
-      <c r="E1105" t="inlineStr"/>
-      <c r="F1105" t="inlineStr"/>
       <c r="G1105" t="inlineStr">
         <is>
           <t>100</t>
@@ -59055,8 +57949,6 @@
           <t>744.04</t>
         </is>
       </c>
-      <c r="E1107" t="inlineStr"/>
-      <c r="F1107" t="inlineStr"/>
       <c r="G1107" t="inlineStr">
         <is>
           <t>100</t>
@@ -59161,8 +58053,6 @@
           <t>744.805</t>
         </is>
       </c>
-      <c r="E1109" t="inlineStr"/>
-      <c r="F1109" t="inlineStr"/>
       <c r="G1109" t="inlineStr">
         <is>
           <t>100</t>
@@ -59267,8 +58157,6 @@
           <t>745.95</t>
         </is>
       </c>
-      <c r="E1111" t="inlineStr"/>
-      <c r="F1111" t="inlineStr"/>
       <c r="G1111" t="inlineStr">
         <is>
           <t>100</t>
@@ -59373,8 +58261,6 @@
           <t>746.57</t>
         </is>
       </c>
-      <c r="E1113" t="inlineStr"/>
-      <c r="F1113" t="inlineStr"/>
       <c r="G1113" t="inlineStr">
         <is>
           <t>100</t>
@@ -59479,8 +58365,6 @@
           <t>745.7995</t>
         </is>
       </c>
-      <c r="E1115" t="inlineStr"/>
-      <c r="F1115" t="inlineStr"/>
       <c r="G1115" t="inlineStr">
         <is>
           <t>100</t>
@@ -59528,8 +58412,6 @@
           <t>744.215</t>
         </is>
       </c>
-      <c r="E1116" t="inlineStr"/>
-      <c r="F1116" t="inlineStr"/>
       <c r="G1116" t="inlineStr">
         <is>
           <t>100</t>
@@ -59691,8 +58573,6 @@
           <t>744.1341</t>
         </is>
       </c>
-      <c r="E1119" t="inlineStr"/>
-      <c r="F1119" t="inlineStr"/>
       <c r="G1119" t="inlineStr">
         <is>
           <t>100</t>
@@ -59740,8 +58620,6 @@
           <t>744.4154</t>
         </is>
       </c>
-      <c r="E1120" t="inlineStr"/>
-      <c r="F1120" t="inlineStr"/>
       <c r="G1120" t="inlineStr">
         <is>
           <t>100</t>
@@ -59903,8 +58781,6 @@
           <t>744.92</t>
         </is>
       </c>
-      <c r="E1123" t="inlineStr"/>
-      <c r="F1123" t="inlineStr"/>
       <c r="G1123" t="inlineStr">
         <is>
           <t>100</t>
@@ -60009,8 +58885,6 @@
           <t>745.035</t>
         </is>
       </c>
-      <c r="E1125" t="inlineStr"/>
-      <c r="F1125" t="inlineStr"/>
       <c r="G1125" t="inlineStr">
         <is>
           <t>100</t>
@@ -60115,8 +58989,6 @@
           <t>745.37</t>
         </is>
       </c>
-      <c r="E1127" t="inlineStr"/>
-      <c r="F1127" t="inlineStr"/>
       <c r="G1127" t="inlineStr">
         <is>
           <t>100</t>
@@ -60221,8 +59093,6 @@
           <t>745.435</t>
         </is>
       </c>
-      <c r="E1129" t="inlineStr"/>
-      <c r="F1129" t="inlineStr"/>
       <c r="G1129" t="inlineStr">
         <is>
           <t>100</t>
@@ -60327,8 +59197,6 @@
           <t>746.0299</t>
         </is>
       </c>
-      <c r="E1131" t="inlineStr"/>
-      <c r="F1131" t="inlineStr"/>
       <c r="G1131" t="inlineStr">
         <is>
           <t>100</t>
@@ -60433,8 +59301,6 @@
           <t>746.2792</t>
         </is>
       </c>
-      <c r="E1133" t="inlineStr"/>
-      <c r="F1133" t="inlineStr"/>
       <c r="G1133" t="inlineStr">
         <is>
           <t>100</t>
@@ -60539,8 +59405,6 @@
           <t>746.98</t>
         </is>
       </c>
-      <c r="E1135" t="inlineStr"/>
-      <c r="F1135" t="inlineStr"/>
       <c r="G1135" t="inlineStr">
         <is>
           <t>100</t>
@@ -60588,8 +59452,6 @@
           <t>746.8623</t>
         </is>
       </c>
-      <c r="E1136" t="inlineStr"/>
-      <c r="F1136" t="inlineStr"/>
       <c r="G1136" t="inlineStr">
         <is>
           <t>100</t>
@@ -60751,8 +59613,6 @@
           <t>745.5</t>
         </is>
       </c>
-      <c r="E1139" t="inlineStr"/>
-      <c r="F1139" t="inlineStr"/>
       <c r="G1139" t="inlineStr">
         <is>
           <t>100</t>
@@ -60857,8 +59717,6 @@
           <t>748.505</t>
         </is>
       </c>
-      <c r="E1141" t="inlineStr"/>
-      <c r="F1141" t="inlineStr"/>
       <c r="G1141" t="inlineStr">
         <is>
           <t>100</t>
@@ -60963,8 +59821,6 @@
           <t>746.606</t>
         </is>
       </c>
-      <c r="E1143" t="inlineStr"/>
-      <c r="F1143" t="inlineStr"/>
       <c r="G1143" t="inlineStr">
         <is>
           <t>100</t>
@@ -61012,8 +59868,6 @@
           <t>745.395</t>
         </is>
       </c>
-      <c r="E1144" t="inlineStr"/>
-      <c r="F1144" t="inlineStr"/>
       <c r="G1144" t="inlineStr">
         <is>
           <t>100</t>
@@ -61118,8 +59972,6 @@
           <t>744.905</t>
         </is>
       </c>
-      <c r="E1146" t="inlineStr"/>
-      <c r="F1146" t="inlineStr"/>
       <c r="G1146" t="inlineStr">
         <is>
           <t>100</t>
@@ -61281,8 +60133,6 @@
           <t>744.8901</t>
         </is>
       </c>
-      <c r="E1149" t="inlineStr"/>
-      <c r="F1149" t="inlineStr"/>
       <c r="G1149" t="inlineStr">
         <is>
           <t>100</t>
@@ -61387,8 +60237,6 @@
           <t>744.5</t>
         </is>
       </c>
-      <c r="E1151" t="inlineStr"/>
-      <c r="F1151" t="inlineStr"/>
       <c r="G1151" t="inlineStr">
         <is>
           <t>100</t>
@@ -61493,8 +60341,6 @@
           <t>744.8336</t>
         </is>
       </c>
-      <c r="E1153" t="inlineStr"/>
-      <c r="F1153" t="inlineStr"/>
       <c r="G1153" t="inlineStr">
         <is>
           <t>100</t>
@@ -61599,8 +60445,6 @@
           <t>745.0645</t>
         </is>
       </c>
-      <c r="E1155" t="inlineStr"/>
-      <c r="F1155" t="inlineStr"/>
       <c r="G1155" t="inlineStr">
         <is>
           <t>100</t>
@@ -61705,8 +60549,6 @@
           <t>745.7</t>
         </is>
       </c>
-      <c r="E1157" t="inlineStr"/>
-      <c r="F1157" t="inlineStr"/>
       <c r="G1157" t="inlineStr">
         <is>
           <t>100</t>
@@ -61811,8 +60653,6 @@
           <t>745.0115</t>
         </is>
       </c>
-      <c r="E1159" t="inlineStr"/>
-      <c r="F1159" t="inlineStr"/>
       <c r="G1159" t="inlineStr">
         <is>
           <t>100</t>
@@ -61917,8 +60757,6 @@
           <t>746.5501</t>
         </is>
       </c>
-      <c r="E1161" t="inlineStr"/>
-      <c r="F1161" t="inlineStr"/>
       <c r="G1161" t="inlineStr">
         <is>
           <t>100</t>
@@ -62023,8 +60861,6 @@
           <t>746.735</t>
         </is>
       </c>
-      <c r="E1163" t="inlineStr"/>
-      <c r="F1163" t="inlineStr"/>
       <c r="G1163" t="inlineStr">
         <is>
           <t>100</t>
@@ -62129,8 +60965,6 @@
           <t>746.49</t>
         </is>
       </c>
-      <c r="E1165" t="inlineStr"/>
-      <c r="F1165" t="inlineStr"/>
       <c r="G1165" t="inlineStr">
         <is>
           <t>100</t>
@@ -62235,8 +61069,6 @@
           <t>747.5788</t>
         </is>
       </c>
-      <c r="E1167" t="inlineStr"/>
-      <c r="F1167" t="inlineStr"/>
       <c r="G1167" t="inlineStr">
         <is>
           <t>100</t>
@@ -62341,8 +61173,6 @@
           <t>747.695</t>
         </is>
       </c>
-      <c r="E1169" t="inlineStr"/>
-      <c r="F1169" t="inlineStr"/>
       <c r="G1169" t="inlineStr">
         <is>
           <t>100</t>
@@ -62447,8 +61277,6 @@
           <t>749.0341</t>
         </is>
       </c>
-      <c r="E1171" t="inlineStr"/>
-      <c r="F1171" t="inlineStr"/>
       <c r="G1171" t="inlineStr">
         <is>
           <t>100</t>
@@ -62553,8 +61381,6 @@
           <t>747.71</t>
         </is>
       </c>
-      <c r="E1173" t="inlineStr"/>
-      <c r="F1173" t="inlineStr"/>
       <c r="G1173" t="inlineStr">
         <is>
           <t>100</t>
@@ -62659,8 +61485,6 @@
           <t>747.25</t>
         </is>
       </c>
-      <c r="E1175" t="inlineStr"/>
-      <c r="F1175" t="inlineStr"/>
       <c r="G1175" t="inlineStr">
         <is>
           <t>100</t>
@@ -62765,8 +61589,6 @@
           <t>747.285</t>
         </is>
       </c>
-      <c r="E1177" t="inlineStr"/>
-      <c r="F1177" t="inlineStr"/>
       <c r="G1177" t="inlineStr">
         <is>
           <t>100</t>
@@ -62871,8 +61693,6 @@
           <t>747.435</t>
         </is>
       </c>
-      <c r="E1179" t="inlineStr"/>
-      <c r="F1179" t="inlineStr"/>
       <c r="G1179" t="inlineStr">
         <is>
           <t>100</t>
@@ -62920,8 +61740,6 @@
           <t>748.4838</t>
         </is>
       </c>
-      <c r="E1180" t="inlineStr"/>
-      <c r="F1180" t="inlineStr"/>
       <c r="G1180" t="inlineStr">
         <is>
           <t>100</t>
@@ -63026,8 +61844,6 @@
           <t>749.58</t>
         </is>
       </c>
-      <c r="E1182" t="inlineStr"/>
-      <c r="F1182" t="inlineStr"/>
       <c r="G1182" t="inlineStr">
         <is>
           <t>100</t>
@@ -63189,8 +62005,6 @@
           <t>749.32</t>
         </is>
       </c>
-      <c r="E1185" t="inlineStr"/>
-      <c r="F1185" t="inlineStr"/>
       <c r="G1185" t="inlineStr">
         <is>
           <t>100</t>
@@ -63295,8 +62109,6 @@
           <t>749.32</t>
         </is>
       </c>
-      <c r="E1187" t="inlineStr"/>
-      <c r="F1187" t="inlineStr"/>
       <c r="G1187" t="inlineStr">
         <is>
           <t>100</t>
@@ -63401,8 +62213,6 @@
           <t>749.71</t>
         </is>
       </c>
-      <c r="E1189" t="inlineStr"/>
-      <c r="F1189" t="inlineStr"/>
       <c r="G1189" t="inlineStr">
         <is>
           <t>100</t>
@@ -63507,8 +62317,6 @@
           <t>740.05</t>
         </is>
       </c>
-      <c r="E1191" t="inlineStr"/>
-      <c r="F1191" t="inlineStr"/>
       <c r="G1191" t="inlineStr">
         <is>
           <t>100</t>
@@ -63613,8 +62421,6 @@
           <t>740.585</t>
         </is>
       </c>
-      <c r="E1193" t="inlineStr"/>
-      <c r="F1193" t="inlineStr"/>
       <c r="G1193" t="inlineStr">
         <is>
           <t>100</t>
@@ -63719,8 +62525,6 @@
           <t>740.065</t>
         </is>
       </c>
-      <c r="E1195" t="inlineStr"/>
-      <c r="F1195" t="inlineStr"/>
       <c r="G1195" t="inlineStr">
         <is>
           <t>100</t>
@@ -63768,8 +62572,6 @@
           <t>739.455</t>
         </is>
       </c>
-      <c r="E1196" t="inlineStr"/>
-      <c r="F1196" t="inlineStr"/>
       <c r="G1196" t="inlineStr">
         <is>
           <t>100</t>
@@ -63931,8 +62733,6 @@
           <t>739.6812</t>
         </is>
       </c>
-      <c r="E1199" t="inlineStr"/>
-      <c r="F1199" t="inlineStr"/>
       <c r="G1199" t="inlineStr">
         <is>
           <t>100</t>
@@ -63980,8 +62780,6 @@
           <t>740.315</t>
         </is>
       </c>
-      <c r="E1200" t="inlineStr"/>
-      <c r="F1200" t="inlineStr"/>
       <c r="G1200" t="inlineStr">
         <is>
           <t>100</t>
@@ -64143,8 +62941,6 @@
           <t>736.47</t>
         </is>
       </c>
-      <c r="E1203" t="inlineStr"/>
-      <c r="F1203" t="inlineStr"/>
       <c r="G1203" t="inlineStr">
         <is>
           <t>100</t>
@@ -64249,8 +63045,6 @@
           <t>736.55</t>
         </is>
       </c>
-      <c r="E1205" t="inlineStr"/>
-      <c r="F1205" t="inlineStr"/>
       <c r="G1205" t="inlineStr">
         <is>
           <t>100</t>
@@ -64355,8 +63149,6 @@
           <t>738.825</t>
         </is>
       </c>
-      <c r="E1207" t="inlineStr"/>
-      <c r="F1207" t="inlineStr"/>
       <c r="G1207" t="inlineStr">
         <is>
           <t>100</t>
@@ -64461,8 +63253,6 @@
           <t>739.7</t>
         </is>
       </c>
-      <c r="E1209" t="inlineStr"/>
-      <c r="F1209" t="inlineStr"/>
       <c r="G1209" t="inlineStr">
         <is>
           <t>100</t>
@@ -64567,8 +63357,6 @@
           <t>737.965</t>
         </is>
       </c>
-      <c r="E1211" t="inlineStr"/>
-      <c r="F1211" t="inlineStr"/>
       <c r="G1211" t="inlineStr">
         <is>
           <t>100</t>
@@ -64673,8 +63461,6 @@
           <t>738.82</t>
         </is>
       </c>
-      <c r="E1213" t="inlineStr"/>
-      <c r="F1213" t="inlineStr"/>
       <c r="G1213" t="inlineStr">
         <is>
           <t>100</t>
@@ -64779,8 +63565,6 @@
           <t>738.6999</t>
         </is>
       </c>
-      <c r="E1215" t="inlineStr"/>
-      <c r="F1215" t="inlineStr"/>
       <c r="G1215" t="inlineStr">
         <is>
           <t>100</t>
@@ -64885,8 +63669,6 @@
           <t>738.0432</t>
         </is>
       </c>
-      <c r="E1217" t="inlineStr"/>
-      <c r="F1217" t="inlineStr"/>
       <c r="G1217" t="inlineStr">
         <is>
           <t>100</t>
@@ -64991,8 +63773,6 @@
           <t>737.972</t>
         </is>
       </c>
-      <c r="E1219" t="inlineStr"/>
-      <c r="F1219" t="inlineStr"/>
       <c r="G1219" t="inlineStr">
         <is>
           <t>100</t>
@@ -65097,8 +63877,6 @@
           <t>744.0399</t>
         </is>
       </c>
-      <c r="E1221" t="inlineStr"/>
-      <c r="F1221" t="inlineStr"/>
       <c r="G1221" t="inlineStr">
         <is>
           <t>100</t>
@@ -65203,8 +63981,6 @@
           <t>743.698</t>
         </is>
       </c>
-      <c r="E1223" t="inlineStr"/>
-      <c r="F1223" t="inlineStr"/>
       <c r="G1223" t="inlineStr">
         <is>
           <t>100</t>
@@ -65309,8 +64085,6 @@
           <t>741.91</t>
         </is>
       </c>
-      <c r="E1225" t="inlineStr"/>
-      <c r="F1225" t="inlineStr"/>
       <c r="G1225" t="inlineStr">
         <is>
           <t>100</t>
@@ -65358,8 +64132,6 @@
           <t>741.0477</t>
         </is>
       </c>
-      <c r="E1226" t="inlineStr"/>
-      <c r="F1226" t="inlineStr"/>
       <c r="G1226" t="inlineStr">
         <is>
           <t>100</t>
@@ -65407,8 +64179,6 @@
           <t>738.195</t>
         </is>
       </c>
-      <c r="E1227" t="inlineStr"/>
-      <c r="F1227" t="inlineStr"/>
       <c r="G1227" t="inlineStr">
         <is>
           <t>100</t>
@@ -65627,8 +64397,6 @@
           <t>738.4334</t>
         </is>
       </c>
-      <c r="E1231" t="inlineStr"/>
-      <c r="F1231" t="inlineStr"/>
       <c r="G1231" t="inlineStr">
         <is>
           <t>100</t>
@@ -65733,8 +64501,6 @@
           <t>737.725</t>
         </is>
       </c>
-      <c r="E1233" t="inlineStr"/>
-      <c r="F1233" t="inlineStr"/>
       <c r="G1233" t="inlineStr">
         <is>
           <t>100</t>
@@ -65839,8 +64605,6 @@
           <t>737.3836</t>
         </is>
       </c>
-      <c r="E1235" t="inlineStr"/>
-      <c r="F1235" t="inlineStr"/>
       <c r="G1235" t="inlineStr">
         <is>
           <t>100</t>
@@ -65888,8 +64652,6 @@
           <t>736.525</t>
         </is>
       </c>
-      <c r="E1236" t="inlineStr"/>
-      <c r="F1236" t="inlineStr"/>
       <c r="G1236" t="inlineStr">
         <is>
           <t>100</t>
@@ -65994,8 +64756,6 @@
           <t>737.4379</t>
         </is>
       </c>
-      <c r="E1238" t="inlineStr"/>
-      <c r="F1238" t="inlineStr"/>
       <c r="G1238" t="inlineStr">
         <is>
           <t>100</t>
@@ -66157,8 +64917,6 @@
           <t>736.69</t>
         </is>
       </c>
-      <c r="E1241" t="inlineStr"/>
-      <c r="F1241" t="inlineStr"/>
       <c r="G1241" t="inlineStr">
         <is>
           <t>100</t>
@@ -66263,8 +65021,6 @@
           <t>737.5099</t>
         </is>
       </c>
-      <c r="E1243" t="inlineStr"/>
-      <c r="F1243" t="inlineStr"/>
       <c r="G1243" t="inlineStr">
         <is>
           <t>100</t>
@@ -66312,8 +65068,6 @@
           <t>737.965</t>
         </is>
       </c>
-      <c r="E1244" t="inlineStr"/>
-      <c r="F1244" t="inlineStr"/>
       <c r="G1244" t="inlineStr">
         <is>
           <t>100</t>
@@ -66418,8 +65172,6 @@
           <t>738.305</t>
         </is>
       </c>
-      <c r="E1246" t="inlineStr"/>
-      <c r="F1246" t="inlineStr"/>
       <c r="G1246" t="inlineStr">
         <is>
           <t>100</t>
@@ -66581,8 +65333,6 @@
           <t>742.1897</t>
         </is>
       </c>
-      <c r="E1249" t="inlineStr"/>
-      <c r="F1249" t="inlineStr"/>
       <c r="G1249" t="inlineStr">
         <is>
           <t>100</t>
@@ -66687,8 +65437,6 @@
           <t>741.32</t>
         </is>
       </c>
-      <c r="E1251" t="inlineStr"/>
-      <c r="F1251" t="inlineStr"/>
       <c r="G1251" t="inlineStr">
         <is>
           <t>100</t>
@@ -66793,8 +65541,6 @@
           <t>740.09</t>
         </is>
       </c>
-      <c r="E1253" t="inlineStr"/>
-      <c r="F1253" t="inlineStr"/>
       <c r="G1253" t="inlineStr">
         <is>
           <t>100</t>
@@ -66899,8 +65645,6 @@
           <t>739.47</t>
         </is>
       </c>
-      <c r="E1255" t="inlineStr"/>
-      <c r="F1255" t="inlineStr"/>
       <c r="G1255" t="inlineStr">
         <is>
           <t>100</t>
@@ -67005,8 +65749,6 @@
           <t>739.535</t>
         </is>
       </c>
-      <c r="E1257" t="inlineStr"/>
-      <c r="F1257" t="inlineStr"/>
       <c r="G1257" t="inlineStr">
         <is>
           <t>100</t>
@@ -67111,8 +65853,6 @@
           <t>736.9999</t>
         </is>
       </c>
-      <c r="E1259" t="inlineStr"/>
-      <c r="F1259" t="inlineStr"/>
       <c r="G1259" t="inlineStr">
         <is>
           <t>100</t>
@@ -67160,8 +65900,6 @@
           <t>737.12</t>
         </is>
       </c>
-      <c r="E1260" t="inlineStr"/>
-      <c r="F1260" t="inlineStr"/>
       <c r="G1260" t="inlineStr">
         <is>
           <t>100</t>
@@ -67266,8 +66004,6 @@
           <t>737.6899</t>
         </is>
       </c>
-      <c r="E1262" t="inlineStr"/>
-      <c r="F1262" t="inlineStr"/>
       <c r="G1262" t="inlineStr">
         <is>
           <t>100</t>
@@ -67372,8 +66108,6 @@
           <t>735.916</t>
         </is>
       </c>
-      <c r="E1264" t="inlineStr"/>
-      <c r="F1264" t="inlineStr"/>
       <c r="G1264" t="inlineStr">
         <is>
           <t>100</t>
@@ -67535,8 +66269,6 @@
           <t>734.125</t>
         </is>
       </c>
-      <c r="E1267" t="inlineStr"/>
-      <c r="F1267" t="inlineStr"/>
       <c r="G1267" t="inlineStr">
         <is>
           <t>100</t>
@@ -67641,8 +66373,6 @@
           <t>734.905</t>
         </is>
       </c>
-      <c r="E1269" t="inlineStr"/>
-      <c r="F1269" t="inlineStr"/>
       <c r="G1269" t="inlineStr">
         <is>
           <t>100</t>
@@ -67747,8 +66477,6 @@
           <t>734.825</t>
         </is>
       </c>
-      <c r="E1271" t="inlineStr"/>
-      <c r="F1271" t="inlineStr"/>
       <c r="G1271" t="inlineStr">
         <is>
           <t>100</t>
@@ -67853,8 +66581,6 @@
           <t>735.12</t>
         </is>
       </c>
-      <c r="E1273" t="inlineStr"/>
-      <c r="F1273" t="inlineStr"/>
       <c r="G1273" t="inlineStr">
         <is>
           <t>100</t>
@@ -67959,8 +66685,6 @@
           <t>735.325</t>
         </is>
       </c>
-      <c r="E1275" t="inlineStr"/>
-      <c r="F1275" t="inlineStr"/>
       <c r="G1275" t="inlineStr">
         <is>
           <t>100</t>
@@ -68065,8 +66789,6 @@
           <t>734.8499</t>
         </is>
       </c>
-      <c r="E1277" t="inlineStr"/>
-      <c r="F1277" t="inlineStr"/>
       <c r="G1277" t="inlineStr">
         <is>
           <t>100</t>
@@ -68171,8 +66893,6 @@
           <t>734.9201</t>
         </is>
       </c>
-      <c r="E1279" t="inlineStr"/>
-      <c r="F1279" t="inlineStr"/>
       <c r="G1279" t="inlineStr">
         <is>
           <t>100</t>
@@ -68277,8 +66997,6 @@
           <t>737.285</t>
         </is>
       </c>
-      <c r="E1281" t="inlineStr"/>
-      <c r="F1281" t="inlineStr"/>
       <c r="G1281" t="inlineStr">
         <is>
           <t>100</t>
@@ -68383,8 +67101,6 @@
           <t>737.555</t>
         </is>
       </c>
-      <c r="E1283" t="inlineStr"/>
-      <c r="F1283" t="inlineStr"/>
       <c r="G1283" t="inlineStr">
         <is>
           <t>100</t>
@@ -68432,8 +67148,6 @@
           <t>738.085</t>
         </is>
       </c>
-      <c r="E1284" t="inlineStr"/>
-      <c r="F1284" t="inlineStr"/>
       <c r="G1284" t="inlineStr">
         <is>
           <t>100</t>
@@ -68595,8 +67309,6 @@
           <t>735.4507</t>
         </is>
       </c>
-      <c r="E1287" t="inlineStr"/>
-      <c r="F1287" t="inlineStr"/>
       <c r="G1287" t="inlineStr">
         <is>
           <t>100</t>
@@ -68644,8 +67356,6 @@
           <t>735.4434</t>
         </is>
       </c>
-      <c r="E1288" t="inlineStr"/>
-      <c r="F1288" t="inlineStr"/>
       <c r="G1288" t="inlineStr">
         <is>
           <t>100</t>
@@ -68807,8 +67517,6 @@
           <t>739.0299</t>
         </is>
       </c>
-      <c r="E1291" t="inlineStr"/>
-      <c r="F1291" t="inlineStr"/>
       <c r="G1291" t="inlineStr">
         <is>
           <t>100</t>
@@ -68913,8 +67621,6 @@
           <t>742.4299</t>
         </is>
       </c>
-      <c r="E1293" t="inlineStr"/>
-      <c r="F1293" t="inlineStr"/>
       <c r="G1293" t="inlineStr">
         <is>
           <t>100</t>
@@ -68962,8 +67668,6 @@
           <t>738.5</t>
         </is>
       </c>
-      <c r="E1294" t="inlineStr"/>
-      <c r="F1294" t="inlineStr"/>
       <c r="G1294" t="inlineStr">
         <is>
           <t>100</t>
@@ -69125,8 +67829,6 @@
           <t>739.01</t>
         </is>
       </c>
-      <c r="E1297" t="inlineStr"/>
-      <c r="F1297" t="inlineStr"/>
       <c r="G1297" t="inlineStr">
         <is>
           <t>100</t>
@@ -69231,8 +67933,6 @@
           <t>740.4068</t>
         </is>
       </c>
-      <c r="E1299" t="inlineStr"/>
-      <c r="F1299" t="inlineStr"/>
       <c r="G1299" t="inlineStr">
         <is>
           <t>100</t>
@@ -69337,8 +68037,6 @@
           <t>741.0316</t>
         </is>
       </c>
-      <c r="E1301" t="inlineStr"/>
-      <c r="F1301" t="inlineStr"/>
       <c r="G1301" t="inlineStr">
         <is>
           <t>100</t>
@@ -69443,8 +68141,6 @@
           <t>741.97</t>
         </is>
       </c>
-      <c r="E1303" t="inlineStr"/>
-      <c r="F1303" t="inlineStr"/>
       <c r="G1303" t="inlineStr">
         <is>
           <t>100</t>
@@ -69549,8 +68245,6 @@
           <t>742.34</t>
         </is>
       </c>
-      <c r="E1305" t="inlineStr"/>
-      <c r="F1305" t="inlineStr"/>
       <c r="G1305" t="inlineStr">
         <is>
           <t>100</t>
@@ -69598,8 +68292,6 @@
           <t>741.6987</t>
         </is>
       </c>
-      <c r="E1306" t="inlineStr"/>
-      <c r="F1306" t="inlineStr"/>
       <c r="G1306" t="inlineStr">
         <is>
           <t>100</t>
@@ -69704,8 +68396,6 @@
           <t>740.8492</t>
         </is>
       </c>
-      <c r="E1308" t="inlineStr"/>
-      <c r="F1308" t="inlineStr"/>
       <c r="G1308" t="inlineStr">
         <is>
           <t>100</t>
@@ -69924,8 +68614,6 @@
           <t>763.0196</t>
         </is>
       </c>
-      <c r="E1312" t="inlineStr"/>
-      <c r="F1312" t="inlineStr"/>
       <c r="G1312" t="inlineStr">
         <is>
           <t>100</t>
@@ -70030,8 +68718,6 @@
           <t>764.03</t>
         </is>
       </c>
-      <c r="E1314" t="inlineStr"/>
-      <c r="F1314" t="inlineStr"/>
       <c r="G1314" t="inlineStr">
         <is>
           <t>100</t>
@@ -70136,8 +68822,6 @@
           <t>764.23</t>
         </is>
       </c>
-      <c r="E1316" t="inlineStr"/>
-      <c r="F1316" t="inlineStr"/>
       <c r="G1316" t="inlineStr">
         <is>
           <t>100</t>
@@ -70242,8 +68926,6 @@
           <t>765.01</t>
         </is>
       </c>
-      <c r="E1318" t="inlineStr"/>
-      <c r="F1318" t="inlineStr"/>
       <c r="G1318" t="inlineStr">
         <is>
           <t>100</t>
@@ -70348,8 +69030,6 @@
           <t>764.5499</t>
         </is>
       </c>
-      <c r="E1320" t="inlineStr"/>
-      <c r="F1320" t="inlineStr"/>
       <c r="G1320" t="inlineStr">
         <is>
           <t>100</t>
@@ -70454,8 +69134,6 @@
           <t>767.9</t>
         </is>
       </c>
-      <c r="E1322" t="inlineStr"/>
-      <c r="F1322" t="inlineStr"/>
       <c r="G1322" t="inlineStr">
         <is>
           <t>100</t>
@@ -70560,8 +69238,6 @@
           <t>775.9078</t>
         </is>
       </c>
-      <c r="E1324" t="inlineStr"/>
-      <c r="F1324" t="inlineStr"/>
       <c r="G1324" t="inlineStr">
         <is>
           <t>100</t>
@@ -70666,8 +69342,6 @@
           <t>774.865</t>
         </is>
       </c>
-      <c r="E1326" t="inlineStr"/>
-      <c r="F1326" t="inlineStr"/>
       <c r="G1326" t="inlineStr">
         <is>
           <t>100</t>
@@ -70772,8 +69446,6 @@
           <t>774.405</t>
         </is>
       </c>
-      <c r="E1328" t="inlineStr"/>
-      <c r="F1328" t="inlineStr"/>
       <c r="G1328" t="inlineStr">
         <is>
           <t>100</t>
@@ -70878,8 +69550,6 @@
           <t>774.58</t>
         </is>
       </c>
-      <c r="E1330" t="inlineStr"/>
-      <c r="F1330" t="inlineStr"/>
       <c r="G1330" t="inlineStr">
         <is>
           <t>100</t>
@@ -70984,8 +69654,6 @@
           <t>774.425</t>
         </is>
       </c>
-      <c r="E1332" t="inlineStr"/>
-      <c r="F1332" t="inlineStr"/>
       <c r="G1332" t="inlineStr">
         <is>
           <t>100</t>
@@ -71090,8 +69758,6 @@
           <t>772.7751</t>
         </is>
       </c>
-      <c r="E1334" t="inlineStr"/>
-      <c r="F1334" t="inlineStr"/>
       <c r="G1334" t="inlineStr">
         <is>
           <t>100</t>
@@ -71196,8 +69862,6 @@
           <t>773.4704</t>
         </is>
       </c>
-      <c r="E1336" t="inlineStr"/>
-      <c r="F1336" t="inlineStr"/>
       <c r="G1336" t="inlineStr">
         <is>
           <t>100</t>
@@ -71302,8 +69966,6 @@
           <t>773.855</t>
         </is>
       </c>
-      <c r="E1338" t="inlineStr"/>
-      <c r="F1338" t="inlineStr"/>
       <c r="G1338" t="inlineStr">
         <is>
           <t>100</t>
@@ -71408,8 +70070,6 @@
           <t>773.1454</t>
         </is>
       </c>
-      <c r="E1340" t="inlineStr"/>
-      <c r="F1340" t="inlineStr"/>
       <c r="G1340" t="inlineStr">
         <is>
           <t>100</t>
@@ -71514,8 +70174,6 @@
           <t>772.58</t>
         </is>
       </c>
-      <c r="E1342" t="inlineStr"/>
-      <c r="F1342" t="inlineStr"/>
       <c r="G1342" t="inlineStr">
         <is>
           <t>100</t>
@@ -71620,8 +70278,6 @@
           <t>772.485</t>
         </is>
       </c>
-      <c r="E1344" t="inlineStr"/>
-      <c r="F1344" t="inlineStr"/>
       <c r="G1344" t="inlineStr">
         <is>
           <t>100</t>
@@ -71726,8 +70382,6 @@
           <t>771.8756</t>
         </is>
       </c>
-      <c r="E1346" t="inlineStr"/>
-      <c r="F1346" t="inlineStr"/>
       <c r="G1346" t="inlineStr">
         <is>
           <t>100</t>
@@ -71832,8 +70486,6 @@
           <t>771.335</t>
         </is>
       </c>
-      <c r="E1348" t="inlineStr"/>
-      <c r="F1348" t="inlineStr"/>
       <c r="G1348" t="inlineStr">
         <is>
           <t>100</t>
@@ -71938,8 +70590,6 @@
           <t>771.5195</t>
         </is>
       </c>
-      <c r="E1350" t="inlineStr"/>
-      <c r="F1350" t="inlineStr"/>
       <c r="G1350" t="inlineStr">
         <is>
           <t>100</t>
@@ -72044,8 +70694,6 @@
           <t>771.569</t>
         </is>
       </c>
-      <c r="E1352" t="inlineStr"/>
-      <c r="F1352" t="inlineStr"/>
       <c r="G1352" t="inlineStr">
         <is>
           <t>100</t>
@@ -72150,8 +70798,6 @@
           <t>771.755</t>
         </is>
       </c>
-      <c r="E1354" t="inlineStr"/>
-      <c r="F1354" t="inlineStr"/>
       <c r="G1354" t="inlineStr">
         <is>
           <t>100</t>
@@ -72256,8 +70902,6 @@
           <t>770.3</t>
         </is>
       </c>
-      <c r="E1356" t="inlineStr"/>
-      <c r="F1356" t="inlineStr"/>
       <c r="G1356" t="inlineStr">
         <is>
           <t>100</t>
@@ -72362,8 +71006,6 @@
           <t>770.785</t>
         </is>
       </c>
-      <c r="E1358" t="inlineStr"/>
-      <c r="F1358" t="inlineStr"/>
       <c r="G1358" t="inlineStr">
         <is>
           <t>100</t>
@@ -72468,8 +71110,6 @@
           <t>770.5081</t>
         </is>
       </c>
-      <c r="E1360" t="inlineStr"/>
-      <c r="F1360" t="inlineStr"/>
       <c r="G1360" t="inlineStr">
         <is>
           <t>100</t>
@@ -72574,8 +71214,6 @@
           <t>769.855</t>
         </is>
       </c>
-      <c r="E1362" t="inlineStr"/>
-      <c r="F1362" t="inlineStr"/>
       <c r="G1362" t="inlineStr">
         <is>
           <t>100</t>
@@ -72680,8 +71318,6 @@
           <t>770.02</t>
         </is>
       </c>
-      <c r="E1364" t="inlineStr"/>
-      <c r="F1364" t="inlineStr"/>
       <c r="G1364" t="inlineStr">
         <is>
           <t>100</t>
@@ -72786,8 +71422,6 @@
           <t>770.445</t>
         </is>
       </c>
-      <c r="E1366" t="inlineStr"/>
-      <c r="F1366" t="inlineStr"/>
       <c r="G1366" t="inlineStr">
         <is>
           <t>100</t>
@@ -72892,8 +71526,6 @@
           <t>770.845</t>
         </is>
       </c>
-      <c r="E1368" t="inlineStr"/>
-      <c r="F1368" t="inlineStr"/>
       <c r="G1368" t="inlineStr">
         <is>
           <t>100</t>
@@ -72998,8 +71630,6 @@
           <t>770.3061</t>
         </is>
       </c>
-      <c r="E1370" t="inlineStr"/>
-      <c r="F1370" t="inlineStr"/>
       <c r="G1370" t="inlineStr">
         <is>
           <t>100</t>
@@ -73104,8 +71734,6 @@
           <t>770.5095</t>
         </is>
       </c>
-      <c r="E1372" t="inlineStr"/>
-      <c r="F1372" t="inlineStr"/>
       <c r="G1372" t="inlineStr">
         <is>
           <t>100</t>
@@ -73210,8 +71838,6 @@
           <t>770.56</t>
         </is>
       </c>
-      <c r="E1374" t="inlineStr"/>
-      <c r="F1374" t="inlineStr"/>
       <c r="G1374" t="inlineStr">
         <is>
           <t>100</t>
@@ -73316,8 +71942,6 @@
           <t>770.049</t>
         </is>
       </c>
-      <c r="E1376" t="inlineStr"/>
-      <c r="F1376" t="inlineStr"/>
       <c r="G1376" t="inlineStr">
         <is>
           <t>100</t>
@@ -73422,8 +72046,6 @@
           <t>769.305</t>
         </is>
       </c>
-      <c r="E1378" t="inlineStr"/>
-      <c r="F1378" t="inlineStr"/>
       <c r="G1378" t="inlineStr">
         <is>
           <t>100</t>
@@ -73528,8 +72150,6 @@
           <t>768.255</t>
         </is>
       </c>
-      <c r="E1380" t="inlineStr"/>
-      <c r="F1380" t="inlineStr"/>
       <c r="G1380" t="inlineStr">
         <is>
           <t>100</t>
@@ -73634,8 +72254,6 @@
           <t>769.855</t>
         </is>
       </c>
-      <c r="E1382" t="inlineStr"/>
-      <c r="F1382" t="inlineStr"/>
       <c r="G1382" t="inlineStr">
         <is>
           <t>100</t>
@@ -73740,8 +72358,6 @@
           <t>772.2299</t>
         </is>
       </c>
-      <c r="E1384" t="inlineStr"/>
-      <c r="F1384" t="inlineStr"/>
       <c r="G1384" t="inlineStr">
         <is>
           <t>100</t>
@@ -73846,8 +72462,6 @@
           <t>772.965</t>
         </is>
       </c>
-      <c r="E1386" t="inlineStr"/>
-      <c r="F1386" t="inlineStr"/>
       <c r="G1386" t="inlineStr">
         <is>
           <t>100</t>
@@ -73895,8 +72509,6 @@
           <t>772.6108</t>
         </is>
       </c>
-      <c r="E1387" t="inlineStr"/>
-      <c r="F1387" t="inlineStr"/>
       <c r="G1387" t="inlineStr">
         <is>
           <t>100</t>
@@ -74058,8 +72670,6 @@
           <t>772.8996</t>
         </is>
       </c>
-      <c r="E1390" t="inlineStr"/>
-      <c r="F1390" t="inlineStr"/>
       <c r="G1390" t="inlineStr">
         <is>
           <t>100</t>
@@ -74164,8 +72774,6 @@
           <t>773.4299</t>
         </is>
       </c>
-      <c r="E1392" t="inlineStr"/>
-      <c r="F1392" t="inlineStr"/>
       <c r="G1392" t="inlineStr">
         <is>
           <t>100</t>
@@ -74270,8 +72878,6 @@
           <t>773.4099</t>
         </is>
       </c>
-      <c r="E1394" t="inlineStr"/>
-      <c r="F1394" t="inlineStr"/>
       <c r="G1394" t="inlineStr">
         <is>
           <t>100</t>
@@ -74319,8 +72925,6 @@
           <t>772.9645</t>
         </is>
       </c>
-      <c r="E1395" t="inlineStr"/>
-      <c r="F1395" t="inlineStr"/>
       <c r="G1395" t="inlineStr">
         <is>
           <t>100</t>
@@ -74425,8 +73029,6 @@
           <t>772.175</t>
         </is>
       </c>
-      <c r="E1397" t="inlineStr"/>
-      <c r="F1397" t="inlineStr"/>
       <c r="G1397" t="inlineStr">
         <is>
           <t>100</t>
@@ -74588,8 +73190,6 @@
           <t>774.025</t>
         </is>
       </c>
-      <c r="E1400" t="inlineStr"/>
-      <c r="F1400" t="inlineStr"/>
       <c r="G1400" t="inlineStr">
         <is>
           <t>100</t>
@@ -74694,8 +73294,6 @@
           <t>774.3001</t>
         </is>
       </c>
-      <c r="E1402" t="inlineStr"/>
-      <c r="F1402" t="inlineStr"/>
       <c r="G1402" t="inlineStr">
         <is>
           <t>100</t>
@@ -74800,8 +73398,6 @@
           <t>774.6101</t>
         </is>
       </c>
-      <c r="E1404" t="inlineStr"/>
-      <c r="F1404" t="inlineStr"/>
       <c r="G1404" t="inlineStr">
         <is>
           <t>100</t>
@@ -74906,8 +73502,6 @@
           <t>773.628</t>
         </is>
       </c>
-      <c r="E1406" t="inlineStr"/>
-      <c r="F1406" t="inlineStr"/>
       <c r="G1406" t="inlineStr">
         <is>
           <t>100</t>
@@ -75012,8 +73606,6 @@
           <t>773.9658</t>
         </is>
       </c>
-      <c r="E1408" t="inlineStr"/>
-      <c r="F1408" t="inlineStr"/>
       <c r="G1408" t="inlineStr">
         <is>
           <t>100</t>
@@ -75118,8 +73710,6 @@
           <t>773.77</t>
         </is>
       </c>
-      <c r="E1410" t="inlineStr"/>
-      <c r="F1410" t="inlineStr"/>
       <c r="G1410" t="inlineStr">
         <is>
           <t>100</t>
@@ -75224,8 +73814,6 @@
           <t>773.46</t>
         </is>
       </c>
-      <c r="E1412" t="inlineStr"/>
-      <c r="F1412" t="inlineStr"/>
       <c r="G1412" t="inlineStr">
         <is>
           <t>100</t>
@@ -75330,8 +73918,6 @@
           <t>773.9</t>
         </is>
       </c>
-      <c r="E1414" t="inlineStr"/>
-      <c r="F1414" t="inlineStr"/>
       <c r="G1414" t="inlineStr">
         <is>
           <t>100</t>
@@ -75436,8 +74022,6 @@
           <t>774.115</t>
         </is>
       </c>
-      <c r="E1416" t="inlineStr"/>
-      <c r="F1416" t="inlineStr"/>
       <c r="G1416" t="inlineStr">
         <is>
           <t>100</t>
@@ -75542,8 +74126,6 @@
           <t>773.7472</t>
         </is>
       </c>
-      <c r="E1418" t="inlineStr"/>
-      <c r="F1418" t="inlineStr"/>
       <c r="G1418" t="inlineStr">
         <is>
           <t>100</t>
@@ -75648,8 +74230,6 @@
           <t>772.9363</t>
         </is>
       </c>
-      <c r="E1420" t="inlineStr"/>
-      <c r="F1420" t="inlineStr"/>
       <c r="G1420" t="inlineStr">
         <is>
           <t>100</t>
@@ -75754,8 +74334,6 @@
           <t>773.1</t>
         </is>
       </c>
-      <c r="E1422" t="inlineStr"/>
-      <c r="F1422" t="inlineStr"/>
       <c r="G1422" t="inlineStr">
         <is>
           <t>100</t>
@@ -75860,8 +74438,6 @@
           <t>772.7795</t>
         </is>
       </c>
-      <c r="E1424" t="inlineStr"/>
-      <c r="F1424" t="inlineStr"/>
       <c r="G1424" t="inlineStr">
         <is>
           <t>100</t>
@@ -75966,8 +74542,6 @@
           <t>756.885</t>
         </is>
       </c>
-      <c r="E1426" t="inlineStr"/>
-      <c r="F1426" t="inlineStr"/>
       <c r="G1426" t="inlineStr">
         <is>
           <t>100</t>
@@ -76015,8 +74589,6 @@
           <t>759.16</t>
         </is>
       </c>
-      <c r="E1427" t="inlineStr"/>
-      <c r="F1427" t="inlineStr"/>
       <c r="G1427" t="inlineStr">
         <is>
           <t>100</t>
@@ -76156,6 +74728,47 @@
           <t>09:59:18</t>
         </is>
       </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1430" t="inlineStr">
+        <is>
+          <t>15:28:52</t>
+        </is>
+      </c>
+      <c r="C1430" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1430" t="inlineStr">
+        <is>
+          <t>766.105</t>
+        </is>
+      </c>
+      <c r="E1430" t="inlineStr"/>
+      <c r="F1430" t="inlineStr"/>
+      <c r="G1430" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H1430" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I1430" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J1430" t="inlineStr"/>
+      <c r="K1430" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/trades_all.xlsx
+++ b/trades_all.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1430"/>
+  <dimension ref="A1:K1435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74750,8 +74750,6 @@
           <t>766.105</t>
         </is>
       </c>
-      <c r="E1430" t="inlineStr"/>
-      <c r="F1430" t="inlineStr"/>
       <c r="G1430" t="inlineStr">
         <is>
           <t>100</t>
@@ -74764,11 +74762,284 @@
       </c>
       <c r="I1430" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J1430" t="inlineStr"/>
-      <c r="K1430" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J1430" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="K1430" t="inlineStr">
+        <is>
+          <t>11:46:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1431" t="inlineStr">
+        <is>
+          <t>09:44:11</t>
+        </is>
+      </c>
+      <c r="C1431" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1431" t="inlineStr">
+        <is>
+          <t>765.0957</t>
+        </is>
+      </c>
+      <c r="G1431" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H1431" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I1431" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J1431" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="K1431" t="inlineStr">
+        <is>
+          <t>10:08:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1432" t="inlineStr">
+        <is>
+          <t>10:00:39</t>
+        </is>
+      </c>
+      <c r="C1432" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1432" t="inlineStr">
+        <is>
+          <t>765.5699</t>
+        </is>
+      </c>
+      <c r="G1432" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H1432" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I1432" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J1432" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="K1432" t="inlineStr">
+        <is>
+          <t>15:51:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1433" t="inlineStr">
+        <is>
+          <t>15:51:06</t>
+        </is>
+      </c>
+      <c r="C1433" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1433" t="inlineStr">
+        <is>
+          <t>765.57</t>
+        </is>
+      </c>
+      <c r="E1433" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="F1433" t="inlineStr">
+        <is>
+          <t>-1.57</t>
+        </is>
+      </c>
+      <c r="G1433" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H1433" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I1433" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J1433" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="K1433" t="inlineStr">
+        <is>
+          <t>10:00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1434" t="inlineStr">
+        <is>
+          <t>10:08:02</t>
+        </is>
+      </c>
+      <c r="C1434" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1434" t="inlineStr">
+        <is>
+          <t>771.1939</t>
+        </is>
+      </c>
+      <c r="E1434" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="F1434" t="inlineStr">
+        <is>
+          <t>+608.23</t>
+        </is>
+      </c>
+      <c r="G1434" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H1434" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I1434" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J1434" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="K1434" t="inlineStr">
+        <is>
+          <t>09:44:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1435" t="inlineStr">
+        <is>
+          <t>11:46:30</t>
+        </is>
+      </c>
+      <c r="C1435" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1435" t="inlineStr">
+        <is>
+          <t>763.5509</t>
+        </is>
+      </c>
+      <c r="E1435" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="F1435" t="inlineStr">
+        <is>
+          <t>-257.00</t>
+        </is>
+      </c>
+      <c r="G1435" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H1435" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I1435" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J1435" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="K1435" t="inlineStr">
+        <is>
+          <t>15:28:52</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/trades_all.xlsx
+++ b/trades_all.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1435"/>
+  <dimension ref="A1:K1439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75041,6 +75041,194 @@
         </is>
       </c>
     </row>
+    <row r="1436">
+      <c r="A1436" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1436" t="inlineStr">
+        <is>
+          <t>11:56:57</t>
+        </is>
+      </c>
+      <c r="C1436" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1436" t="n">
+        <v>769.9367</v>
+      </c>
+      <c r="G1436" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1436" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I1436" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1436" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="K1436" t="inlineStr">
+        <is>
+          <t>12:02:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1437" t="inlineStr">
+        <is>
+          <t>12:02:13</t>
+        </is>
+      </c>
+      <c r="C1437" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1437" t="n">
+        <v>770.645</v>
+      </c>
+      <c r="E1437" t="inlineStr">
+        <is>
+          <t>多</t>
+        </is>
+      </c>
+      <c r="F1437" t="n">
+        <v>69.23999999999999</v>
+      </c>
+      <c r="G1437" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1437" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I1437" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1437" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="K1437" t="inlineStr">
+        <is>
+          <t>11:56:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1438" t="inlineStr">
+        <is>
+          <t>12:03:33</t>
+        </is>
+      </c>
+      <c r="C1438" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1438" t="n">
+        <v>770.2</v>
+      </c>
+      <c r="G1438" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1438" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I1438" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1438" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="K1438" t="inlineStr">
+        <is>
+          <t>12:10:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1439" t="inlineStr">
+        <is>
+          <t>12:10:50</t>
+        </is>
+      </c>
+      <c r="C1439" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1439" t="n">
+        <v>770.0001</v>
+      </c>
+      <c r="E1439" t="inlineStr">
+        <is>
+          <t>多</t>
+        </is>
+      </c>
+      <c r="F1439" t="n">
+        <v>-21.58</v>
+      </c>
+      <c r="G1439" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1439" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I1439" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1439" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="K1439" t="inlineStr">
+        <is>
+          <t>12:03:33</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trades_all.xlsx
+++ b/trades_all.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1439"/>
+  <dimension ref="A1:K1444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75229,6 +75229,199 @@
         </is>
       </c>
     </row>
+    <row r="1440">
+      <c r="A1440" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1440" t="inlineStr">
+        <is>
+          <t>12:14:09</t>
+        </is>
+      </c>
+      <c r="C1440" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1440" t="n">
+        <v>767.635</v>
+      </c>
+      <c r="G1440" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1440" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I1440" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1440" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="K1440" t="inlineStr">
+        <is>
+          <t>12:21:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1441" t="inlineStr">
+        <is>
+          <t>12:21:53</t>
+        </is>
+      </c>
+      <c r="C1441" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1441" t="n">
+        <v>767.7837</v>
+      </c>
+      <c r="E1441" t="inlineStr">
+        <is>
+          <t>多</t>
+        </is>
+      </c>
+      <c r="F1441" t="n">
+        <v>13.29</v>
+      </c>
+      <c r="G1441" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1441" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I1441" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1441" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="K1441" t="inlineStr">
+        <is>
+          <t>12:14:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1442" t="inlineStr">
+        <is>
+          <t>12:35:27</t>
+        </is>
+      </c>
+      <c r="C1442" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1442" t="n">
+        <v>766.6396</v>
+      </c>
+      <c r="G1442" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1442" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I1442" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1443" t="inlineStr">
+        <is>
+          <t>12:56:47</t>
+        </is>
+      </c>
+      <c r="C1443" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1443" t="n">
+        <v>765.9261</v>
+      </c>
+      <c r="G1443" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1443" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I1443" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1444" t="inlineStr">
+        <is>
+          <t>13:12:02</t>
+        </is>
+      </c>
+      <c r="C1444" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1444" t="n">
+        <v>764.01</v>
+      </c>
+      <c r="G1444" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1444" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I1444" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trades_all.xlsx
+++ b/trades_all.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1444"/>
+  <dimension ref="A1:K1447"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75352,7 +75352,17 @@
       </c>
       <c r="I1442" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J1442" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="K1442" t="inlineStr">
+        <is>
+          <t>11:34:09</t>
         </is>
       </c>
     </row>
@@ -75385,7 +75395,17 @@
       </c>
       <c r="I1443" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J1443" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="K1443" t="inlineStr">
+        <is>
+          <t>11:20:41</t>
         </is>
       </c>
     </row>
@@ -75418,7 +75438,170 @@
       </c>
       <c r="I1444" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J1444" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="K1444" t="inlineStr">
+        <is>
+          <t>11:18:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B1445" t="inlineStr">
+        <is>
+          <t>11:18:33</t>
+        </is>
+      </c>
+      <c r="C1445" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1445" t="n">
+        <v>769.062</v>
+      </c>
+      <c r="E1445" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="F1445" t="n">
+        <v>503.62</v>
+      </c>
+      <c r="G1445" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1445" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I1445" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J1445" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="K1445" t="inlineStr">
+        <is>
+          <t>13:12:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B1446" t="inlineStr">
+        <is>
+          <t>11:20:41</t>
+        </is>
+      </c>
+      <c r="C1446" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1446" t="n">
+        <v>769.1316</v>
+      </c>
+      <c r="E1446" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="F1446" t="n">
+        <v>318.97</v>
+      </c>
+      <c r="G1446" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1446" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I1446" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J1446" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="K1446" t="inlineStr">
+        <is>
+          <t>12:56:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B1447" t="inlineStr">
+        <is>
+          <t>11:34:09</t>
+        </is>
+      </c>
+      <c r="C1447" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1447" t="n">
+        <v>769.755</v>
+      </c>
+      <c r="E1447" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="F1447" t="n">
+        <v>309.95</v>
+      </c>
+      <c r="G1447" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1447" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I1447" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J1447" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="K1447" t="inlineStr">
+        <is>
+          <t>12:35:27</t>
         </is>
       </c>
     </row>

--- a/trades_all.xlsx
+++ b/trades_all.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1447"/>
+  <dimension ref="A1:K1449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75605,6 +75605,100 @@
         </is>
       </c>
     </row>
+    <row r="1448">
+      <c r="A1448" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B1448" t="inlineStr">
+        <is>
+          <t>09:38:25</t>
+        </is>
+      </c>
+      <c r="C1448" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1448" t="n">
+        <v>770.3499</v>
+      </c>
+      <c r="G1448" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1448" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I1448" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1448" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="K1448" t="inlineStr">
+        <is>
+          <t>10:16:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B1449" t="inlineStr">
+        <is>
+          <t>10:16:02</t>
+        </is>
+      </c>
+      <c r="C1449" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1449" t="n">
+        <v>768.95</v>
+      </c>
+      <c r="E1449" t="inlineStr">
+        <is>
+          <t>多</t>
+        </is>
+      </c>
+      <c r="F1449" t="n">
+        <v>-141.57</v>
+      </c>
+      <c r="G1449" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1449" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I1449" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1449" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="K1449" t="inlineStr">
+        <is>
+          <t>09:38:25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trades_all.xlsx
+++ b/trades_all.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1449"/>
+  <dimension ref="A1:K1453"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75699,6 +75699,138 @@
         </is>
       </c>
     </row>
+    <row r="1450">
+      <c r="A1450" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1450" t="inlineStr">
+        <is>
+          <t>11:32:46</t>
+        </is>
+      </c>
+      <c r="C1450" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1450" t="n">
+        <v>763.1416</v>
+      </c>
+      <c r="G1450" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1450" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I1450" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1451" t="inlineStr">
+        <is>
+          <t>12:34:33</t>
+        </is>
+      </c>
+      <c r="C1451" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1451" t="n">
+        <v>764.1999</v>
+      </c>
+      <c r="G1451" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1451" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I1451" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1452" t="inlineStr">
+        <is>
+          <t>14:56:49</t>
+        </is>
+      </c>
+      <c r="C1452" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1452" t="n">
+        <v>762.09</v>
+      </c>
+      <c r="G1452" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1452" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I1452" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1453" t="inlineStr">
+        <is>
+          <t>15:05:26</t>
+        </is>
+      </c>
+      <c r="C1453" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1453" t="n">
+        <v>761.8049999999999</v>
+      </c>
+      <c r="G1453" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1453" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I1453" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trades_all.xlsx
+++ b/trades_all.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1453"/>
+  <dimension ref="A1:K1461"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75728,7 +75728,17 @@
       </c>
       <c r="I1450" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J1450" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="K1450" t="inlineStr">
+        <is>
+          <t>11:57:35</t>
         </is>
       </c>
     </row>
@@ -75761,7 +75771,17 @@
       </c>
       <c r="I1451" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J1451" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="K1451" t="inlineStr">
+        <is>
+          <t>11:55:53</t>
         </is>
       </c>
     </row>
@@ -75794,7 +75814,17 @@
       </c>
       <c r="I1452" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J1452" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="K1452" t="inlineStr">
+        <is>
+          <t>11:55:02</t>
         </is>
       </c>
     </row>
@@ -75827,7 +75857,409 @@
       </c>
       <c r="I1453" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J1453" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="K1453" t="inlineStr">
+        <is>
+          <t>11:52:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B1454" t="inlineStr">
+        <is>
+          <t>13:19:47</t>
+        </is>
+      </c>
+      <c r="C1454" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1454" t="n">
+        <v>760.87</v>
+      </c>
+      <c r="G1454" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1454" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I1454" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J1454" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="K1454" t="inlineStr">
+        <is>
+          <t>11:51:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="A1455" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B1455" t="inlineStr">
+        <is>
+          <t>09:57:54</t>
+        </is>
+      </c>
+      <c r="C1455" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1455" t="n">
+        <v>766.36</v>
+      </c>
+      <c r="G1455" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1455" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I1455" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1455" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="K1455" t="inlineStr">
+        <is>
+          <t>10:45:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B1456" t="inlineStr">
+        <is>
+          <t>10:45:39</t>
+        </is>
+      </c>
+      <c r="C1456" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1456" t="n">
+        <v>767.5154</v>
+      </c>
+      <c r="E1456" t="inlineStr">
+        <is>
+          <t>多</t>
+        </is>
+      </c>
+      <c r="F1456" t="n">
+        <v>113.96</v>
+      </c>
+      <c r="G1456" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1456" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I1456" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1456" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="K1456" t="inlineStr">
+        <is>
+          <t>09:57:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B1457" t="inlineStr">
+        <is>
+          <t>11:51:49</t>
+        </is>
+      </c>
+      <c r="C1457" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1457" t="n">
+        <v>770.375</v>
+      </c>
+      <c r="E1457" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="F1457" t="n">
+        <v>948.91</v>
+      </c>
+      <c r="G1457" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1457" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I1457" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J1457" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="K1457" t="inlineStr">
+        <is>
+          <t>13:19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B1458" t="inlineStr">
+        <is>
+          <t>11:52:34</t>
+        </is>
+      </c>
+      <c r="C1458" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1458" t="n">
+        <v>770.325</v>
+      </c>
+      <c r="E1458" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="F1458" t="n">
+        <v>850.41</v>
+      </c>
+      <c r="G1458" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1458" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I1458" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J1458" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="K1458" t="inlineStr">
+        <is>
+          <t>15:05:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B1459" t="inlineStr">
+        <is>
+          <t>11:55:02</t>
+        </is>
+      </c>
+      <c r="C1459" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1459" t="n">
+        <v>770.3583</v>
+      </c>
+      <c r="E1459" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="F1459" t="n">
+        <v>825.24</v>
+      </c>
+      <c r="G1459" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1459" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I1459" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J1459" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="K1459" t="inlineStr">
+        <is>
+          <t>14:56:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B1460" t="inlineStr">
+        <is>
+          <t>11:55:53</t>
+        </is>
+      </c>
+      <c r="C1460" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1460" t="n">
+        <v>770.4267</v>
+      </c>
+      <c r="E1460" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="F1460" t="n">
+        <v>621.09</v>
+      </c>
+      <c r="G1460" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1460" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I1460" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J1460" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="K1460" t="inlineStr">
+        <is>
+          <t>12:34:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B1461" t="inlineStr">
+        <is>
+          <t>11:57:35</t>
+        </is>
+      </c>
+      <c r="C1461" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1461" t="n">
+        <v>770.45</v>
+      </c>
+      <c r="E1461" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="F1461" t="n">
+        <v>729.25</v>
+      </c>
+      <c r="G1461" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1461" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I1461" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J1461" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="K1461" t="inlineStr">
+        <is>
+          <t>11:32:46</t>
         </is>
       </c>
     </row>

--- a/trades_all.xlsx
+++ b/trades_all.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1461"/>
+  <dimension ref="A1:K1463"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76263,6 +76263,100 @@
         </is>
       </c>
     </row>
+    <row r="1462">
+      <c r="A1462" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B1462" t="inlineStr">
+        <is>
+          <t>09:54:29</t>
+        </is>
+      </c>
+      <c r="C1462" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1462" t="n">
+        <v>768.29</v>
+      </c>
+      <c r="G1462" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1462" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I1462" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1462" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="K1462" t="inlineStr">
+        <is>
+          <t>10:00:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B1463" t="inlineStr">
+        <is>
+          <t>10:00:07</t>
+        </is>
+      </c>
+      <c r="C1463" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1463" t="n">
+        <v>768.8757000000001</v>
+      </c>
+      <c r="E1463" t="inlineStr">
+        <is>
+          <t>多</t>
+        </is>
+      </c>
+      <c r="F1463" t="n">
+        <v>56.99</v>
+      </c>
+      <c r="G1463" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1463" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I1463" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J1463" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="K1463" t="inlineStr">
+        <is>
+          <t>09:54:29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trades_all.xlsx
+++ b/trades_all.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1463"/>
+  <dimension ref="A1:K1469"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76357,6 +76357,204 @@
         </is>
       </c>
     </row>
+    <row r="1464">
+      <c r="A1464" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B1464" t="inlineStr">
+        <is>
+          <t>09:41:22</t>
+        </is>
+      </c>
+      <c r="C1464" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1464" t="n">
+        <v>760.8222</v>
+      </c>
+      <c r="G1464" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1464" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I1464" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B1465" t="inlineStr">
+        <is>
+          <t>09:53:59</t>
+        </is>
+      </c>
+      <c r="C1465" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1465" t="n">
+        <v>760.4698</v>
+      </c>
+      <c r="G1465" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1465" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I1465" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B1466" t="inlineStr">
+        <is>
+          <t>10:09:23</t>
+        </is>
+      </c>
+      <c r="C1466" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1466" t="n">
+        <v>759.8099</v>
+      </c>
+      <c r="G1466" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1466" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I1466" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B1467" t="inlineStr">
+        <is>
+          <t>10:12:09</t>
+        </is>
+      </c>
+      <c r="C1467" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1467" t="n">
+        <v>759.0599</v>
+      </c>
+      <c r="G1467" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1467" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I1467" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B1468" t="inlineStr">
+        <is>
+          <t>10:13:03</t>
+        </is>
+      </c>
+      <c r="C1468" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1468" t="n">
+        <v>758.8049999999999</v>
+      </c>
+      <c r="G1468" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1468" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I1468" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B1469" t="inlineStr">
+        <is>
+          <t>11:16:12</t>
+        </is>
+      </c>
+      <c r="C1469" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D1469" t="n">
+        <v>758.655</v>
+      </c>
+      <c r="G1469" t="n">
+        <v>100</v>
+      </c>
+      <c r="H1469" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I1469" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
